--- a/calculatie/Thebe22_calculatiemodel_VDL.xlsx
+++ b/calculatie/Thebe22_calculatiemodel_VDL.xlsx
@@ -13,9 +13,11 @@
     <sheet name="Risicos" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eenheidsprijzen" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Optimalisaties" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NvI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Tellingen" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -193,6 +195,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -691,7 +696,7 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ook de hoeveelheden zijn aannames uit de teksten van BBN en Winkelman. Tekeningen (bijlage 1 t/m 4, L.0.01, T.0.01, R.0.01) waren bij het opstellen niet beschikbaar. Tel alle aantallen na op tekening.</t>
+          <t>Versie 2 (25-09-2026): installatie-aantallen zijn geteld op de tekeningen E.001, L.0.01-A/B, D.0.01-A/B, T.0.01, T.0.02, R.0.01 en R.-1.01 (zie tabblad 'Tellingen'). De Nota van Inlichtingen van 21-09-2026 is verwerkt (zie tabblad 'NvI'). De bouwkundige tekeningen (BBN bijlage 1 t/m 4) ontbreken nog: wandlengtes en vloeroppervlakken zijn afgeleid uit het stramien van 7,2 m. Tel alles na op DWG.</t>
         </is>
       </c>
     </row>
@@ -844,11 +849,11 @@
       </c>
       <c r="C5" s="11" t="n"/>
       <c r="D5" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,13)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,13)</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,13)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,13)</f>
         <v/>
       </c>
       <c r="F5" s="13">
@@ -873,11 +878,11 @@
       </c>
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,14)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,14)</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,14)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,14)</f>
         <v/>
       </c>
       <c r="F6" s="13">
@@ -902,11 +907,11 @@
       </c>
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,15)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,15)</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,15)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,15)</f>
         <v/>
       </c>
       <c r="F7" s="13">
@@ -931,11 +936,11 @@
       </c>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,16)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,16)</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,16)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,16)</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -960,11 +965,11 @@
       </c>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,17)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,17)</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,17)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,17)</f>
         <v/>
       </c>
       <c r="F9" s="13">
@@ -989,11 +994,11 @@
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,18)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,18)</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,18)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,18)</f>
         <v/>
       </c>
       <c r="F10" s="13">
@@ -1018,11 +1023,11 @@
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,19)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,19)</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,19)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,19)</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1047,11 +1052,11 @@
       </c>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,20)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,20)</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,20)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,20)</f>
         <v/>
       </c>
       <c r="F12" s="13">
@@ -1076,11 +1081,11 @@
       </c>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,21)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,21)</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,21)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,21)</f>
         <v/>
       </c>
       <c r="F13" s="13">
@@ -1121,11 +1126,11 @@
       </c>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,23)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,23)</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,23)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,23)</f>
         <v/>
       </c>
       <c r="F15" s="13">
@@ -1150,11 +1155,11 @@
       </c>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,24)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,24)</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,24)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,24)</f>
         <v/>
       </c>
       <c r="F16" s="13">
@@ -1179,11 +1184,11 @@
       </c>
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,25)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,25)</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,25)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,25)</f>
         <v/>
       </c>
       <c r="F17" s="13">
@@ -1208,11 +1213,11 @@
       </c>
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,26)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,26)</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,26)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,26)</f>
         <v/>
       </c>
       <c r="F18" s="13">
@@ -1237,11 +1242,11 @@
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,27)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,27)</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,27)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,27)</f>
         <v/>
       </c>
       <c r="F19" s="13">
@@ -1266,11 +1271,11 @@
       </c>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,28)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,28)</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,28)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,28)</f>
         <v/>
       </c>
       <c r="F20" s="13">
@@ -1295,11 +1300,11 @@
       </c>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,29)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,29)</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,29)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,29)</f>
         <v/>
       </c>
       <c r="F21" s="13">
@@ -1324,11 +1329,11 @@
       </c>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,30)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,30)</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,30)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,30)</f>
         <v/>
       </c>
       <c r="F22" s="13">
@@ -1353,11 +1358,11 @@
       </c>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,31)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,31)</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,31)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,31)</f>
         <v/>
       </c>
       <c r="F23" s="13">
@@ -1382,11 +1387,11 @@
       </c>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,32)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,32)</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,32)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,32)</f>
         <v/>
       </c>
       <c r="F24" s="13">
@@ -1411,11 +1416,11 @@
       </c>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,33)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,33)</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,33)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,33)</f>
         <v/>
       </c>
       <c r="F25" s="13">
@@ -1440,11 +1445,11 @@
       </c>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,34)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,34)</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,34)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,34)</f>
         <v/>
       </c>
       <c r="F26" s="13">
@@ -1485,11 +1490,11 @@
       </c>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,36)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,36)</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,36)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,36)</f>
         <v/>
       </c>
       <c r="F28" s="13">
@@ -1514,11 +1519,11 @@
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,37)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,37)</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,37)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,37)</f>
         <v/>
       </c>
       <c r="F29" s="13">
@@ -1543,11 +1548,11 @@
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$105,Begroting!$A$2:$A$105,38)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,38)</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$11,Risicos!$H$2:$H$11,38)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,38)</f>
         <v/>
       </c>
       <c r="F30" s="13">
@@ -1725,7 +1730,7 @@
         </is>
       </c>
       <c r="F44" s="21">
-        <f>Risicos!I13/F35</f>
+        <f>Risicos!I15/F35</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1839,7 +1844,7 @@
         </is>
       </c>
       <c r="F2" s="24" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G2" s="25" t="n">
         <v>4200</v>
@@ -1860,7 +1865,7 @@
       </c>
       <c r="K2" s="23" t="inlineStr">
         <is>
-          <t>Aantal nieuw vs. te verplaatsen uittellen op W-tekeningen; bestek zegt: uitgaan van grootste bouwgrootte</t>
+          <t>Telling L.0.01-A/B: 34 fancoils nodig (29 kamers + 3 keuken 0.24 + 1 keuken 0.64 + 1 personeelsruimte 0.73); D.0.01-A/B toont 29 bestaande → 5 nieuw. Bouwgrootte: grootste aanhouden (E&amp;W 7.4.2)</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1894,7 @@
         </is>
       </c>
       <c r="F3" s="24" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G3" s="25" t="n">
         <v>1400</v>
@@ -1910,7 +1915,7 @@
       </c>
       <c r="K3" s="23" t="inlineStr">
         <is>
-          <t>Aantal uittellen op tekening</t>
+          <t>29 bestaande fancoils volgens demontagetekeningen D.0.01-A (19) en D.0.01-B (10)</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1994,7 @@
         </is>
       </c>
       <c r="F5" s="24" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>190</v>
@@ -2135,7 +2140,7 @@
         </is>
       </c>
       <c r="F8" s="24" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>220</v>
@@ -2154,7 +2159,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr"/>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>34 fancoils + 6 kanaalverwarmers</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="n">
@@ -2217,12 +2226,12 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Douche-aansluiting warm/koud incl. afvoer (0.42, 0.70, 0.71)</t>
+          <t>Douche-aansluiting warm/koud incl. afvoer (0.37, 0.42, 0.70, 0.71)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1/6.2</t>
+          <t>E&amp;W 6.1/6.2 + T.0.01</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -2231,7 +2240,7 @@
         </is>
       </c>
       <c r="F10" s="24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10" s="25" t="n">
         <v>1500</v>
@@ -2252,7 +2261,7 @@
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>Aantal douches uittellen op T.0.01</t>
+          <t>T.0.01: 4 douches 0.42 + 4 douches 0.37 + 2 (0.70/0.71). 0.37 staat niet in de E&amp;W-tekst</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2290,7 @@
         </is>
       </c>
       <c r="F11" s="24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>1150</v>
@@ -2302,7 +2311,7 @@
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
-          <t>Voorgeschreven fabricaat</t>
+          <t>Voorgeschreven fabricaat; 10 douches volgens T.0.01</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2372,12 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>Wastafels ruimte 0.42 incl. toestel en aansluiting</t>
+          <t>Wastafels 0.37 en 0.42 incl. toestel en aansluiting</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1/6.3</t>
+          <t>E&amp;W 6.1/6.3 + T.0.01</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -2377,7 +2386,7 @@
         </is>
       </c>
       <c r="F13" s="24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G13" s="25" t="n">
         <v>950</v>
@@ -2398,7 +2407,7 @@
       </c>
       <c r="K13" s="23" t="inlineStr">
         <is>
-          <t>Aantal uittellen</t>
+          <t>T.0.01: 4 in 0.42 + 4 in 0.37</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2422,12 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>Aansluiten aanrechten 0.24, 0.64 en pantry 0.01 (warm/koud + afvoer; 0.24 via nieuw tracé naar vetafscheider)</t>
+          <t>Aansluiten tappunten aanrechten 0.24 (3), 0.64 (3) en pantry 0.01 (1) (warm/koud + afvoer; 0.24 via nieuw tracé naar vetafscheider)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1.1</t>
+          <t>E&amp;W 6.1.1 + T.0.01</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -2427,10 +2436,10 @@
         </is>
       </c>
       <c r="F14" s="24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="H14" s="26">
         <f>F14*G14</f>
@@ -2555,12 +2564,12 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>Uitbreiding VWA-stelsel (PVC / Dyka Sono in plafonds), brandmanchetten</t>
+          <t>Uitbreiding VWA-stelsel: ca. 40 m PVC in plafond parkeergarage (R.-1.01) + ca. 12 vloerdoorboringen, Dyka Sono in plafonds, brandmanchetten</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1.3</t>
+          <t>E&amp;W 6.1.3 + R.-1.01/R.0.01</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -2572,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>9500</v>
+        <v>16000</v>
       </c>
       <c r="H17" s="26">
         <f>F17*G17</f>
@@ -2588,7 +2597,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K17" s="23" t="inlineStr"/>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>R.-1.01: nieuwe leiding in kelder naar vetafscheider. Kernboringen door BG-vloer met vloerverwarming</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="n">
@@ -2707,7 +2720,7 @@
         </is>
       </c>
       <c r="F20" s="24" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G20" s="25" t="n">
         <v>1350</v>
@@ -2728,7 +2741,7 @@
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>Kanaallengtes uittrekken op L.0.01A/B</t>
+          <t>L.0.01-A/B: 29 kamers + keukens, personeelsruimte, gespreksruimten, badruimten</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2770,7 @@
         </is>
       </c>
       <c r="F21" s="24" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G21" s="25" t="n">
         <v>780</v>
@@ -2778,7 +2791,7 @@
       </c>
       <c r="K21" s="23" t="inlineStr">
         <is>
-          <t>Type onduidelijk: FDC25 (8.4.2) vs FDC M24S (9.4) – aantal uittellen</t>
+          <t>L.0.01 + E.001: 2 per kamer (toevoer + retour) = 58, plus ca. 6 in 60-min scheidingen. Type onduidelijk: FDC25 vs FDC M24S</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2820,7 @@
         </is>
       </c>
       <c r="F22" s="24" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="G22" s="25" t="n">
         <v>175</v>
@@ -2828,7 +2841,7 @@
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>Aantal uittellen</t>
+          <t>L.0.01: per kamer 6 roosters (CTV, CRVM, 2× RTB, 2× RRB) = 174 + ca. 56 in keukens/overige ruimten</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2983,7 @@
       </c>
       <c r="K25" s="23" t="inlineStr">
         <is>
-          <t>Offerte Techno Horeca is bijgevoegd – bedrag overnemen. Let op: BBN 3.7.2 noemt wasemschouw + wandkappen</t>
+          <t>Offerte Techno Horeca is bijgevoegd – bedrag overnemen. E.001 toont 7 AK-aansluitpunten, E&amp;W 8 kappen; BBN 3.7.2 noemt wasemschouw + wandkappen</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3058,7 @@
         </is>
       </c>
       <c r="F27" s="24" t="n">
-        <v>130</v>
+        <v>215</v>
       </c>
       <c r="G27" s="25" t="n">
         <v>210</v>
@@ -3066,7 +3079,7 @@
       </c>
       <c r="K27" s="23" t="inlineStr">
         <is>
-          <t>Aantal volgt uit lichtplan</t>
+          <t>E.001: A1 60x60 (92), E1/E2 downlights (36), F (8), W (9), H hanglamp (1 per kamer); typische kamers doorgerekend naar 29</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3099,7 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.10</t>
+          <t>E&amp;W 10.10 + E.001</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -3095,7 +3108,7 @@
         </is>
       </c>
       <c r="F28" s="24" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G28" s="25" t="n">
         <v>265</v>
@@ -3114,7 +3127,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr"/>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>E.001: 11 NV/NV1-punten getekend + pictogrammen; aantal volgt uit projectering NEN 1838</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="n">
@@ -3283,7 +3300,7 @@
         </is>
       </c>
       <c r="F32" s="24" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="G32" s="25" t="n">
         <v>135</v>
@@ -3304,7 +3321,7 @@
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>Incl. punten die niet op tekening staan (10.7)</t>
+          <t>E.001: KK per kamer + keukens (~32), 3O per kamer (29), Alg. (14), WM (4), DR (3), overig. Let op: punten die niet op tekening staan, horen er ook bij (10.7)</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3667,7 @@
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2</t>
+          <t>E&amp;W 11.2 + E.001</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
@@ -3659,7 +3676,7 @@
         </is>
       </c>
       <c r="F40" s="24" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="G40" s="25" t="n">
         <v>195</v>
@@ -3680,7 +3697,7 @@
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>Aantal volgt uit tekening</t>
+          <t>E.001: 8 D-punten (kantoor, gespreksruimten, beveiliging)</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3717,7 @@
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2</t>
+          <t>E&amp;W 11.2 + E.001</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
@@ -3709,7 +3726,7 @@
         </is>
       </c>
       <c r="F41" s="24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G41" s="25" t="n">
         <v>320</v>
@@ -3728,7 +3745,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K41" s="23" t="inlineStr"/>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>E.001: 12 Wi-Fi-punten</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n">
@@ -3888,7 +3909,7 @@
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.3</t>
+          <t>E&amp;W 12.2.3 + E.001</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
@@ -3897,7 +3918,7 @@
         </is>
       </c>
       <c r="F45" s="24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G45" s="25" t="n">
         <v>230</v>
@@ -3929,12 +3950,12 @@
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>Handbrandmelders (in deur brandslanghaspelkast) + slow-whoops klasse B</t>
+          <t>Handbrandmelders (4) + slow-whoops / sirenesokkels klasse B (ca. 35)</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.6/12.3</t>
+          <t>E&amp;W 12.2.6/12.3 + E.001</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
@@ -3943,10 +3964,10 @@
         </is>
       </c>
       <c r="F46" s="24" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="H46" s="26">
         <f>F46*G46</f>
@@ -3964,7 +3985,7 @@
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>Extra signaalgevers zijn niet verrekenbaar</t>
+          <t>E.001: HBM 4, SW/R-SW/MS-SW-combinaties ca. 35 na doorrekenen typische kamers. Extra signaalgevers niet verrekenbaar</t>
         </is>
       </c>
     </row>
@@ -4986,7 +5007,7 @@
       </c>
       <c r="D68" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1/3.3.3</t>
+          <t>BBN 3.3.1/3.3.3 + NvI vraag 6</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
@@ -5016,7 +5037,7 @@
       </c>
       <c r="K68" s="23" t="inlineStr">
         <is>
-          <t>Uitgangspunt: ca. 300 m1 × 3,3 m tot betondek – uitmeten op bijlage 1 en 4</t>
+          <t>Afgeleid uit stramien 7,2 m op L.0.01/E.001: ca. 300 m1 nieuwe wand (kamerscheidend + gangwanden) × 3,3 m. NvI vraag 6: alle kamerscheidende wanden volledig nieuw. Hoogte tot betondek nameten</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5052,12 @@
       </c>
       <c r="C69" s="23" t="inlineStr">
         <is>
-          <t>Toeslag verhoogde geluidsisolatie (47 dB noord, 59 dB kantoor/spreekruimten)</t>
+          <t>Toeslag verhoogde geluidsisolatie 47 dB kamers noord (0.49–0.56, 0.74–0.76)</t>
         </is>
       </c>
       <c r="D69" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.2/3.3.3</t>
+          <t>BBN 3.3.3</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
@@ -5045,10 +5066,10 @@
         </is>
       </c>
       <c r="F69" s="24" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="G69" s="25" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H69" s="26">
         <f>F69*G69</f>
@@ -5066,7 +5087,7 @@
       </c>
       <c r="K69" s="23" t="inlineStr">
         <is>
-          <t>59 dB is zwaar voor metal-stud: navragen</t>
+          <t>Ca. 48 m1 × 3,3 m</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5102,12 @@
       </c>
       <c r="C70" s="23" t="inlineStr">
         <is>
-          <t>Scanbehang + sauswerk wanden (beide zijden)</t>
+          <t>Toeslag 59 dB: dubbele metal-stud frame wand 155–170 mm (kantoor/gespreksruimten 0.04, 0.05, 0.62, 0.63)</t>
         </is>
       </c>
       <c r="D70" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1</t>
+          <t>BBN 3.3.2 / NvI vraag 5</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
@@ -5095,10 +5116,10 @@
         </is>
       </c>
       <c r="F70" s="24" t="n">
-        <v>2000</v>
+        <v>60</v>
       </c>
       <c r="G70" s="25" t="n">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="H70" s="26">
         <f>F70*G70</f>
@@ -5106,7 +5127,7 @@
       </c>
       <c r="I70" s="23" t="inlineStr">
         <is>
-          <t>OA schilder</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J70" s="23" t="inlineStr">
@@ -5114,7 +5135,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K70" s="23" t="inlineStr"/>
+      <c r="K70" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 5: alleen haalbaar met dubbele frames; DnT,A of Rw niet beantwoord. Ca. 18 m1 × 3,3 m</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="23" t="n">
@@ -5127,24 +5152,24 @@
       </c>
       <c r="C71" s="23" t="inlineStr">
         <is>
-          <t>Deurstel EI30 akoestisch, 40-44 mm, insteekslot, elektrische sluitplaat (voorbereid op Trigion), drangers</t>
+          <t>Scanbehang + sauswerk wanden (beide zijden)</t>
         </is>
       </c>
       <c r="D71" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.2</t>
+          <t>BBN 3.3.1</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F71" s="24" t="n">
-        <v>35</v>
+        <v>2000</v>
       </c>
       <c r="G71" s="25" t="n">
-        <v>2150</v>
+        <v>14</v>
       </c>
       <c r="H71" s="26">
         <f>F71*G71</f>
@@ -5152,19 +5177,15 @@
       </c>
       <c r="I71" s="23" t="inlineStr">
         <is>
-          <t>VDL / OA leverancier</t>
+          <t>OA schilder</t>
         </is>
       </c>
       <c r="J71" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
-        </is>
-      </c>
-      <c r="K71" s="23" t="inlineStr">
-        <is>
-          <t>Levertijd kritisch voor planning</t>
-        </is>
-      </c>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K71" s="23" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="23" t="n">
@@ -5177,12 +5198,12 @@
       </c>
       <c r="C72" s="23" t="inlineStr">
         <is>
-          <t>Overige binnendeurstellen (techniek, berging, gemeenschappelijk)</t>
+          <t>Deurstel EI30 akoestisch, 40-44 mm, insteekslot, elektrische sluitplaat (voorbereid op Trigion), vrijloopdranger</t>
         </is>
       </c>
       <c r="D72" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1</t>
+          <t>BBN 3.4.2 + E.001</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
@@ -5191,10 +5212,10 @@
         </is>
       </c>
       <c r="F72" s="24" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G72" s="25" t="n">
-        <v>1250</v>
+        <v>2150</v>
       </c>
       <c r="H72" s="26">
         <f>F72*G72</f>
@@ -5202,15 +5223,19 @@
       </c>
       <c r="I72" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>VDL / OA leverancier</t>
         </is>
       </c>
       <c r="J72" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K72" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K72" s="23" t="inlineStr">
+        <is>
+          <t>29 kamerdeuren + 6 overig. E.001 toont VLD per kamerdeur maar maar 2 ES + 3 kaartlezers: BBN (ES per deur) aangehouden als strengste eis. Levertijd kritisch</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="23" t="n">
@@ -5223,7 +5248,7 @@
       </c>
       <c r="C73" s="23" t="inlineStr">
         <is>
-          <t>Sluitplan / cilinders met moedersleutelsysteem</t>
+          <t>Overige binnendeurstellen (techniek, berging, gemeenschappelijk)</t>
         </is>
       </c>
       <c r="D73" s="23" t="inlineStr">
@@ -5237,10 +5262,10 @@
         </is>
       </c>
       <c r="F73" s="24" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G73" s="25" t="n">
-        <v>110</v>
+        <v>1250</v>
       </c>
       <c r="H73" s="26">
         <f>F73*G73</f>
@@ -5248,7 +5273,7 @@
       </c>
       <c r="I73" s="23" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J73" s="23" t="inlineStr">
@@ -5269,7 +5294,7 @@
       </c>
       <c r="C74" s="23" t="inlineStr">
         <is>
-          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
+          <t>Sluitplan / cilinders met moedersleutelsysteem</t>
         </is>
       </c>
       <c r="D74" s="23" t="inlineStr">
@@ -5283,10 +5308,10 @@
         </is>
       </c>
       <c r="F74" s="24" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G74" s="25" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="H74" s="26">
         <f>F74*G74</f>
@@ -5294,7 +5319,7 @@
       </c>
       <c r="I74" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J74" s="23" t="inlineStr">
@@ -5306,33 +5331,33 @@
     </row>
     <row r="75">
       <c r="A75" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>Vervangen plafondafwerking</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C75" s="23" t="inlineStr">
         <is>
-          <t>Verwijderen bestaand plafond incl. constructie</t>
+          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
         </is>
       </c>
       <c r="D75" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.5</t>
+          <t>BBN 3.4.1</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F75" s="24" t="n">
-        <v>1250</v>
+        <v>10</v>
       </c>
       <c r="G75" s="25" t="n">
-        <v>8</v>
+        <v>260</v>
       </c>
       <c r="H75" s="26">
         <f>F75*G75</f>
@@ -5340,7 +5365,7 @@
       </c>
       <c r="I75" s="23" t="inlineStr">
         <is>
-          <t>OA plafondmonteur</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J75" s="23" t="inlineStr">
@@ -5361,7 +5386,7 @@
       </c>
       <c r="C76" s="23" t="inlineStr">
         <is>
-          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
+          <t>Verwijderen bestaand plafond incl. constructie</t>
         </is>
       </c>
       <c r="D76" s="23" t="inlineStr">
@@ -5375,10 +5400,10 @@
         </is>
       </c>
       <c r="F76" s="24" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="G76" s="25" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H76" s="26">
         <f>F76*G76</f>
@@ -5398,33 +5423,33 @@
     </row>
     <row r="77">
       <c r="A77" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen zonwering</t>
+          <t>Vervangen plafondafwerking</t>
         </is>
       </c>
       <c r="C77" s="23" t="inlineStr">
         <is>
-          <t>Demonteren bestaande binnenzonwering</t>
+          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
         </is>
       </c>
       <c r="D77" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.1</t>
+          <t>BBN 3.5</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F77" s="24" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="G77" s="25" t="n">
-        <v>1500</v>
+        <v>42</v>
       </c>
       <c r="H77" s="26">
         <f>F77*G77</f>
@@ -5432,7 +5457,7 @@
       </c>
       <c r="I77" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA plafondmonteur</t>
         </is>
       </c>
       <c r="J77" s="23" t="inlineStr">
@@ -5440,11 +5465,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K77" s="23" t="inlineStr">
-        <is>
-          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
-        </is>
-      </c>
+      <c r="K77" s="23" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="23" t="n">
@@ -5457,7 +5478,7 @@
       </c>
       <c r="C78" s="23" t="inlineStr">
         <is>
-          <t>Verduisterende gordijnen incl. rails, gelijk aan verdiepingen</t>
+          <t>Demonteren bestaande binnenzonwering</t>
         </is>
       </c>
       <c r="D78" s="23" t="inlineStr">
@@ -5467,14 +5488,14 @@
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F78" s="24" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="G78" s="25" t="n">
-        <v>95</v>
+        <v>1500</v>
       </c>
       <c r="H78" s="26">
         <f>F78*G78</f>
@@ -5482,7 +5503,7 @@
       </c>
       <c r="I78" s="23" t="inlineStr">
         <is>
-          <t>OA stoffeerder</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J78" s="23" t="inlineStr">
@@ -5492,27 +5513,27 @@
       </c>
       <c r="K78" s="23" t="inlineStr">
         <is>
-          <t>Raamlengtes uitmeten</t>
+          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Aanpassen zonwering</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
+          <t>Verduisterende gordijnen incl. rails, gelijk aan verdiepingen</t>
         </is>
       </c>
       <c r="D79" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.7.1</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
@@ -5521,10 +5542,10 @@
         </is>
       </c>
       <c r="F79" s="24" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G79" s="25" t="n">
-        <v>780</v>
+        <v>95</v>
       </c>
       <c r="H79" s="26">
         <f>F79*G79</f>
@@ -5532,7 +5553,7 @@
       </c>
       <c r="I79" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>OA stoffeerder</t>
         </is>
       </c>
       <c r="J79" s="23" t="inlineStr">
@@ -5540,7 +5561,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K79" s="23" t="inlineStr"/>
+      <c r="K79" s="23" t="inlineStr">
+        <is>
+          <t>Raamlengtes uitmeten</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="23" t="n">
@@ -5553,7 +5578,7 @@
       </c>
       <c r="C80" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok eetruimte</t>
+          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
         </is>
       </c>
       <c r="D80" s="23" t="inlineStr">
@@ -5567,7 +5592,7 @@
         </is>
       </c>
       <c r="F80" s="24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G80" s="25" t="n">
         <v>780</v>
@@ -5599,7 +5624,7 @@
       </c>
       <c r="C81" s="23" t="inlineStr">
         <is>
-          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
+          <t>Keukenblok eetruimte</t>
         </is>
       </c>
       <c r="D81" s="23" t="inlineStr">
@@ -5609,14 +5634,14 @@
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F81" s="24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G81" s="25" t="n">
-        <v>950</v>
+        <v>780</v>
       </c>
       <c r="H81" s="26">
         <f>F81*G81</f>
@@ -5632,11 +5657,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K81" s="23" t="inlineStr">
-        <is>
-          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
-        </is>
-      </c>
+      <c r="K81" s="23" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="23" t="n">
@@ -5649,7 +5670,7 @@
       </c>
       <c r="C82" s="23" t="inlineStr">
         <is>
-          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
+          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
         </is>
       </c>
       <c r="D82" s="23" t="inlineStr">
@@ -5663,10 +5684,10 @@
         </is>
       </c>
       <c r="F82" s="24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G82" s="25" t="n">
-        <v>520</v>
+        <v>950</v>
       </c>
       <c r="H82" s="26">
         <f>F82*G82</f>
@@ -5682,7 +5703,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K82" s="23" t="inlineStr"/>
+      <c r="K82" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="23" t="n">
@@ -5695,12 +5720,12 @@
       </c>
       <c r="C83" s="23" t="inlineStr">
         <is>
-          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
         </is>
       </c>
       <c r="D83" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.3</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
@@ -5709,10 +5734,10 @@
         </is>
       </c>
       <c r="F83" s="24" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G83" s="25" t="n">
-        <v>1350</v>
+        <v>520</v>
       </c>
       <c r="H83" s="26">
         <f>F83*G83</f>
@@ -5728,41 +5753,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K83" s="23" t="inlineStr">
-        <is>
-          <t>Aantal volgens bijlage 1. LET OP: water/afvoer naar kamers staat NIET in E&amp;W</t>
-        </is>
-      </c>
+      <c r="K83" s="23" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B84" s="23" t="inlineStr">
+        <is>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+        </is>
+      </c>
+      <c r="C84" s="23" t="inlineStr">
+        <is>
+          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="inlineStr">
+        <is>
+          <t>BBN 3.7.3</t>
+        </is>
+      </c>
+      <c r="E84" s="23" t="inlineStr">
+        <is>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="B84" s="23" t="inlineStr">
-        <is>
-          <t>Realiseren douchevoorzieningen</t>
-        </is>
-      </c>
-      <c r="C84" s="23" t="inlineStr">
-        <is>
-          <t>Metal-stud douchewanden, watervaste beplating</t>
-        </is>
-      </c>
-      <c r="D84" s="23" t="inlineStr">
-        <is>
-          <t>BBN 3.3.4</t>
-        </is>
-      </c>
-      <c r="E84" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="F84" s="24" t="n">
-        <v>80</v>
-      </c>
       <c r="G84" s="25" t="n">
-        <v>125</v>
+        <v>1350</v>
       </c>
       <c r="H84" s="26">
         <f>F84*G84</f>
@@ -5770,7 +5791,7 @@
       </c>
       <c r="I84" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J84" s="23" t="inlineStr">
@@ -5778,7 +5799,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K84" s="23" t="inlineStr"/>
+      <c r="K84" s="23" t="inlineStr">
+        <is>
+          <t>29 kamers (kk op alle plattegronden). LET OP: T.0.01/R.0.01 tonen GEEN water/afvoer naar de kamers; BBN 3.7.3 vraagt wel RVS-spoelbak + kraan</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="23" t="n">
@@ -5791,7 +5816,7 @@
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>Wandtegelwerk douches incl. afdichtingssysteem</t>
+          <t>Metal-stud douchewanden, watervaste beplating</t>
         </is>
       </c>
       <c r="D85" s="23" t="inlineStr">
@@ -5805,10 +5830,10 @@
         </is>
       </c>
       <c r="F85" s="24" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="G85" s="25" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="H85" s="26">
         <f>F85*G85</f>
@@ -5816,7 +5841,7 @@
       </c>
       <c r="I85" s="23" t="inlineStr">
         <is>
-          <t>OA tegelzetter</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J85" s="23" t="inlineStr">
@@ -5837,12 +5862,12 @@
       </c>
       <c r="C86" s="23" t="inlineStr">
         <is>
-          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
+          <t>Wandtegelwerk douches incl. afdichtingssysteem</t>
         </is>
       </c>
       <c r="D86" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.3</t>
+          <t>BBN 3.3.4</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
@@ -5851,10 +5876,10 @@
         </is>
       </c>
       <c r="F86" s="24" t="n">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="G86" s="25" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="H86" s="26">
         <f>F86*G86</f>
@@ -5883,24 +5908,24 @@
       </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>Trespa douchedeuren incl. beslag en profielen</t>
+          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
         </is>
       </c>
       <c r="D87" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.3</t>
+          <t>BBN 3.2.3</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F87" s="24" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="G87" s="25" t="n">
-        <v>680</v>
+        <v>145</v>
       </c>
       <c r="H87" s="26">
         <f>F87*G87</f>
@@ -5908,7 +5933,7 @@
       </c>
       <c r="I87" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA tegelzetter</t>
         </is>
       </c>
       <c r="J87" s="23" t="inlineStr">
@@ -5920,33 +5945,33 @@
     </row>
     <row r="88">
       <c r="A88" s="23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B88" s="23" t="inlineStr">
         <is>
-          <t>Realiseren hekwerk terrein</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C88" s="23" t="inlineStr">
         <is>
-          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
+          <t>Trespa douchedeuren incl. beslag en profielen</t>
         </is>
       </c>
       <c r="D88" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.2</t>
+          <t>BBN 3.4.3</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F88" s="24" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G88" s="25" t="n">
-        <v>225</v>
+        <v>680</v>
       </c>
       <c r="H88" s="26">
         <f>F88*G88</f>
@@ -5954,7 +5979,7 @@
       </c>
       <c r="I88" s="23" t="inlineStr">
         <is>
-          <t>OA hekwerk</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J88" s="23" t="inlineStr">
@@ -5962,41 +5987,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K88" s="23" t="inlineStr">
-        <is>
-          <t>Lengte uitmeten</t>
-        </is>
-      </c>
+      <c r="K88" s="23" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B89" s="23" t="inlineStr">
         <is>
-          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
+          <t>Realiseren hekwerk terrein</t>
         </is>
       </c>
       <c r="C89" s="23" t="inlineStr">
         <is>
-          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
+          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
         </is>
       </c>
       <c r="D89" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.1</t>
+          <t>BBN 3.8.2</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F89" s="24" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G89" s="25" t="n">
-        <v>1500</v>
+        <v>225</v>
       </c>
       <c r="H89" s="26">
         <f>F89*G89</f>
@@ -6004,7 +6025,7 @@
       </c>
       <c r="I89" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA hekwerk</t>
         </is>
       </c>
       <c r="J89" s="23" t="inlineStr">
@@ -6012,7 +6033,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K89" s="23" t="inlineStr"/>
+      <c r="K89" s="23" t="inlineStr">
+        <is>
+          <t>Lengte uitmeten</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="23" t="n">
@@ -6025,7 +6050,7 @@
       </c>
       <c r="C90" s="23" t="inlineStr">
         <is>
-          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
+          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
         </is>
       </c>
       <c r="D90" s="23" t="inlineStr">
@@ -6035,14 +6060,14 @@
       </c>
       <c r="E90" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F90" s="24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G90" s="25" t="n">
-        <v>4300</v>
+        <v>1500</v>
       </c>
       <c r="H90" s="26">
         <f>F90*G90</f>
@@ -6062,33 +6087,33 @@
     </row>
     <row r="91">
       <c r="A91" s="23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B91" s="23" t="inlineStr">
         <is>
-          <t>Realiseren fietsenstalling</t>
+          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
         </is>
       </c>
       <c r="C91" s="23" t="inlineStr">
         <is>
-          <t>Beloopbare vloerroosters Dejo o.g. over ventilatiekuil, incl. onderconstructie, thermisch verzinkt, demontabel</t>
+          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
         </is>
       </c>
       <c r="D91" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.3</t>
+          <t>BBN 3.8.1</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F91" s="24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G91" s="25" t="n">
-        <v>460</v>
+        <v>4300</v>
       </c>
       <c r="H91" s="26">
         <f>F91*G91</f>
@@ -6096,7 +6121,7 @@
       </c>
       <c r="I91" s="23" t="inlineStr">
         <is>
-          <t>OA staalbouw</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J91" s="23" t="inlineStr">
@@ -6104,11 +6129,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K91" s="23" t="inlineStr">
-        <is>
-          <t>m² uitmeten; fietsenrekken niet genoemd</t>
-        </is>
-      </c>
+      <c r="K91" s="23" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="23" t="n">
@@ -6121,7 +6142,7 @@
       </c>
       <c r="C92" s="23" t="inlineStr">
         <is>
-          <t>Constructieve berekening roosters/oplegging</t>
+          <t>Beloopbare vloerroosters Dejo o.g. over ventilatiekuil, incl. onderconstructie, thermisch verzinkt, demontabel</t>
         </is>
       </c>
       <c r="D92" s="23" t="inlineStr">
@@ -6131,14 +6152,14 @@
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F92" s="24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G92" s="25" t="n">
-        <v>1500</v>
+        <v>460</v>
       </c>
       <c r="H92" s="26">
         <f>F92*G92</f>
@@ -6146,7 +6167,7 @@
       </c>
       <c r="I92" s="23" t="inlineStr">
         <is>
-          <t>Constructeur</t>
+          <t>OA staalbouw</t>
         </is>
       </c>
       <c r="J92" s="23" t="inlineStr">
@@ -6154,37 +6175,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K92" s="23" t="inlineStr"/>
+      <c r="K92" s="23" t="inlineStr">
+        <is>
+          <t>m² uitmeten; fietsenrekken niet genoemd</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" s="23" t="inlineStr">
         <is>
-          <t>Doorvoeringen inbranden voor de installaties</t>
+          <t>Realiseren fietsenstalling</t>
         </is>
       </c>
       <c r="C93" s="23" t="inlineStr">
         <is>
-          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
+          <t>Constructieve berekening roosters/oplegging</t>
         </is>
       </c>
       <c r="D93" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
+          <t>BBN 3.8.3</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F93" s="24" t="n">
-        <v>260</v>
+        <v>1</v>
       </c>
       <c r="G93" s="25" t="n">
-        <v>48</v>
+        <v>1500</v>
       </c>
       <c r="H93" s="26">
         <f>F93*G93</f>
@@ -6192,49 +6217,45 @@
       </c>
       <c r="I93" s="23" t="inlineStr">
         <is>
-          <t>VMT Brandpreventie</t>
+          <t>Constructeur</t>
         </is>
       </c>
       <c r="J93" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
-        </is>
-      </c>
-      <c r="K93" s="23" t="inlineStr">
-        <is>
-          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
-        </is>
-      </c>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K93" s="23" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B94" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
+          <t>Doorvoeringen inbranden voor de installaties</t>
         </is>
       </c>
       <c r="C94" s="23" t="inlineStr">
         <is>
-          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
+          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
         </is>
       </c>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.1</t>
+          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F94" s="24" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="G94" s="25" t="n">
-        <v>5000</v>
+        <v>48</v>
       </c>
       <c r="H94" s="26">
         <f>F94*G94</f>
@@ -6242,15 +6263,19 @@
       </c>
       <c r="I94" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>VMT Brandpreventie</t>
         </is>
       </c>
       <c r="J94" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K94" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K94" s="23" t="inlineStr">
+        <is>
+          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="23" t="n">
@@ -6263,12 +6288,12 @@
       </c>
       <c r="C95" s="23" t="inlineStr">
         <is>
-          <t>Opleveringsschoonmaak</t>
+          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
         </is>
       </c>
       <c r="D95" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.2</t>
+          <t>BBN 6.1</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
@@ -6280,7 +6305,7 @@
         <v>1</v>
       </c>
       <c r="G95" s="25" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="H95" s="26">
         <f>F95*G95</f>
@@ -6288,7 +6313,7 @@
       </c>
       <c r="I95" s="23" t="inlineStr">
         <is>
-          <t>OA schoonmaak</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J95" s="23" t="inlineStr">
@@ -6300,21 +6325,21 @@
     </row>
     <row r="96">
       <c r="A96" s="23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B96" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
         </is>
       </c>
       <c r="C96" s="23" t="inlineStr">
         <is>
-          <t>Bouwkundige engineering, detaillering, constructeur</t>
+          <t>Opleveringsschoonmaak</t>
         </is>
       </c>
       <c r="D96" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.1</t>
+          <t>BBN 6.2</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
@@ -6326,7 +6351,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="25" t="n">
-        <v>12000</v>
+        <v>3500</v>
       </c>
       <c r="H96" s="26">
         <f>F96*G96</f>
@@ -6334,7 +6359,7 @@
       </c>
       <c r="I96" s="23" t="inlineStr">
         <is>
-          <t>VDL / adviseur</t>
+          <t>OA schoonmaak</t>
         </is>
       </c>
       <c r="J96" s="23" t="inlineStr">
@@ -6355,12 +6380,12 @@
       </c>
       <c r="C97" s="23" t="inlineStr">
         <is>
-          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
+          <t>Bouwkundige engineering, detaillering, constructeur</t>
         </is>
       </c>
       <c r="D97" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.7/3.9</t>
+          <t>BBN 4.1</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -6372,7 +6397,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="25" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H97" s="26">
         <f>F97*G97</f>
@@ -6380,7 +6405,7 @@
       </c>
       <c r="I97" s="23" t="inlineStr">
         <is>
-          <t>OA installateurs</t>
+          <t>VDL / adviseur</t>
         </is>
       </c>
       <c r="J97" s="23" t="inlineStr">
@@ -6388,11 +6413,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K97" s="23" t="inlineStr">
-        <is>
-          <t>Reken op 5 weken review-cyclus met Winkelman</t>
-        </is>
-      </c>
+      <c r="K97" s="23" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="23" t="n">
@@ -6405,12 +6426,12 @@
       </c>
       <c r="C98" s="23" t="inlineStr">
         <is>
-          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
+          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
         </is>
       </c>
       <c r="D98" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9 / E&amp;W 3.3</t>
+          <t>E&amp;W 3.7/3.9</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
@@ -6422,7 +6443,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="25" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="H98" s="26">
         <f>F98*G98</f>
@@ -6430,7 +6451,7 @@
       </c>
       <c r="I98" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA installateurs</t>
         </is>
       </c>
       <c r="J98" s="23" t="inlineStr">
@@ -6438,25 +6459,29 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K98" s="23" t="inlineStr"/>
+      <c r="K98" s="23" t="inlineStr">
+        <is>
+          <t>Reken op 5 weken review-cyclus met Winkelman</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B99" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C99" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
+          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
         </is>
       </c>
       <c r="D99" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.6 / E&amp;W 3.9</t>
+          <t>BBN 3.9 / E&amp;W 3.3</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
@@ -6468,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="25" t="n">
-        <v>6500</v>
+        <v>16000</v>
       </c>
       <c r="H99" s="26">
         <f>F99*G99</f>
@@ -6476,7 +6501,7 @@
       </c>
       <c r="I99" s="23" t="inlineStr">
         <is>
-          <t>VDL + OA</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J99" s="23" t="inlineStr">
@@ -6488,33 +6513,33 @@
     </row>
     <row r="100">
       <c r="A100" s="23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B100" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Revisietekeningen</t>
         </is>
       </c>
       <c r="C100" s="23" t="inlineStr">
         <is>
-          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
+          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
         </is>
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9</t>
+          <t>BBN 4.6 / E&amp;W 3.9</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
         <is>
-          <t>week</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F100" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G100" s="25" t="n">
-        <v>2600</v>
+        <v>6500</v>
       </c>
       <c r="H100" s="26">
         <f>F100*G100</f>
@@ -6522,7 +6547,7 @@
       </c>
       <c r="I100" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>VDL + OA</t>
         </is>
       </c>
       <c r="J100" s="23" t="inlineStr">
@@ -6530,11 +6555,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K100" s="23" t="inlineStr">
-        <is>
-          <t>Doorlooptijd ca. 12 weken</t>
-        </is>
-      </c>
+      <c r="K100" s="23" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="23" t="n">
@@ -6547,24 +6568,24 @@
       </c>
       <c r="C101" s="23" t="inlineStr">
         <is>
-          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
+          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3</t>
+          <t>BBN 3.9</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>week</t>
         </is>
       </c>
       <c r="F101" s="24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G101" s="25" t="n">
-        <v>5500</v>
+        <v>2600</v>
       </c>
       <c r="H101" s="26">
         <f>F101*G101</f>
@@ -6580,7 +6601,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K101" s="23" t="inlineStr"/>
+      <c r="K101" s="23" t="inlineStr">
+        <is>
+          <t>Doorlooptijd ca. 12 weken</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="23" t="n">
@@ -6593,24 +6618,24 @@
       </c>
       <c r="C102" s="23" t="inlineStr">
         <is>
-          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
+          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
         </is>
       </c>
       <c r="D102" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3/6.2</t>
+          <t>BBN 4.3</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F102" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G102" s="25" t="n">
-        <v>475</v>
+        <v>5500</v>
       </c>
       <c r="H102" s="26">
         <f>F102*G102</f>
@@ -6618,7 +6643,7 @@
       </c>
       <c r="I102" s="23" t="inlineStr">
         <is>
-          <t>OA afval</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J102" s="23" t="inlineStr">
@@ -6639,24 +6664,24 @@
       </c>
       <c r="C103" s="23" t="inlineStr">
         <is>
-          <t>V&amp;G-plan uitvoeringsfase, werkplan, bouwplaatsinrichting, afzettingen</t>
+          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
         </is>
       </c>
       <c r="D103" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9/4.3/6.3</t>
+          <t>BBN 4.3/6.2</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F103" s="24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G103" s="25" t="n">
-        <v>3500</v>
+        <v>475</v>
       </c>
       <c r="H103" s="26">
         <f>F103*G103</f>
@@ -6664,7 +6689,7 @@
       </c>
       <c r="I103" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA afval</t>
         </is>
       </c>
       <c r="J103" s="23" t="inlineStr">
@@ -6685,12 +6710,12 @@
       </c>
       <c r="C104" s="23" t="inlineStr">
         <is>
-          <t>Klein materieel, steigers/rolsteigers, transport</t>
+          <t>V&amp;G-plan uitvoeringsfase, werkplan, bouwplaatsinrichting, afzettingen</t>
         </is>
       </c>
       <c r="D104" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.2</t>
+          <t>BBN 3.9/4.3/6.3</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -6702,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="25" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="H104" s="26">
         <f>F104*G104</f>
@@ -6731,12 +6756,12 @@
       </c>
       <c r="C105" s="23" t="inlineStr">
         <is>
-          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+          <t>Klein materieel, steigers/rolsteigers, transport</t>
         </is>
       </c>
       <c r="D105" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.2 / BBN 4.4</t>
+          <t>BBN 4.2</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
@@ -6748,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="G105" s="25" t="n">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="H105" s="26">
         <f>F105*G105</f>
@@ -6766,27 +6791,123 @@
       </c>
       <c r="K105" s="23" t="inlineStr"/>
     </row>
-    <row r="106"/>
+    <row r="106">
+      <c r="A106" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B106" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C106" s="23" t="inlineStr">
+        <is>
+          <t>Parkeerkosten (betaald parkeren, 2 voertuigen, ca. 60 werkdagen)</t>
+        </is>
+      </c>
+      <c r="D106" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 9</t>
+        </is>
+      </c>
+      <c r="E106" s="23" t="inlineStr">
+        <is>
+          <t>dag</t>
+        </is>
+      </c>
+      <c r="F106" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="G106" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="H106" s="26">
+        <f>F106*G106</f>
+        <v/>
+      </c>
+      <c r="I106" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J106" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K106" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 9: betaald parkeren; regeling niet beantwoord</t>
+        </is>
+      </c>
+    </row>
     <row r="107">
-      <c r="C107" s="16" t="inlineStr">
+      <c r="A107" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B107" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
+        <is>
+          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+        </is>
+      </c>
+      <c r="D107" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 3.2 / BBN 4.4</t>
+        </is>
+      </c>
+      <c r="E107" s="23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F107" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H107" s="26">
+        <f>F107*G107</f>
+        <v/>
+      </c>
+      <c r="I107" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J107" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K107" s="23" t="inlineStr"/>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="C109" s="16" t="inlineStr">
         <is>
           <t>Totaal directe kosten (excl. opslagen AK/W&amp;R/CAR en risico's)</t>
         </is>
       </c>
-      <c r="H107" s="28">
-        <f>SUM(H2:H105)</f>
+      <c r="H109" s="28">
+        <f>SUM(H2:H107)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K105"/>
-  <conditionalFormatting sqref="J2:J105">
+  <autoFilter ref="A1:K107"/>
+  <conditionalFormatting sqref="J2:J107">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J2="Richtprijs"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Richtprijs,Offerte aanvragen,Offerte ontvangen,Eigen norm,Stelpost (voorgeschreven)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6800,7 +6921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7159,19 +7280,19 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Versnelling om vóór eind 2026 op te leveren (overwerk, extra ploegen, kerstperiode)</t>
+          <t>Versnelling om vóór eind 2026 op te leveren: start ca. 9 nov volgens NvI vraag 8 (overwerk, extra ploegen, kerstperiode)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Offerteaanvraag / BBN 6.4</t>
+          <t>Offerteaanvraag / NvI vraag 8/15</t>
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="F9" s="26">
         <f>D9*E9</f>
@@ -7201,16 +7322,16 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Pantry's slaapkamers: water en afvoer staan niet in E&amp;W</t>
+          <t>Pantry's slaapkamers: water en afvoer staan niet in E&amp;W en niet op T.0.01/R.0.01</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.3 vs E&amp;W 6.1/6.2</t>
+          <t>BBN 3.7.3 vs E&amp;W 6.1/6.2 + T.0.01</t>
         </is>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="E10" s="30" t="n">
         <v>25000</v>
@@ -7233,7 +7354,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Groot verschil tussen documenten. Niet meegeprijsd: aanname vastleggen, bij voorkeur via de inkoper laten bevestigen.</t>
+          <t>Tekeningen bevestigen: alleen koelkast (kk) per kamer, geen tappunt. Niet meegeprijsd; uitgangspunt vastleggen.</t>
         </is>
       </c>
     </row>
@@ -7243,19 +7364,19 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+          <t>Kernboringen door BG-vloer boven parkeergarage: vloerverwarming en brandwerend dichten</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 4.2.2/7.1</t>
+          <t>R.-1.01 / E&amp;W 6.1.1</t>
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="F11" s="26">
         <f>D11*E11</f>
@@ -7263,11 +7384,11 @@
       </c>
       <c r="G11" s="31" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H11" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="26">
         <f>IF(G11="Ja",F11,0)</f>
@@ -7275,36 +7396,120 @@
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
+          <t>Ca. 12 doorboringen; garage is apart brandcompartiment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Tellingen uit PDF-tekeningen wijken af van de werkelijke aantallen</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Tekeningen E.001, L.0.01, T.0.01</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F12" s="26">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="I12" s="26">
+        <f>IF(G12="Ja",F12,0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>Tellingen zijn visueel/uit tekstlabels. Laat installateurs natellen op DWG (NvI vraag 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 4.2.2/7.1</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F13" s="26">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" s="26">
+        <f>IF(G13="Ja",F13,0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
           <t>Het bestek stelt dat de aannemer mag uitgaan van voldoende capaciteit, dus dit risico ligt bij de opdrachtgever.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Totaal meegeprijsde risico's</t>
         </is>
       </c>
-      <c r="I13" s="28">
-        <f>SUM(I2:I11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="32" t="inlineStr">
+      <c r="I15" s="28">
+        <f>SUM(I2:I13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>Totaal verwachte waarde alle risico's (ter info)</t>
         </is>
       </c>
-      <c r="I14" s="20">
-        <f>SUM(F2:F11)</f>
+      <c r="I16" s="20">
+        <f>SUM(F2:F13)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G2:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Ja,Nee"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7549,7 +7754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7648,15 +7853,1034 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
+          <t>HPL-douchecabines zoals op de verdiepingen i.p.v. metal-stud + tegelwerk (NvI vraag 14)</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>Sneller en goedkoper; privacy blijft gewaarborgd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Marmoleum naadloos doorzetten in woonkamers i.p.v. combinatie met tapijttegels (NvI vraag 11)</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>Minder overgangen, beter reinigbaar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>RVS-onderkasten en -werkblad in keuken 0.24 (64 personen) (NvI vraag 12)</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>Meerprijs, maar HPL is niet hittebestendig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
           <t>Planningsvoorstel: gefaseerde oplevering (eerst zuidvleugel, dan noord)</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>Geen kostenverschil, wel eerder bewoonbaar en minder planningsrisico.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Nota van Inlichtingen 21-09-2026 (TN-606498) – verwerking in het model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Let op: het document bevat alleen de vragen. De antwoorden zijn 'naar individuele vragen en antwoorden vertaald' en het componentenboek staat als bijlage op TenderNed. Download deze en controleer onderstaande aannames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Vraag (samengevat)</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>Antwoord in dit document</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>Verwerking in model</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Materiaalboek SPIE 2022 en sanitairboek ontbreken</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Componentenboek toegevoegd als bijlage (niet ontvangen)</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>Fabricaten conform E&amp;W aangehouden; controleren tegen componentenboek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>DWG-bestanden voor revisie?</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>Verwezen naar afzonderlijk antwoord</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>Revisiepost ongewijzigd. Met DWG kunnen aantallen exact worden geteld.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>Afprijzen van posten die van een voorstel afhangen (lichtplan, warmteverlies, fietsenstalling)</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Als vaste prijs op basis van het bestek; engineering in post E36.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Stoot- of inbraakwerendheidsklasse wanden?</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Geen extra klasse meegeprijsd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>59 dB: DnT,A of Rw? Vraagt dubbele frames 155–170 mm</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Dubbele frame wand meegeprijsd voor kantoor/gespreksruimten (60 m²).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Alle kamerscheidende wanden volledig nieuw, plafond eruit</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Zo meegeprijsd: 300 m1 nieuwe wand tot betondek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>Brandklasse gordijnen en tapijt?</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>Standaard brandklasse (Cfl-s1 / B1) in richtprijs; controleren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>Planning krap: gunning 12 okt, start 9 nov, V&amp;G 4 weken vooraf</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>Versnellingsrisico verhoogd naar 70% × € 15.000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>Betaald parkeren: regie, plek of kaart?</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>Parkeerkosten opgenomen in ABK (€ 1.800).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>Type systeemplafond of standaard 60x60 wit?</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Standaard 600x600 wit aangehouden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>Naadloos marmoleum i.p.v. tapijt/marmoleum per kamer?</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Basis volgens bestek; genoemd als optimalisatie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>RVS-kasten in keuken (64 personen) i.p.v. HPL?</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Basis HPL volgens bestek; RVS als optimalisatie met meerprijs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>Meubilair en inrichting door aannemer?</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>Niet meegeprijsd (niet in scope BBN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>HPL-douchecabines zoals boven i.p.v. metal-stud + tegels?</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>Basis volgens bestek; HPL-cabines als optimalisatie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>08:00–16:00 hard of afbouw een uur eerder/later?</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>Niet in dit document</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>Uitgegaan van 08:00–16:00 voor lawaaiig werk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>Opvallend: de NvI noemt Gemeente Wijdemeren als aanbestedende dienst en is gedateerd na de oorspronkelijke sluitingsdatum (18-09). Controleer de actuele sluitingsdatum op TenderNed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Tellingen uit de tekeningen (versie 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>Onderdeel</t>
+        </is>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
+        <is>
+          <t>Aantal</t>
+        </is>
+      </c>
+      <c r="C3" s="33" t="inlineStr">
+        <is>
+          <t>Tekening</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="inlineStr">
+        <is>
+          <t>Toelichting</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>Zekerheid</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>Bewonerskamers</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>L.0.01-A/B, E.001</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>17 in deel A (0.07–0.23), 12 in deel B (0.49–0.56, 0.50a, 0.74–0.76)</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>Fancoils benodigd</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>L.0.01-A/B</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>1 per kamer (29) + 3 keuken 0.24 + 1 keuken 0.64 + 1 personeelsruimte 0.73</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>Fancoils bestaand (demontage)</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>D.0.01-A/B</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>19 in deel A, 10 in deel B</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>Kanaalverwarmers/-koelers</t>
+        </is>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>E&amp;W 7.1, L.0.01</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>0.04, 0.05, 0.44, 0.45, 0.62, 0.63</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>Brandkleppen</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>ca. 64</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>L.0.01, E.001</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>2 per kamer + ca. 6 in 60-min scheidingen</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>Roosters</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>ca. 230</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>L.0.01-A/B</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>6 per kamer + keukens/overige ruimten</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>Douches</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>T.0.01</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>4 in 0.42, 4 in 0.37, 2 in 0.70/0.71</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>Wastafels</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>T.0.01</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>4 in 0.42, 4 in 0.37</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Tappunten aanrecht</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>T.0.01</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>3 in 0.24, 3 in 0.64, 1 pantry 0.01</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>Wasmachines / drogers</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>4 / 3</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>T.0.01, E.001</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>wm/wd in 0.57</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>Water naar kamers (pantry)</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>T.0.01, R.0.01</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Alleen koelkast (kk) per kamer</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>Nieuwe VWA kelder</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>ca. 40 m</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>R.-1.01</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Van keuken/badruimten naar vetafscheider</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>Armaturen</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>ca. 215</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>E.001</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>A1 92, E1 16, E2 20, F 8, W 9, H + typische kamers doorgerekend</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>Noodverlichting</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>ca. 25</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>E.001</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>11 NV/NV1-punten + pictogrammen</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>Wandcontactdozen</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>ca. 95</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>E.001</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>KK, 3O, Alg., WM, DR</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>Kooktoestel / afzuigkap-aansluitingen</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>7 / 7</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>E.001</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>KT en AK</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>Data / Wi-Fi</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>8 / 12</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>E.001</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>D en Wi-Fi-codes</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>BMI: handmelders / sirenes / automatische melders</t>
+        </is>
+      </c>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>4 / ca. 35 / ca. 24</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>E.001</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>HBM; SW-combinaties; R en R/SW</t>
+        </is>
+      </c>
+      <c r="E21" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>Kaartlezers / elektrische sluitplaten</t>
+        </is>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>3 / 2</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>E.001</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>Wijkt af van BBN 3.4.2 (ES per kamerdeur)</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>Nieuwe binnenwanden</t>
+        </is>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>ca. 300 m1</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>Afgeleid uit stramien 7,2 m</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="inlineStr">
+        <is>
+          <t>Kamers 3,6 m breed; bouwkundige tekeningen ontbreken</t>
+        </is>
+      </c>
+      <c r="E23" s="37" t="inlineStr">
+        <is>
+          <t>Laag</t>
         </is>
       </c>
     </row>

--- a/calculatie/Thebe22_calculatiemodel_VDL.xlsx
+++ b/calculatie/Thebe22_calculatiemodel_VDL.xlsx
@@ -14,10 +14,11 @@
     <sheet name="Eenheidsprijzen" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Optimalisaties" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="NvI" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tellingen" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Componentenboek" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tellingen" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -696,7 +697,7 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Versie 2 (25-09-2026): installatie-aantallen zijn geteld op de tekeningen E.001, L.0.01-A/B, D.0.01-A/B, T.0.01, T.0.02, R.0.01 en R.-1.01 (zie tabblad 'Tellingen'). De Nota van Inlichtingen van 21-09-2026 is verwerkt (zie tabblad 'NvI'). De bouwkundige tekeningen (BBN bijlage 1 t/m 4) ontbreken nog: wandlengtes en vloeroppervlakken zijn afgeleid uit het stramien van 7,2 m. Tel alles na op DWG.</t>
+          <t>Versie 3 (30-09-2026): antwoorden NvI en componentenboek verwerkt (tabbladen NvI en Componentenboek). Versie 2: installatie-aantallen zijn geteld op de tekeningen E.001, L.0.01-A/B, D.0.01-A/B, T.0.01, T.0.02, R.0.01 en R.-1.01 (zie tabblad 'Tellingen'). De Nota van Inlichtingen van 21-09-2026 is verwerkt (zie tabblad 'NvI'). De bouwkundige tekeningen (BBN bijlage 1 t/m 4) ontbreken nog: wandlengtes en vloeroppervlakken zijn afgeleid uit het stramien van 7,2 m. Tel alles na op DWG.</t>
         </is>
       </c>
     </row>
@@ -849,11 +850,11 @@
       </c>
       <c r="C5" s="11" t="n"/>
       <c r="D5" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,13)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,13)</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,13)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,13)</f>
         <v/>
       </c>
       <c r="F5" s="13">
@@ -878,11 +879,11 @@
       </c>
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,14)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,14)</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,14)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,14)</f>
         <v/>
       </c>
       <c r="F6" s="13">
@@ -907,11 +908,11 @@
       </c>
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,15)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,15)</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,15)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,15)</f>
         <v/>
       </c>
       <c r="F7" s="13">
@@ -936,11 +937,11 @@
       </c>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,16)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,16)</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,16)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,16)</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -965,11 +966,11 @@
       </c>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,17)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,17)</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,17)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,17)</f>
         <v/>
       </c>
       <c r="F9" s="13">
@@ -994,11 +995,11 @@
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,18)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,18)</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,18)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,18)</f>
         <v/>
       </c>
       <c r="F10" s="13">
@@ -1023,11 +1024,11 @@
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,19)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,19)</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,19)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,19)</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1052,11 +1053,11 @@
       </c>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,20)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,20)</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,20)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,20)</f>
         <v/>
       </c>
       <c r="F12" s="13">
@@ -1081,11 +1082,11 @@
       </c>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,21)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,21)</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,21)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,21)</f>
         <v/>
       </c>
       <c r="F13" s="13">
@@ -1126,11 +1127,11 @@
       </c>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,23)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,23)</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,23)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,23)</f>
         <v/>
       </c>
       <c r="F15" s="13">
@@ -1155,11 +1156,11 @@
       </c>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,24)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,24)</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,24)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,24)</f>
         <v/>
       </c>
       <c r="F16" s="13">
@@ -1184,11 +1185,11 @@
       </c>
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,25)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,25)</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,25)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,25)</f>
         <v/>
       </c>
       <c r="F17" s="13">
@@ -1213,11 +1214,11 @@
       </c>
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,26)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,26)</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,26)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,26)</f>
         <v/>
       </c>
       <c r="F18" s="13">
@@ -1242,11 +1243,11 @@
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,27)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,27)</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,27)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,27)</f>
         <v/>
       </c>
       <c r="F19" s="13">
@@ -1271,11 +1272,11 @@
       </c>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,28)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,28)</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,28)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,28)</f>
         <v/>
       </c>
       <c r="F20" s="13">
@@ -1300,11 +1301,11 @@
       </c>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,29)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,29)</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,29)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,29)</f>
         <v/>
       </c>
       <c r="F21" s="13">
@@ -1329,11 +1330,11 @@
       </c>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,30)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,30)</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,30)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,30)</f>
         <v/>
       </c>
       <c r="F22" s="13">
@@ -1358,11 +1359,11 @@
       </c>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,31)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,31)</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,31)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,31)</f>
         <v/>
       </c>
       <c r="F23" s="13">
@@ -1387,20 +1388,21 @@
       </c>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,32)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,32)</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,32)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,32)</f>
         <v/>
       </c>
       <c r="F24" s="13">
         <f>ROUND(D24+E24,0)</f>
         <v/>
       </c>
-      <c r="G24" s="10">
-        <f>IF(F24&lt;=0,"FOUT: nul-bedrag niet toegestaan","ok")</f>
-        <v/>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>€ 0 conform NvI vraag 3/29 (buiten beschouwing)</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1416,11 +1418,11 @@
       </c>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,33)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,33)</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,33)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,33)</f>
         <v/>
       </c>
       <c r="F25" s="13">
@@ -1445,11 +1447,11 @@
       </c>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,34)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,34)</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,34)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,34)</f>
         <v/>
       </c>
       <c r="F26" s="13">
@@ -1490,11 +1492,11 @@
       </c>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,36)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,36)</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,36)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,36)</f>
         <v/>
       </c>
       <c r="F28" s="13">
@@ -1519,11 +1521,11 @@
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,37)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,37)</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,37)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,37)</f>
         <v/>
       </c>
       <c r="F29" s="13">
@@ -1548,11 +1550,11 @@
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$107,Begroting!$A$2:$A$107,38)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,38)</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$13,Risicos!$H$2:$H$13,38)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,38)</f>
         <v/>
       </c>
       <c r="F30" s="13">
@@ -1730,7 +1732,7 @@
         </is>
       </c>
       <c r="F44" s="21">
-        <f>Risicos!I15/F35</f>
+        <f>Risicos!I16/F35</f>
         <v/>
       </c>
     </row>
@@ -1746,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1980,12 +1982,12 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Ruimtethermostaat CIAT 99DAsei incl. inbouw in brandwerende wand</t>
+          <t>Ruimtethermostaat CIAT incl. inbouw in brandwerende wand</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 9.2.3</t>
+          <t>E&amp;W 9.2.3 / Componentenboek nr. 24</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -2013,7 +2015,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr"/>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>Type-conflict: E&amp;W 99DAsei, componentenboek RTR-E 7203. Gelijk aan verdiepingen aanhouden</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n">
@@ -2226,12 +2232,12 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Douche-aansluiting warm/koud incl. afvoer (0.37, 0.42, 0.70, 0.71)</t>
+          <t>Douche-aansluiting warm/koud incl. afvoer en RVS-afvoerput Aquaberg 4815 (0.37, 0.42, 0.70, 0.71)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1/6.2 + T.0.01</t>
+          <t>E&amp;W 6.1/6.2 + T.0.01 + Componentenboek nr. 6</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -2243,7 +2249,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="25" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="H10" s="26">
         <f>F10*G10</f>
@@ -2276,12 +2282,12 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>Legionellapreventie De Melker M-Check per douche</t>
+          <t>De Melker M-Check douchepaneel MC.501229 (thermostaat, piëzo, tijdsbegrenzing, spoelfunctie) per douche</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.2.1/9.3</t>
+          <t>E&amp;W 6.2.1/9.3 + Componentenboek nr. 4</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -2293,7 +2299,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>1150</v>
+        <v>1450</v>
       </c>
       <c r="H11" s="26">
         <f>F11*G11</f>
@@ -2372,12 +2378,12 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>Wastafels 0.37 en 0.42 incl. toestel en aansluiting</t>
+          <t>Wastrog Intersan Sanilav 3.0 RVS 1200 mm incl. kranen en aansluiting (0.37 en 0.42)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1/6.3 + T.0.01</t>
+          <t>Componentenboek nr. 5 + T.0.01</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -2386,10 +2392,10 @@
         </is>
       </c>
       <c r="F13" s="24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>950</v>
+        <v>2100</v>
       </c>
       <c r="H13" s="26">
         <f>F13*G13</f>
@@ -2402,12 +2408,12 @@
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K13" s="23" t="inlineStr">
         <is>
-          <t>T.0.01: 4 in 0.42 + 4 in 0.37</t>
+          <t>T.0.01: 8 tappunten → 4 wastroggen van 2 tappunten (aanname); fabricaat volgens componentenboek</t>
         </is>
       </c>
     </row>
@@ -2422,24 +2428,24 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>Aansluiten tappunten aanrechten 0.24 (3), 0.64 (3) en pantry 0.01 (1) (warm/koud + afvoer; 0.24 via nieuw tracé naar vetafscheider)</t>
+          <t>MIVA-toiletruimte 0.72: wandcloset Geberit 300 comfort verlengd + Duofix + Linido steunen, MIVA-wastafel Geberit 300 comfort + Hansgrohe Care</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1.1 + T.0.01</t>
+          <t>Componentenboek nr. 9/11 + T.0.01 (WC-02/WT-02)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F14" s="24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>950</v>
+        <v>2900</v>
       </c>
       <c r="H14" s="26">
         <f>F14*G14</f>
@@ -2452,10 +2458,14 @@
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K14" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>WC-02/WT-02 op T.0.01; uitvoering volgens componentenboek</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="n">
@@ -2468,12 +2478,12 @@
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>Wasmachine-aansluitingen 0.57 incl. nieuwe afvoer (boren i.c.m. vloerverwarming)</t>
+          <t>Aansluiten tappunten aanrechten 0.24 (3), 0.64 (3) en pantry 0.01 (1) (warm/koud + afvoer; 0.24 via nieuw tracé naar vetafscheider)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1.1</t>
+          <t>E&amp;W 6.1.1 + T.0.01</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -2482,10 +2492,10 @@
         </is>
       </c>
       <c r="F15" s="24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="H15" s="26">
         <f>F15*G15</f>
@@ -2501,11 +2511,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K15" s="23" t="inlineStr">
-        <is>
-          <t>Aantal wasmachines uittellen</t>
-        </is>
-      </c>
+      <c r="K15" s="23" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="n">
@@ -2518,24 +2524,24 @@
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Closets 0.66/0.67 aansluiten, kinderclosets demonteren/afdoppen (0.66, 0.67, 0.70, 0.71)</t>
+          <t>Wasmachine-aansluitingen 0.57 incl. nieuwe afvoer (boren i.c.m. vloerverwarming)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 5.4/5.5</t>
+          <t>E&amp;W 6.1.1</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F16" s="24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>3200</v>
+        <v>1150</v>
       </c>
       <c r="H16" s="26">
         <f>F16*G16</f>
@@ -2551,7 +2557,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr"/>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>Aantal wasmachines uittellen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="23" t="n">
@@ -2564,12 +2574,12 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>Uitbreiding VWA-stelsel: ca. 40 m PVC in plafond parkeergarage (R.-1.01) + ca. 12 vloerdoorboringen, Dyka Sono in plafonds, brandmanchetten</t>
+          <t>2 standaard wandclosets 0.66/0.67 (vervangen kinderclosets, aansluitingen hergebruiken) + demonteren/afdoppen kinderclosets 0.70/0.71</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.1.3 + R.-1.01/R.0.01</t>
+          <t>E&amp;W 5.4/5.5 + NvI vraag 30</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -2581,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="H17" s="26">
         <f>F17*G17</f>
@@ -2599,7 +2609,7 @@
       </c>
       <c r="K17" s="23" t="inlineStr">
         <is>
-          <t>R.-1.01: nieuwe leiding in kelder naar vetafscheider. Kernboringen door BG-vloer met vloerverwarming</t>
+          <t>NvI vraag 30: het nieuwe sanitair betreft 2 standaard wandclosets</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2624,12 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Afpersen, spoelen, legionellabemonstering + vrijverklaring</t>
+          <t>Uitbreiding VWA-stelsel: ca. 40 m PVC in plafond parkeergarage (R.-1.01) + ca. 12 vloerdoorboringen, Dyka Sono in plafonds, brandmanchetten</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 6.2.5</t>
+          <t>E&amp;W 6.1.3 + R.-1.01/R.0.01</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -2631,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>1500</v>
+        <v>16000</v>
       </c>
       <c r="H18" s="26">
         <f>F18*G18</f>
@@ -2647,25 +2657,29 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr"/>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>R.-1.01: nieuwe leiding in kelder naar vetafscheider. Kernboringen door BG-vloer met vloerverwarming</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Luchtbehandelingskast / ventilatie-installatie, incl. kanaalwerk</t>
+          <t>Warmtapwaterinstallatie</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>Demontage kanalen, roosters en appendages BG conform demontagetekeningen, afplakken kanaalsysteem</t>
+          <t>Afpersen, spoelen, legionellabemonstering + vrijverklaring</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 5.8</t>
+          <t>E&amp;W 6.2.5</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -2677,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>6500</v>
+        <v>1500</v>
       </c>
       <c r="H19" s="26">
         <f>F19*G19</f>
@@ -2706,24 +2720,24 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>Nieuw kanalenstelsel verzinkt klasse C vanaf schachtuittrede, per ruimte (toevoer + retour/overstroom), incl. isolatie toevoer</t>
+          <t>Demontage kanalen, roosters en appendages BG conform demontagetekeningen, afplakken kanaalsysteem</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.1/8.4.5/8.7</t>
+          <t>E&amp;W 5.8</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>ruimte</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F20" s="24" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>1350</v>
+        <v>6500</v>
       </c>
       <c r="H20" s="26">
         <f>F20*G20</f>
@@ -2739,11 +2753,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr">
-        <is>
-          <t>L.0.01-A/B: 29 kamers + keukens, personeelsruimte, gespreksruimten, badruimten</t>
-        </is>
-      </c>
+      <c r="K20" s="23" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="23" t="n">
@@ -2756,24 +2766,24 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Brandklep Solid Air FDC motorbediend 24V veerteruggang (toevoer + retour per kamerwand)</t>
+          <t>Nieuw kanalenstelsel verzinkt klasse C vanaf schachtuittrede, per ruimte (toevoer + retour/overstroom), incl. isolatie toevoer</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.4.2/9.4</t>
+          <t>E&amp;W 8.1/8.4.5/8.7</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>ruimte</t>
         </is>
       </c>
       <c r="F21" s="24" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>780</v>
+        <v>1350</v>
       </c>
       <c r="H21" s="26">
         <f>F21*G21</f>
@@ -2786,12 +2796,12 @@
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
         <is>
-          <t>L.0.01 + E.001: 2 per kamer (toevoer + retour) = 58, plus ca. 6 in 60-min scheidingen. Type onduidelijk: FDC25 vs FDC M24S</t>
+          <t>L.0.01-A/B: 29 kamers + keukens, personeelsruimte, gespreksruimten, badruimten</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2816,12 @@
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>Roosters Solid Air (CTV/CRVM/RTB/RRB) incl. ≥1 m akoestische slang en instelklep</t>
+          <t>Brandklep Solid Air FDC motorbediend 24V veerteruggang (toevoer + retour per kamerwand)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.4.3</t>
+          <t>E&amp;W 8.4.2/9.4</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -2820,10 +2830,10 @@
         </is>
       </c>
       <c r="F22" s="24" t="n">
-        <v>230</v>
+        <v>64</v>
       </c>
       <c r="G22" s="25" t="n">
-        <v>175</v>
+        <v>780</v>
       </c>
       <c r="H22" s="26">
         <f>F22*G22</f>
@@ -2836,12 +2846,12 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>L.0.01: per kamer 6 roosters (CTV, CRVM, 2× RTB, 2× RRB) = 174 + ca. 56 in keukens/overige ruimten</t>
+          <t>L.0.01 + E.001: 2 per kamer = 58, plus ca. 6 in 60-min scheidingen. Componentenboek nr. 21: FDC25 24V DC (typeconflict E&amp;W opgelost)</t>
         </is>
       </c>
     </row>
@@ -2856,24 +2866,24 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>Plenumafzuiging gang + geluiddempende deurroosters (2 st)</t>
+          <t>Roosters Solid Air (CTV/CRVM/RTB/RRB) incl. ≥1 m akoestische slang en instelklep</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.4.1</t>
+          <t>E&amp;W 8.4.3</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F23" s="24" t="n">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>4500</v>
+        <v>175</v>
       </c>
       <c r="H23" s="26">
         <f>F23*G23</f>
@@ -2889,7 +2899,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K23" s="23" t="inlineStr"/>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>L.0.01: per kamer 6 roosters (CTV, CRVM, 2× RTB, 2× RRB) = 174 + ca. 56 in keukens/overige ruimten</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="n">
@@ -2902,12 +2916,12 @@
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Boxventilator wasruimte 0.57 met vochtregeling en tijdklok</t>
+          <t>Verlaagde plenumbox Solid Air model 450 per fancoil (toevoer + recirculatie)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.5</t>
+          <t>Componentenboek nr. 17</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -2916,10 +2930,10 @@
         </is>
       </c>
       <c r="F24" s="24" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="G24" s="25" t="n">
-        <v>2600</v>
+        <v>260</v>
       </c>
       <c r="H24" s="26">
         <f>F24*G24</f>
@@ -2935,7 +2949,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr"/>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Gelijk aan verdiepingen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="n">
@@ -2948,24 +2966,24 @@
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>Recirculatie-afzuigkap Quattro Correto CW4090 + plasmafilter (4 st keuken 0.24, 4 st keuken 0.64)</t>
+          <t>Plenumafzuiging gang + geluiddempende deurroosters (2 st)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.4.6/8.4.7</t>
+          <t>E&amp;W 8.4.1</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F25" s="24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G25" s="25" t="n">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="H25" s="26">
         <f>F25*G25</f>
@@ -2973,19 +2991,15 @@
       </c>
       <c r="I25" s="23" t="inlineStr">
         <is>
-          <t>Techno Horeca / OA</t>
+          <t>OA W-installateur</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="inlineStr">
-        <is>
-          <t>Offerte Techno Horeca is bijgevoegd – bedrag overnemen. E.001 toont 7 AK-aansluitpunten, E&amp;W 8 kappen; BBN 3.7.2 noemt wasemschouw + wandkappen</t>
-        </is>
-      </c>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="23" t="n">
@@ -2998,24 +3012,24 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>Luchtzijdig inregelen gehele BG + één gecombineerd meetrapport (Delta-P)</t>
+          <t>Boxventilator wasruimte 0.57 met vochtregeling en tijdklok</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.6</t>
+          <t>E&amp;W 8.5</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F26" s="24" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="25" t="n">
-        <v>5000</v>
+        <v>2600</v>
       </c>
       <c r="H26" s="26">
         <f>F26*G26</f>
@@ -3023,33 +3037,33 @@
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>Delta-P (voorgeschreven)</t>
+          <t>OA W-installateur</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>Verlichtingsinstallatie</t>
+          <t>Luchtbehandelingskast / ventilatie-installatie, incl. kanaalwerk</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Verlichtingsarmaturen LED (downlights, inleg 600x600, plafonnière + hanglamp kamers) incl. aansluiting</t>
+          <t>Recirculatie-afzuigkap Quattro Correto CW4090 + plasmafilter (4 st keuken 0.24, 4 st keuken 0.64)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.9</t>
+          <t>E&amp;W 8.4.6/8.4.7</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -3058,10 +3072,10 @@
         </is>
       </c>
       <c r="F27" s="24" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="G27" s="25" t="n">
-        <v>210</v>
+        <v>4600</v>
       </c>
       <c r="H27" s="26">
         <f>F27*G27</f>
@@ -3069,49 +3083,49 @@
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>Techno Horeca / OA</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
         <is>
-          <t>E.001: A1 60x60 (92), E1/E2 downlights (36), F (8), W (9), H hanglamp (1 per kamer); typische kamers doorgerekend naar 29</t>
+          <t>Offerte Techno Horeca is bijgevoegd – bedrag overnemen. E.001 toont 7 AK-aansluitpunten, E&amp;W 8 kappen; BBN 3.7.2 noemt wasemschouw + wandkappen</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>Verlichtingsinstallatie</t>
+          <t>Luchtbehandelingskast / ventilatie-installatie, incl. kanaalwerk</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>Noodverlichting en vluchtwegsignalering decentraal (autonoom)</t>
+          <t>Luchtzijdig inregelen gehele BG + één gecombineerd meetrapport (Delta-P)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.10 + E.001</t>
+          <t>E&amp;W 8.6</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F28" s="24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>265</v>
+        <v>5000</v>
       </c>
       <c r="H28" s="26">
         <f>F28*G28</f>
@@ -3119,19 +3133,15 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>Delta-P (voorgeschreven)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>E.001: 11 NV/NV1-punten getekend + pictogrammen; aantal volgt uit projectering NEN 1838</t>
-        </is>
-      </c>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="23" t="n">
@@ -3144,12 +3154,12 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>Aanwezigheidsdetectie / DALI-dimmers / nachtbedrijf gangen en sanitair</t>
+          <t>Verlichtingsarmaturen LED (downlights, inleg 600x600, plafonnière + hanglamp kamers) incl. aansluiting</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.11</t>
+          <t>E&amp;W 10.9</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
@@ -3158,10 +3168,10 @@
         </is>
       </c>
       <c r="F29" s="24" t="n">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="G29" s="25" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="H29" s="26">
         <f>F29*G29</f>
@@ -3177,25 +3187,29 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K29" s="23" t="inlineStr"/>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>E.001: A1 60x60 (92), E1/E2 downlights (36), F (8), W (9), H hanglamp (1 per kamer); typische kamers doorgerekend naar 29</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Centrale elektrotechnische voorzieningen</t>
+          <t>Verlichtingsinstallatie</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>Nieuwe verdeelinrichting keuken (LKK) incl. voedingskabel vanuit HSVI parkeergarage</t>
+          <t>Noodverlichting en vluchtwegsignalering decentraal (autonoom)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.6</t>
+          <t>E&amp;W 10.10 + E.001</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -3204,10 +3218,10 @@
         </is>
       </c>
       <c r="F30" s="24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G30" s="25" t="n">
-        <v>9500</v>
+        <v>265</v>
       </c>
       <c r="H30" s="26">
         <f>F30*G30</f>
@@ -3225,27 +3239,27 @@
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>Kabellengte parkeergarage → keuken bepalen</t>
+          <t>E.001: 11 NV/NV1-punten getekend + pictogrammen; aantal volgt uit projectering NEN 1838</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Centrale elektrotechnische voorzieningen</t>
+          <t>Verlichtingsinstallatie</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen LK0-1 en LK0-2 (groepen, 20% reserve) incl. overspanningsbeveiliging + signaleringslamp</t>
+          <t>Aanwezigheidsdetectie / DALI-dimmers / nachtbedrijf gangen en sanitair</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.6.1/10.8</t>
+          <t>E&amp;W 10.11</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -3254,10 +3268,10 @@
         </is>
       </c>
       <c r="F31" s="24" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>3800</v>
+        <v>160</v>
       </c>
       <c r="H31" s="26">
         <f>F31*G31</f>
@@ -3286,12 +3300,12 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>Wandcontactdozen / aansluitpunten incl. leidingwerk in buis</t>
+          <t>Nieuwe verdeelinrichting keuken (LKK) incl. voedingskabel vanuit HSVI parkeergarage</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.7</t>
+          <t>E&amp;W 10.6</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
@@ -3300,10 +3314,10 @@
         </is>
       </c>
       <c r="F32" s="24" t="n">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>135</v>
+        <v>9500</v>
       </c>
       <c r="H32" s="26">
         <f>F32*G32</f>
@@ -3321,7 +3335,7 @@
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>E.001: KK per kamer + keukens (~32), 3O per kamer (29), Alg. (14), WM (4), DR (3), overig. Let op: punten die niet op tekening staan, horen er ook bij (10.7)</t>
+          <t>Kabellengte parkeergarage → keuken bepalen</t>
         </is>
       </c>
     </row>
@@ -3336,12 +3350,12 @@
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>Krachtaansluitingen inductiekookplaten (6 st) en afzuigkappen</t>
+          <t>Aanpassen LK0-1 en LK0-2 (groepen, 20% reserve) incl. overspanningsbeveiliging + signaleringslamp</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.7.6</t>
+          <t>E&amp;W 10.6.1/10.8</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -3350,10 +3364,10 @@
         </is>
       </c>
       <c r="F33" s="24" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G33" s="25" t="n">
-        <v>420</v>
+        <v>3800</v>
       </c>
       <c r="H33" s="26">
         <f>F33*G33</f>
@@ -3382,12 +3396,12 @@
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>Voedingen ventilatorconvectoren, brandkleppen, M-Check, boxventilator</t>
+          <t>Wandcontactdozen / aansluitpunten incl. leidingwerk in buis</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 9.2.1/9.4.1</t>
+          <t>E&amp;W 10.7</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -3396,10 +3410,10 @@
         </is>
       </c>
       <c r="F34" s="24" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G34" s="25" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="H34" s="26">
         <f>F34*G34</f>
@@ -3415,7 +3429,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr"/>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>E.001: KK per kamer + keukens (~32), 3O per kamer (29), Alg. (14), WM (4), DR (3), overig. Let op: punten die niet op tekening staan, horen er ook bij (10.7)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="n">
@@ -3428,24 +3446,24 @@
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>Aarding en potentiaalvereffening (incl. natte ruimten)</t>
+          <t>Krachtaansluitingen inductiekookplaten (6 st) en afzuigkappen</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.4</t>
+          <t>E&amp;W 10.7.6</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F35" s="24" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G35" s="25" t="n">
-        <v>3200</v>
+        <v>420</v>
       </c>
       <c r="H35" s="26">
         <f>F35*G35</f>
@@ -3474,24 +3492,24 @@
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>Kabelgoten / kanalisatie + 35 m nieuw wandgootdeksel</t>
+          <t>Voedingen ventilatorconvectoren, brandkleppen, M-Check, boxventilator</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.5</t>
+          <t>E&amp;W 9.2.1/9.4.1</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F36" s="24" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G36" s="25" t="n">
-        <v>6200</v>
+        <v>175</v>
       </c>
       <c r="H36" s="26">
         <f>F36*G36</f>
@@ -3520,12 +3538,12 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>NEN 3140 / NEN 1010 metingen en rapportage</t>
+          <t>Aarding en potentiaalvereffening (incl. natte ruimten)</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.9.3</t>
+          <t>E&amp;W 10.4</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
@@ -3537,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="25" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="H37" s="26">
         <f>F37*G37</f>
@@ -3557,21 +3575,21 @@
     </row>
     <row r="38">
       <c r="A38" s="23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen regeltechniek</t>
+          <t>Centrale elektrotechnische voorzieningen</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Demonteren vervallen I/O-punten, GBS-datapunten en bekabeling, opschonen regelkasten (Priva ongewijzigd)</t>
+          <t>Kabelgoten / kanalisatie + 35 m nieuw wandgootdeksel</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 5.9</t>
+          <t>E&amp;W 10.5</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
@@ -3583,7 +3601,7 @@
         <v>1</v>
       </c>
       <c r="G38" s="25" t="n">
-        <v>3500</v>
+        <v>6200</v>
       </c>
       <c r="H38" s="26">
         <f>F38*G38</f>
@@ -3591,7 +3609,7 @@
       </c>
       <c r="I38" s="23" t="inlineStr">
         <is>
-          <t>OA W/regeltechniek</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
@@ -3599,29 +3617,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>Geen nul-prijs: deze post heeft wel inhoud</t>
-        </is>
-      </c>
+      <c r="K38" s="23" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen regeltechniek</t>
+          <t>Centrale elektrotechnische voorzieningen</t>
         </is>
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>Regeltechnische documentatie (processchema's, I/O-lijsten) + instructie ≥2 uur</t>
+          <t>NEN 3140 / NEN 1010 metingen en rapportage</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 9.5</t>
+          <t>E&amp;W 3.9.3</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
@@ -3633,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="25" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="H39" s="26">
         <f>F39*G39</f>
@@ -3641,7 +3655,7 @@
       </c>
       <c r="I39" s="23" t="inlineStr">
         <is>
-          <t>OA W/regeltechniek</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J39" s="23" t="inlineStr">
@@ -3653,33 +3667,33 @@
     </row>
     <row r="40">
       <c r="A40" s="23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Communicatievoorzieningen</t>
+          <t>Aanpassen regeltechniek</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>Data-aansluiting CAT6a LSZH incl. outlet en bekabeling</t>
+          <t>Demonteren vervallen I/O-punten, GBS-datapunten en bekabeling, opschonen regelkasten (Priva ongewijzigd)</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2 + E.001</t>
+          <t>E&amp;W 5.9</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F40" s="24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G40" s="25" t="n">
-        <v>195</v>
+        <v>3500</v>
       </c>
       <c r="H40" s="26">
         <f>F40*G40</f>
@@ -3687,7 +3701,7 @@
       </c>
       <c r="I40" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>OA W/regeltechniek</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -3697,39 +3711,39 @@
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>E.001: 8 D-punten (kantoor, gespreksruimten, beveiliging)</t>
+          <t>Geen nul-prijs: deze post heeft wel inhoud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Communicatievoorzieningen</t>
+          <t>Aanpassen regeltechniek</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>WLAN access point-aansluiting 2-voudig met PoE</t>
+          <t>Regeltechnische documentatie (processchema's, I/O-lijsten) + instructie ≥2 uur</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2 + E.001</t>
+          <t>E&amp;W 9.5</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F41" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G41" s="25" t="n">
-        <v>320</v>
+        <v>1800</v>
       </c>
       <c r="H41" s="26">
         <f>F41*G41</f>
@@ -3737,7 +3751,7 @@
       </c>
       <c r="I41" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>OA W/regeltechniek</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -3745,11 +3759,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>E.001: 12 Wi-Fi-punten</t>
-        </is>
-      </c>
+      <c r="K41" s="23" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n">
@@ -3762,24 +3772,24 @@
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Patchpanelen/rangeerpanelen in bestaand 19"-rack + aansluit- en patchsnoeren (75%)</t>
+          <t>Data-aansluiting CAT6a LSZH incl. outlet en bekabeling</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2.1</t>
+          <t>E&amp;W 11.2 + E.001</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F42" s="24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G42" s="25" t="n">
-        <v>2800</v>
+        <v>195</v>
       </c>
       <c r="H42" s="26">
         <f>F42*G42</f>
@@ -3795,7 +3805,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K42" s="23" t="inlineStr"/>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>E.001: 8 D-punten (kantoor, gespreksruimten, beveiliging)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="n">
@@ -3808,24 +3822,24 @@
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>Bekabeling camera's en toegangscontrole volgens opgave Trigion</t>
+          <t>WLAN access point-aansluiting 2-voudig met PoE</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2 / bijlage 13</t>
+          <t>E&amp;W 11.2 + E.001</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F43" s="24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G43" s="25" t="n">
-        <v>4500</v>
+        <v>320</v>
       </c>
       <c r="H43" s="26">
         <f>F43*G43</f>
@@ -3838,44 +3852,44 @@
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>Opgave Trigion (bijlage) uitrekenen</t>
+          <t>E.001: 12 Wi-Fi-punten</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Toegangscontrole en beveiliging</t>
+          <t>Communicatievoorzieningen</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>Rookmelders met NEN 2555-functionaliteit in bewonerskamers incl. sturingen</t>
+          <t>Patchpanelen/rangeerpanelen in bestaand 19"-rack + aansluit- en patchsnoeren (75%)</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.3</t>
+          <t>E&amp;W 11.2.1</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F44" s="24" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G44" s="25" t="n">
-        <v>290</v>
+        <v>2800</v>
       </c>
       <c r="H44" s="26">
         <f>F44*G44</f>
@@ -3883,45 +3897,45 @@
       </c>
       <c r="I44" s="23" t="inlineStr">
         <is>
-          <t>Erkend branddetectiebedrijf</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Toegangscontrole en beveiliging</t>
+          <t>Communicatievoorzieningen</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>Automatische melders verkeers-, gezamenlijke en risicoruimten</t>
+          <t>Bekabeling camera's en toegangscontrole volgens opgave Trigion</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.3 + E.001</t>
+          <t>E&amp;W 11.2 / bijlage 13</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F45" s="24" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G45" s="25" t="n">
-        <v>230</v>
+        <v>4500</v>
       </c>
       <c r="H45" s="26">
         <f>F45*G45</f>
@@ -3929,7 +3943,7 @@
       </c>
       <c r="I45" s="23" t="inlineStr">
         <is>
-          <t>Erkend branddetectiebedrijf</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J45" s="23" t="inlineStr">
@@ -3937,7 +3951,11 @@
           <t>Offerte aanvragen</t>
         </is>
       </c>
-      <c r="K45" s="23" t="inlineStr"/>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>Opgave Trigion (bijlage) uitrekenen</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="23" t="n">
@@ -3950,12 +3968,12 @@
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>Handbrandmelders (4) + slow-whoops / sirenesokkels klasse B (ca. 35)</t>
+          <t>Rookmelders met NEN 2555-functionaliteit in bewonerskamers incl. sturingen</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.6/12.3 + E.001</t>
+          <t>E&amp;W 12.2.3</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
@@ -3964,10 +3982,10 @@
         </is>
       </c>
       <c r="F46" s="24" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="H46" s="26">
         <f>F46*G46</f>
@@ -3983,11 +4001,7 @@
           <t>Offerte aanvragen</t>
         </is>
       </c>
-      <c r="K46" s="23" t="inlineStr">
-        <is>
-          <t>E.001: HBM 4, SW/R-SW/MS-SW-combinaties ca. 35 na doorrekenen typische kamers. Extra signaalgevers niet verrekenbaar</t>
-        </is>
-      </c>
+      <c r="K46" s="23" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="23" t="n">
@@ -4000,24 +4014,24 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Uitbreiding BMC/lus-capaciteit + aanpassen OAI-zonering</t>
+          <t>Automatische melders verkeers-, gezamenlijke en risicoruimten</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.3</t>
+          <t>E&amp;W 12.2.3 + E.001</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F47" s="24" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G47" s="25" t="n">
-        <v>4500</v>
+        <v>230</v>
       </c>
       <c r="H47" s="26">
         <f>F47*G47</f>
@@ -4033,11 +4047,7 @@
           <t>Offerte aanvragen</t>
         </is>
       </c>
-      <c r="K47" s="23" t="inlineStr">
-        <is>
-          <t>Capaciteit bestaande BMC onbekend – zie risico's</t>
-        </is>
-      </c>
+      <c r="K47" s="23" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
@@ -4050,24 +4060,24 @@
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>PvE/Nota van Aanvulling BMI/OAI + goedkeuring brandweer, projectering</t>
+          <t>Handbrandmelders (4) + slow-whoops / sirenesokkels klasse B (ca. 35)</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.1</t>
+          <t>E&amp;W 12.2.6/12.3 + E.001</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F48" s="24" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G48" s="25" t="n">
-        <v>3500</v>
+        <v>245</v>
       </c>
       <c r="H48" s="26">
         <f>F48*G48</f>
@@ -4083,7 +4093,11 @@
           <t>Offerte aanvragen</t>
         </is>
       </c>
-      <c r="K48" s="23" t="inlineStr"/>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>E.001: HBM 4, SW/R-SW/MS-SW-combinaties ca. 35 na doorrekenen typische kamers. Extra signaalgevers niet verrekenbaar</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="23" t="n">
@@ -4096,12 +4110,12 @@
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>Inbedrijfstelling, rapport van oplevering, inspectie erkende instelling, eerste certificaat</t>
+          <t>Uitbreiding BMC/lus-capaciteit + aanpassen OAI-zonering</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.1/12.2.2</t>
+          <t>E&amp;W 12.2.3</t>
         </is>
       </c>
       <c r="E49" s="23" t="inlineStr">
@@ -4113,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="25" t="n">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="H49" s="26">
         <f>F49*G49</f>
@@ -4129,7 +4143,11 @@
           <t>Offerte aanvragen</t>
         </is>
       </c>
-      <c r="K49" s="23" t="inlineStr"/>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>Capaciteit bestaande BMC onbekend – zie risico's</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="n">
@@ -4142,12 +4160,12 @@
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>GTV-voedingen en aansturing brandkleppen + deurvastzetters/vrijloopdrangers</t>
+          <t>PvE/Nota van Aanvulling BMI/OAI + goedkeuring brandweer, projectering</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.4</t>
+          <t>E&amp;W 12.2.1</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
@@ -4159,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="25" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="H50" s="26">
         <f>F50*G50</f>
@@ -4172,14 +4190,10 @@
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
-        <is>
-          <t>Demarcatie onduidelijk (8.4.2 'door derden' vs 12.2.4 'aannemer') – hier meegeprijsd</t>
-        </is>
-      </c>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="23" t="n">
@@ -4192,24 +4206,24 @@
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>Alarmsignalering mindervalidentoilet</t>
+          <t>Inbedrijfstelling, rapport van oplevering, inspectie erkende instelling, eerste certificaat</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.5</t>
+          <t>E&amp;W 12.2.1/12.2.2</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F51" s="24" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="25" t="n">
-        <v>850</v>
+        <v>4800</v>
       </c>
       <c r="H51" s="26">
         <f>F51*G51</f>
@@ -4217,12 +4231,12 @@
       </c>
       <c r="I51" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>Erkend branddetectiebedrijf</t>
         </is>
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr"/>
@@ -4238,12 +4252,12 @@
       </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
-          <t>Stelpost toegangscontrole tussendeur 'time-out' (Salto-tag)</t>
+          <t>GTV-voedingen en aansturing brandkleppen + deurvastzetters/vrijloopdrangers</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.4</t>
+          <t>E&amp;W 12.2.4</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
@@ -4254,8 +4268,8 @@
       <c r="F52" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="27" t="n">
-        <v>2000</v>
+      <c r="G52" s="25" t="n">
+        <v>4500</v>
       </c>
       <c r="H52" s="26">
         <f>F52*G52</f>
@@ -4263,49 +4277,49 @@
       </c>
       <c r="I52" s="23" t="inlineStr">
         <is>
-          <t>Stelpost</t>
+          <t>Erkend branddetectiebedrijf</t>
         </is>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>Stelpost (voorgeschreven)</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K52" s="23" t="inlineStr">
         <is>
-          <t>Voorgeschreven verrekenbare stelpost</t>
+          <t>Demarcatie onduidelijk (8.4.2 'door derden' vs 12.2.4 'aannemer') – hier meegeprijsd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (installaties)</t>
+          <t>Toegangscontrole en beveiliging</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>Stelpost tijdelijke voorzieningen t.b.v. bedrijfsvoering tijdens werkzaamheden</t>
+          <t>Alarmsignalering mindervalidentoilet</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 5.1</t>
+          <t>E&amp;W 12.5</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F53" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="27" t="n">
-        <v>10000</v>
+      <c r="G53" s="25" t="n">
+        <v>850</v>
       </c>
       <c r="H53" s="26">
         <f>F53*G53</f>
@@ -4313,37 +4327,33 @@
       </c>
       <c r="I53" s="23" t="inlineStr">
         <is>
-          <t>Stelpost</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J53" s="23" t="inlineStr">
         <is>
-          <t>Stelpost (voorgeschreven)</t>
-        </is>
-      </c>
-      <c r="K53" s="23" t="inlineStr">
-        <is>
-          <t>Voorgeschreven verrekenbare stelpost</t>
-        </is>
-      </c>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K53" s="23" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (installaties)</t>
+          <t>Toegangscontrole en beveiliging</t>
         </is>
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>Horizontaal/verticaal transport installatiedelen + hulpmiddelen</t>
+          <t>Stelpost toegangscontrole tussendeur 'time-out' (Salto-tag)</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.10</t>
+          <t>E&amp;W 12.4</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
@@ -4354,7 +4364,7 @@
       <c r="F54" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="25" t="n">
+      <c r="G54" s="27" t="n">
         <v>2000</v>
       </c>
       <c r="H54" s="26">
@@ -4363,33 +4373,37 @@
       </c>
       <c r="I54" s="23" t="inlineStr">
         <is>
-          <t>OA installateurs</t>
+          <t>Stelpost</t>
         </is>
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K54" s="23" t="inlineStr"/>
+          <t>Stelpost (voorgeschreven)</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr">
+        <is>
+          <t>Voorgeschreven verrekenbare stelpost</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
+          <t>Evt. andere bijkomende kosten (installaties)</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
-          <t>Opname kozijnen en ruiten, vaststellen scope</t>
+          <t>Stelpost tijdelijke voorzieningen t.b.v. bedrijfsvoering tijdens werkzaamheden</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.3</t>
+          <t>E&amp;W 5.1</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
@@ -4400,8 +4414,8 @@
       <c r="F55" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="25" t="n">
-        <v>750</v>
+      <c r="G55" s="27" t="n">
+        <v>10000</v>
       </c>
       <c r="H55" s="26">
         <f>F55*G55</f>
@@ -4409,45 +4423,49 @@
       </c>
       <c r="I55" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>Stelpost</t>
         </is>
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K55" s="23" t="inlineStr"/>
+          <t>Stelpost (voorgeschreven)</t>
+        </is>
+      </c>
+      <c r="K55" s="23" t="inlineStr">
+        <is>
+          <t>Voorgeschreven verrekenbare stelpost</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
+          <t>Evt. andere bijkomende kosten (installaties)</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>Vervangen beschadigde ruiten ZHR++/HR++ (U≤1,1), zo nodig gelaagd/gehard, incl. glaslatten</t>
+          <t>Horizontaal/verticaal transport installatiedelen + hulpmiddelen</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.3</t>
+          <t>E&amp;W 3.10</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F56" s="24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G56" s="25" t="n">
-        <v>275</v>
+        <v>2000</v>
       </c>
       <c r="H56" s="26">
         <f>F56*G56</f>
@@ -4455,7 +4473,7 @@
       </c>
       <c r="I56" s="23" t="inlineStr">
         <is>
-          <t>OA glaszetter</t>
+          <t>OA installateurs</t>
         </is>
       </c>
       <c r="J56" s="23" t="inlineStr">
@@ -4463,11 +4481,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K56" s="23" t="inlineStr">
-        <is>
-          <t>Hoeveelheid onbekend – schouw! Zie risico's</t>
-        </is>
-      </c>
+      <c r="K56" s="23" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="23" t="n">
@@ -4480,24 +4494,24 @@
       </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
-          <t>Privacyfolie ruiten sanitair blok (lichtdoorlatend, waterbestendig)</t>
+          <t>Opname kozijnen en ruiten, vaststellen scope</t>
         </is>
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.2</t>
+          <t>BBN 3.1.3</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F57" s="24" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G57" s="25" t="n">
-        <v>75</v>
+        <v>750</v>
       </c>
       <c r="H57" s="26">
         <f>F57*G57</f>
@@ -4505,7 +4519,7 @@
       </c>
       <c r="I57" s="23" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J57" s="23" t="inlineStr">
@@ -4526,24 +4540,24 @@
       </c>
       <c r="C58" s="23" t="inlineStr">
         <is>
-          <t>Doorgeefluik binnenzijde demonteren, sluiten, isoleren en afwerken</t>
+          <t>Vervangen beschadigde ruiten ZHR++/HR++ (U≤1,1), zo nodig gelaagd/gehard, incl. glaslatten</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.4</t>
+          <t>BBN 3.1.3</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F58" s="24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G58" s="25" t="n">
-        <v>1250</v>
+        <v>275</v>
       </c>
       <c r="H58" s="26">
         <f>F58*G58</f>
@@ -4551,7 +4565,7 @@
       </c>
       <c r="I58" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA glaszetter</t>
         </is>
       </c>
       <c r="J58" s="23" t="inlineStr">
@@ -4559,25 +4573,29 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K58" s="23" t="inlineStr"/>
+      <c r="K58" s="23" t="inlineStr">
+        <is>
+          <t>Hoeveelheid onbekend – schouw! Zie risico's</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>Vervangen vloerafwerking en plinten</t>
+          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>Verwijderen bestaande vloerafwerking incl. lijmresten en egalisatie (excl. terrazzo gangen en toilettegels)</t>
+          <t>Privacyfolie ruiten sanitair blok (lichtdoorlatend, waterbestendig)</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.1</t>
+          <t>BBN 3.1.2</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
@@ -4586,10 +4604,10 @@
         </is>
       </c>
       <c r="F59" s="24" t="n">
-        <v>1100</v>
+        <v>20</v>
       </c>
       <c r="G59" s="25" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="H59" s="26">
         <f>F59*G59</f>
@@ -4597,7 +4615,7 @@
       </c>
       <c r="I59" s="23" t="inlineStr">
         <is>
-          <t>OA vloerenlegger</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J59" s="23" t="inlineStr">
@@ -4605,41 +4623,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K59" s="23" t="inlineStr">
-        <is>
-          <t>m² uitmeten op bijlage 3</t>
-        </is>
-      </c>
+      <c r="K59" s="23" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>Vervangen vloerafwerking en plinten</t>
+          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
         </is>
       </c>
       <c r="C60" s="23" t="inlineStr">
         <is>
-          <t>Ondergrond herstellen en egaliseren</t>
+          <t>Doorgeefluik binnenzijde demonteren, sluiten, isoleren en afwerken</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.1</t>
+          <t>BBN 3.1.4</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F60" s="24" t="n">
-        <v>1100</v>
+        <v>1</v>
       </c>
       <c r="G60" s="25" t="n">
-        <v>15</v>
+        <v>1250</v>
       </c>
       <c r="H60" s="26">
         <f>F60*G60</f>
@@ -4647,7 +4661,7 @@
       </c>
       <c r="I60" s="23" t="inlineStr">
         <is>
-          <t>OA vloerenlegger</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J60" s="23" t="inlineStr">
@@ -4655,11 +4669,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K60" s="23" t="inlineStr">
-        <is>
-          <t>Volledig aangenomen</t>
-        </is>
-      </c>
+      <c r="K60" s="23" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="23" t="n">
@@ -4672,12 +4682,12 @@
       </c>
       <c r="C61" s="23" t="inlineStr">
         <is>
-          <t>Linoleum/marmoleum (kamers, gangen, keukenzones)</t>
+          <t>Verwijderen bestaande vloerafwerking incl. lijmresten en egalisatie (excl. terrazzo gangen en toilettegels)</t>
         </is>
       </c>
       <c r="D61" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.2/3.2.4</t>
+          <t>BBN 3.2.1</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
@@ -4686,10 +4696,10 @@
         </is>
       </c>
       <c r="F61" s="24" t="n">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="G61" s="25" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H61" s="26">
         <f>F61*G61</f>
@@ -4705,7 +4715,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K61" s="23" t="inlineStr"/>
+      <c r="K61" s="23" t="inlineStr">
+        <is>
+          <t>m² uitmeten op bijlage 3</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="23" t="n">
@@ -4718,12 +4732,12 @@
       </c>
       <c r="C62" s="23" t="inlineStr">
         <is>
-          <t>Tapijttegels zitgedeelten woonkamer</t>
+          <t>Ondergrond herstellen en egaliseren</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.4</t>
+          <t>BBN 3.2.1</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
@@ -4732,10 +4746,10 @@
         </is>
       </c>
       <c r="F62" s="24" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="G62" s="25" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H62" s="26">
         <f>F62*G62</f>
@@ -4753,7 +4767,7 @@
       </c>
       <c r="K62" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.2 spreekt zichzelf tegen (linoleum/tapijttegels)</t>
+          <t>Volledig aangenomen</t>
         </is>
       </c>
     </row>
@@ -4768,24 +4782,24 @@
       </c>
       <c r="C63" s="23" t="inlineStr">
         <is>
-          <t>Hardhouten plint 54x15 mm</t>
+          <t>Naadloze marmoleum-achtige afwerking in alle ruimten (kamers, gangen, woonkamers, keukens)</t>
         </is>
       </c>
       <c r="D63" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.2</t>
+          <t>BBN 3.2.2/3.2.4 + NvI vraag 11/17</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F63" s="24" t="n">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="G63" s="25" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H63" s="26">
         <f>F63*G63</f>
@@ -4793,7 +4807,7 @@
       </c>
       <c r="I63" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA vloerenlegger</t>
         </is>
       </c>
       <c r="J63" s="23" t="inlineStr">
@@ -4814,24 +4828,24 @@
       </c>
       <c r="C64" s="23" t="inlineStr">
         <is>
-          <t>Overgangsprofielen en dorpels (natte ruimten, buitendeuren)</t>
+          <t>Hardhouten plint 54x15 mm</t>
         </is>
       </c>
       <c r="D64" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.1</t>
+          <t>BBN 3.2.2</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F64" s="24" t="n">
-        <v>45</v>
+        <v>900</v>
       </c>
       <c r="G64" s="25" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="H64" s="26">
         <f>F64*G64</f>
@@ -4860,24 +4874,24 @@
       </c>
       <c r="C65" s="23" t="inlineStr">
         <is>
-          <t>Herstel en reinigen tegels toiletruimten</t>
+          <t>Overgangsprofielen en dorpels (natte ruimten, buitendeuren)</t>
         </is>
       </c>
       <c r="D65" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.3</t>
+          <t>BBN 3.2.1</t>
         </is>
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F65" s="24" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G65" s="25" t="n">
-        <v>1200</v>
+        <v>65</v>
       </c>
       <c r="H65" s="26">
         <f>F65*G65</f>
@@ -4897,21 +4911,21 @@
     </row>
     <row r="66">
       <c r="A66" s="23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B66" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
+          <t>Vervangen vloerafwerking en plinten</t>
         </is>
       </c>
       <c r="C66" s="23" t="inlineStr">
         <is>
-          <t>Slopen niet-dragende binnenwanden + herstel aansluitvlakken</t>
+          <t>Herstel en reinigen tegels toiletruimten</t>
         </is>
       </c>
       <c r="D66" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1</t>
+          <t>BBN 3.2.3</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
@@ -4923,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="25" t="n">
-        <v>8500</v>
+        <v>1200</v>
       </c>
       <c r="H66" s="26">
         <f>F66*G66</f>
@@ -4952,12 +4966,12 @@
       </c>
       <c r="C67" s="23" t="inlineStr">
         <is>
-          <t>Glaswanden zorgvuldig demonteren, labelen, beschermd opslaan voor hergebruik</t>
+          <t>Slopen niet-dragende binnenwanden + herstel aansluitvlakken</t>
         </is>
       </c>
       <c r="D67" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.2</t>
+          <t>BBN 3.3.1</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
@@ -4969,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="25" t="n">
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="H67" s="26">
         <f>F67*G67</f>
@@ -4985,11 +4999,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K67" s="23" t="inlineStr">
-        <is>
-          <t>Herplaatsing elders valt niet expliciet in scope – vragen</t>
-        </is>
-      </c>
+      <c r="K67" s="23" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="23" t="n">
@@ -5002,24 +5012,24 @@
       </c>
       <c r="C68" s="23" t="inlineStr">
         <is>
-          <t>Metal-stud wand EI30, dubbel beplaat, geïsoleerd, tot betondek, gelijmd op vloer (vloerverwarming)</t>
+          <t>Glaswanden zorgvuldig demonteren, labelen, beschermd opslaan in het gebouw voor hergebruik op locatie</t>
         </is>
       </c>
       <c r="D68" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1/3.3.3 + NvI vraag 6</t>
+          <t>BBN 3.3.2 + NvI vraag 21</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F68" s="24" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="G68" s="25" t="n">
-        <v>105</v>
+        <v>4500</v>
       </c>
       <c r="H68" s="26">
         <f>F68*G68</f>
@@ -5037,7 +5047,7 @@
       </c>
       <c r="K68" s="23" t="inlineStr">
         <is>
-          <t>Afgeleid uit stramien 7,2 m op L.0.01/E.001: ca. 300 m1 nieuwe wand (kamerscheidend + gangwanden) × 3,3 m. NvI vraag 6: alle kamerscheidende wanden volledig nieuw. Hoogte tot betondek nameten</t>
+          <t>NvI vraag 21: alleen glazen wanden; opslag in overleg, mogelijk in het gebouw</t>
         </is>
       </c>
     </row>
@@ -5052,24 +5062,24 @@
       </c>
       <c r="C69" s="23" t="inlineStr">
         <is>
-          <t>Toeslag verhoogde geluidsisolatie 47 dB kamers noord (0.49–0.56, 0.74–0.76)</t>
+          <t>Herstel aansluitingen vloer/wand/plafond na slopen binnenwanden (inschatting)</t>
         </is>
       </c>
       <c r="D69" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.3</t>
+          <t>NvI vraag 19</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F69" s="24" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="G69" s="25" t="n">
-        <v>32</v>
+        <v>3500</v>
       </c>
       <c r="H69" s="26">
         <f>F69*G69</f>
@@ -5087,7 +5097,7 @@
       </c>
       <c r="K69" s="23" t="inlineStr">
         <is>
-          <t>Ca. 48 m1 × 3,3 m</t>
+          <t>NvI vraag 19: inschatting door aannemer, meenemen in de posten</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5112,12 @@
       </c>
       <c r="C70" s="23" t="inlineStr">
         <is>
-          <t>Toeslag 59 dB: dubbele metal-stud frame wand 155–170 mm (kantoor/gespreksruimten 0.04, 0.05, 0.62, 0.63)</t>
+          <t>Metal-stud wand EI30, dubbel beplaat, geïsoleerd, tot betondek, gelijmd op vloer (vloerverwarming)</t>
         </is>
       </c>
       <c r="D70" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.2 / NvI vraag 5</t>
+          <t>BBN 3.3.1/3.3.3 + NvI vraag 6</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
@@ -5116,10 +5126,10 @@
         </is>
       </c>
       <c r="F70" s="24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="G70" s="25" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="H70" s="26">
         <f>F70*G70</f>
@@ -5137,7 +5147,7 @@
       </c>
       <c r="K70" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 5: alleen haalbaar met dubbele frames; DnT,A of Rw niet beantwoord. Ca. 18 m1 × 3,3 m</t>
+          <t>Afgeleid uit stramien 7,2 m op L.0.01/E.001: ca. 300 m1 nieuwe wand (kamerscheidend + gangwanden) × 3,3 m. NvI vraag 6: alle kamerscheidende wanden volledig nieuw. Hoogte tot betondek nameten</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5162,12 @@
       </c>
       <c r="C71" s="23" t="inlineStr">
         <is>
-          <t>Scanbehang + sauswerk wanden (beide zijden)</t>
+          <t>Toeslag verhoogde geluidsisolatie 47 dB kamers noord (0.49–0.56, 0.74–0.76)</t>
         </is>
       </c>
       <c r="D71" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1</t>
+          <t>BBN 3.3.3</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
@@ -5166,10 +5176,10 @@
         </is>
       </c>
       <c r="F71" s="24" t="n">
-        <v>2000</v>
+        <v>160</v>
       </c>
       <c r="G71" s="25" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H71" s="26">
         <f>F71*G71</f>
@@ -5177,7 +5187,7 @@
       </c>
       <c r="I71" s="23" t="inlineStr">
         <is>
-          <t>OA schilder</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J71" s="23" t="inlineStr">
@@ -5185,7 +5195,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K71" s="23" t="inlineStr"/>
+      <c r="K71" s="23" t="inlineStr">
+        <is>
+          <t>Ca. 48 m1 × 3,3 m</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="23" t="n">
@@ -5198,24 +5212,24 @@
       </c>
       <c r="C72" s="23" t="inlineStr">
         <is>
-          <t>Deurstel EI30 akoestisch, 40-44 mm, insteekslot, elektrische sluitplaat (voorbereid op Trigion), vrijloopdranger</t>
+          <t>Toeslag 59 dB: dubbele metal-stud frame wand 155–170 mm (kantoor/gespreksruimten 0.04, 0.05, 0.62, 0.63)</t>
         </is>
       </c>
       <c r="D72" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.2 + E.001</t>
+          <t>BBN 3.3.2 / NvI vraag 5</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F72" s="24" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="G72" s="25" t="n">
-        <v>2150</v>
+        <v>115</v>
       </c>
       <c r="H72" s="26">
         <f>F72*G72</f>
@@ -5223,17 +5237,17 @@
       </c>
       <c r="I72" s="23" t="inlineStr">
         <is>
-          <t>VDL / OA leverancier</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J72" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K72" s="23" t="inlineStr">
         <is>
-          <t>29 kamerdeuren + 6 overig. E.001 toont VLD per kamerdeur maar maar 2 ES + 3 kaartlezers: BBN (ES per deur) aangehouden als strengste eis. Levertijd kritisch</t>
+          <t>NvI vraag 5: alleen haalbaar met dubbele frames; DnT,A of Rw niet beantwoord. Ca. 18 m1 × 3,3 m</t>
         </is>
       </c>
     </row>
@@ -5248,24 +5262,24 @@
       </c>
       <c r="C73" s="23" t="inlineStr">
         <is>
-          <t>Overige binnendeurstellen (techniek, berging, gemeenschappelijk)</t>
+          <t>Scanbehang + sauswerk wanden (beide zijden)</t>
         </is>
       </c>
       <c r="D73" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1</t>
+          <t>BBN 3.3.1</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F73" s="24" t="n">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="G73" s="25" t="n">
-        <v>1250</v>
+        <v>14</v>
       </c>
       <c r="H73" s="26">
         <f>F73*G73</f>
@@ -5273,7 +5287,7 @@
       </c>
       <c r="I73" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA schilder</t>
         </is>
       </c>
       <c r="J73" s="23" t="inlineStr">
@@ -5294,12 +5308,12 @@
       </c>
       <c r="C74" s="23" t="inlineStr">
         <is>
-          <t>Sluitplan / cilinders met moedersleutelsysteem</t>
+          <t>Deurstel EI30 akoestisch, 40-44 mm, insteekslot, elektrische sluitplaat (voorbereid op Trigion), vrijloopdranger</t>
         </is>
       </c>
       <c r="D74" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1</t>
+          <t>BBN 3.4.2 + E.001</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
@@ -5308,10 +5322,10 @@
         </is>
       </c>
       <c r="F74" s="24" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G74" s="25" t="n">
-        <v>110</v>
+        <v>2150</v>
       </c>
       <c r="H74" s="26">
         <f>F74*G74</f>
@@ -5319,15 +5333,19 @@
       </c>
       <c r="I74" s="23" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>VDL / OA leverancier</t>
         </is>
       </c>
       <c r="J74" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K74" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K74" s="23" t="inlineStr">
+        <is>
+          <t>29 kamerdeuren + 6 overig. E.001 toont VLD per kamerdeur maar maar 2 ES + 3 kaartlezers: BBN (ES per deur) aangehouden als strengste eis. Levertijd kritisch</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="23" t="n">
@@ -5340,7 +5358,7 @@
       </c>
       <c r="C75" s="23" t="inlineStr">
         <is>
-          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
+          <t>Overige binnendeurstellen (techniek, berging, gemeenschappelijk)</t>
         </is>
       </c>
       <c r="D75" s="23" t="inlineStr">
@@ -5354,10 +5372,10 @@
         </is>
       </c>
       <c r="F75" s="24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G75" s="25" t="n">
-        <v>260</v>
+        <v>1250</v>
       </c>
       <c r="H75" s="26">
         <f>F75*G75</f>
@@ -5377,33 +5395,33 @@
     </row>
     <row r="76">
       <c r="A76" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B76" s="23" t="inlineStr">
         <is>
-          <t>Vervangen plafondafwerking</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C76" s="23" t="inlineStr">
         <is>
-          <t>Verwijderen bestaand plafond incl. constructie</t>
+          <t>Sluitplan / cilinders met moedersleutelsysteem, hang- en sluitwerk SKG2</t>
         </is>
       </c>
       <c r="D76" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.5</t>
+          <t>BBN 3.4.1 + NvI vraag 4</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F76" s="24" t="n">
-        <v>1250</v>
+        <v>45</v>
       </c>
       <c r="G76" s="25" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="H76" s="26">
         <f>F76*G76</f>
@@ -5411,7 +5429,7 @@
       </c>
       <c r="I76" s="23" t="inlineStr">
         <is>
-          <t>OA plafondmonteur</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J76" s="23" t="inlineStr">
@@ -5419,37 +5437,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K76" s="23" t="inlineStr"/>
+      <c r="K76" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 4: nieuw hang- en sluitwerk SKG2; wanden hotelstandaard, geen extra inbraakwerendheid</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>Vervangen plafondafwerking</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C77" s="23" t="inlineStr">
         <is>
-          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
+          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
         </is>
       </c>
       <c r="D77" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.5</t>
+          <t>BBN 3.4.1</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F77" s="24" t="n">
-        <v>1200</v>
+        <v>10</v>
       </c>
       <c r="G77" s="25" t="n">
-        <v>42</v>
+        <v>260</v>
       </c>
       <c r="H77" s="26">
         <f>F77*G77</f>
@@ -5457,7 +5479,7 @@
       </c>
       <c r="I77" s="23" t="inlineStr">
         <is>
-          <t>OA plafondmonteur</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J77" s="23" t="inlineStr">
@@ -5469,33 +5491,33 @@
     </row>
     <row r="78">
       <c r="A78" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B78" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen zonwering</t>
+          <t>Vervangen plafondafwerking</t>
         </is>
       </c>
       <c r="C78" s="23" t="inlineStr">
         <is>
-          <t>Demonteren bestaande binnenzonwering</t>
+          <t>Verwijderen bestaand plafond incl. constructie</t>
         </is>
       </c>
       <c r="D78" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.1</t>
+          <t>BBN 3.5</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F78" s="24" t="n">
-        <v>1</v>
+        <v>1250</v>
       </c>
       <c r="G78" s="25" t="n">
-        <v>1500</v>
+        <v>8</v>
       </c>
       <c r="H78" s="26">
         <f>F78*G78</f>
@@ -5503,7 +5525,7 @@
       </c>
       <c r="I78" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA plafondmonteur</t>
         </is>
       </c>
       <c r="J78" s="23" t="inlineStr">
@@ -5511,41 +5533,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K78" s="23" t="inlineStr">
-        <is>
-          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
-        </is>
-      </c>
+      <c r="K78" s="23" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen zonwering</t>
+          <t>Vervangen plafondafwerking</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
         <is>
-          <t>Verduisterende gordijnen incl. rails, gelijk aan verdiepingen</t>
+          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
         </is>
       </c>
       <c r="D79" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.1</t>
+          <t>BBN 3.5</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F79" s="24" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="G79" s="25" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="H79" s="26">
         <f>F79*G79</f>
@@ -5553,7 +5571,7 @@
       </c>
       <c r="I79" s="23" t="inlineStr">
         <is>
-          <t>OA stoffeerder</t>
+          <t>OA plafondmonteur</t>
         </is>
       </c>
       <c r="J79" s="23" t="inlineStr">
@@ -5561,41 +5579,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K79" s="23" t="inlineStr">
-        <is>
-          <t>Raamlengtes uitmeten</t>
-        </is>
-      </c>
+      <c r="K79" s="23" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B80" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Aanpassen zonwering</t>
         </is>
       </c>
       <c r="C80" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
+          <t>Demonteren bestaande binnenzonwering</t>
         </is>
       </c>
       <c r="D80" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.7.1</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F80" s="24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G80" s="25" t="n">
-        <v>780</v>
+        <v>1500</v>
       </c>
       <c r="H80" s="26">
         <f>F80*G80</f>
@@ -5603,7 +5617,7 @@
       </c>
       <c r="I80" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J80" s="23" t="inlineStr">
@@ -5611,25 +5625,29 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K80" s="23" t="inlineStr"/>
+      <c r="K80" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Aanpassen zonwering</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok eetruimte</t>
+          <t>Verduisterende gordijnen brandvertragend (hotelfunctie) incl. rails, gelijk aan verdiepingen</t>
         </is>
       </c>
       <c r="D81" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.7.1 + NvI vraag 7/26</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
@@ -5638,10 +5656,10 @@
         </is>
       </c>
       <c r="F81" s="24" t="n">
-        <v>7</v>
+        <v>150</v>
       </c>
       <c r="G81" s="25" t="n">
-        <v>780</v>
+        <v>110</v>
       </c>
       <c r="H81" s="26">
         <f>F81*G81</f>
@@ -5649,7 +5667,7 @@
       </c>
       <c r="I81" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>OA stoffeerder</t>
         </is>
       </c>
       <c r="J81" s="23" t="inlineStr">
@@ -5657,7 +5675,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K81" s="23" t="inlineStr"/>
+      <c r="K81" s="23" t="inlineStr">
+        <is>
+          <t>Raamlengtes uitmeten</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="23" t="n">
@@ -5670,7 +5692,7 @@
       </c>
       <c r="C82" s="23" t="inlineStr">
         <is>
-          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
+          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
         </is>
       </c>
       <c r="D82" s="23" t="inlineStr">
@@ -5680,14 +5702,14 @@
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F82" s="24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G82" s="25" t="n">
-        <v>950</v>
+        <v>780</v>
       </c>
       <c r="H82" s="26">
         <f>F82*G82</f>
@@ -5703,11 +5725,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K82" s="23" t="inlineStr">
-        <is>
-          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
-        </is>
-      </c>
+      <c r="K82" s="23" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="23" t="n">
@@ -5720,7 +5738,7 @@
       </c>
       <c r="C83" s="23" t="inlineStr">
         <is>
-          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
+          <t>Keukenblok eetruimte</t>
         </is>
       </c>
       <c r="D83" s="23" t="inlineStr">
@@ -5730,14 +5748,14 @@
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F83" s="24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G83" s="25" t="n">
-        <v>520</v>
+        <v>780</v>
       </c>
       <c r="H83" s="26">
         <f>F83*G83</f>
@@ -5766,12 +5784,12 @@
       </c>
       <c r="C84" s="23" t="inlineStr">
         <is>
-          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
         </is>
       </c>
       <c r="D84" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.3</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
@@ -5780,10 +5798,10 @@
         </is>
       </c>
       <c r="F84" s="24" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G84" s="25" t="n">
-        <v>1350</v>
+        <v>950</v>
       </c>
       <c r="H84" s="26">
         <f>F84*G84</f>
@@ -5801,39 +5819,39 @@
       </c>
       <c r="K84" s="23" t="inlineStr">
         <is>
-          <t>29 kamers (kk op alle plattegronden). LET OP: T.0.01/R.0.01 tonen GEEN water/afvoer naar de kamers; BBN 3.7.3 vraagt wel RVS-spoelbak + kraan</t>
+          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B85" s="23" t="inlineStr">
         <is>
-          <t>Realiseren douchevoorzieningen</t>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
         </is>
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>Metal-stud douchewanden, watervaste beplating</t>
+          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
         </is>
       </c>
       <c r="D85" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.4</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F85" s="24" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="G85" s="25" t="n">
-        <v>125</v>
+        <v>520</v>
       </c>
       <c r="H85" s="26">
         <f>F85*G85</f>
@@ -5841,7 +5859,7 @@
       </c>
       <c r="I85" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J85" s="23" t="inlineStr">
@@ -5853,33 +5871,33 @@
     </row>
     <row r="86">
       <c r="A86" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+        </is>
+      </c>
+      <c r="C86" s="23" t="inlineStr">
+        <is>
+          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>BBN 3.7.3</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="inlineStr">
+        <is>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="B86" s="23" t="inlineStr">
-        <is>
-          <t>Realiseren douchevoorzieningen</t>
-        </is>
-      </c>
-      <c r="C86" s="23" t="inlineStr">
-        <is>
-          <t>Wandtegelwerk douches incl. afdichtingssysteem</t>
-        </is>
-      </c>
-      <c r="D86" s="23" t="inlineStr">
-        <is>
-          <t>BBN 3.3.4</t>
-        </is>
-      </c>
-      <c r="E86" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="F86" s="24" t="n">
-        <v>160</v>
-      </c>
       <c r="G86" s="25" t="n">
-        <v>98</v>
+        <v>1350</v>
       </c>
       <c r="H86" s="26">
         <f>F86*G86</f>
@@ -5887,7 +5905,7 @@
       </c>
       <c r="I86" s="23" t="inlineStr">
         <is>
-          <t>OA tegelzetter</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J86" s="23" t="inlineStr">
@@ -5895,7 +5913,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K86" s="23" t="inlineStr"/>
+      <c r="K86" s="23" t="inlineStr">
+        <is>
+          <t>29 kamers (kk op alle plattegronden). LET OP: T.0.01/R.0.01 tonen GEEN water/afvoer naar de kamers; BBN 3.7.3 vraagt wel RVS-spoelbak + kraan</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="23" t="n">
@@ -5908,24 +5930,24 @@
       </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
+          <t>HPL-douchecabines incl. scheidingswanden, deuren en beslag (0.37 en 0.42)</t>
         </is>
       </c>
       <c r="D87" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.3</t>
+          <t>NvI vraag 14</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F87" s="24" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G87" s="25" t="n">
-        <v>145</v>
+        <v>1650</v>
       </c>
       <c r="H87" s="26">
         <f>F87*G87</f>
@@ -5933,15 +5955,19 @@
       </c>
       <c r="I87" s="23" t="inlineStr">
         <is>
-          <t>OA tegelzetter</t>
+          <t>OA leverancier cabines</t>
         </is>
       </c>
       <c r="J87" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K87" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K87" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 14: HPL-cabines en -wanden toegestaan, zoals op de verdiepingen</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="23" t="n">
@@ -5954,24 +5980,24 @@
       </c>
       <c r="C88" s="23" t="inlineStr">
         <is>
-          <t>Trespa douchedeuren incl. beslag en profielen</t>
+          <t>Wandtegelwerk wit geglazuurd op buitenwanden douche-/badruimten incl. afdichtingssysteem</t>
         </is>
       </c>
       <c r="D88" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.3</t>
+          <t>BBN 3.3.4 + NvI vraag 16</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F88" s="24" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="G88" s="25" t="n">
-        <v>680</v>
+        <v>92</v>
       </c>
       <c r="H88" s="26">
         <f>F88*G88</f>
@@ -5979,7 +6005,7 @@
       </c>
       <c r="I88" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA tegelzetter</t>
         </is>
       </c>
       <c r="J88" s="23" t="inlineStr">
@@ -5987,37 +6013,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K88" s="23" t="inlineStr"/>
+      <c r="K88" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 16: gebruikelijke kwaliteit, geglazuurd wit. Minder m² door HPL-cabines</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B89" s="23" t="inlineStr">
         <is>
-          <t>Realiseren hekwerk terrein</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C89" s="23" t="inlineStr">
         <is>
-          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
+          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
         </is>
       </c>
       <c r="D89" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.2</t>
+          <t>BBN 3.2.3</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F89" s="24" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G89" s="25" t="n">
-        <v>225</v>
+        <v>145</v>
       </c>
       <c r="H89" s="26">
         <f>F89*G89</f>
@@ -6025,7 +6055,7 @@
       </c>
       <c r="I89" s="23" t="inlineStr">
         <is>
-          <t>OA hekwerk</t>
+          <t>OA tegelzetter</t>
         </is>
       </c>
       <c r="J89" s="23" t="inlineStr">
@@ -6033,29 +6063,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K89" s="23" t="inlineStr">
-        <is>
-          <t>Lengte uitmeten</t>
-        </is>
-      </c>
+      <c r="K89" s="23" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B90" s="23" t="inlineStr">
         <is>
-          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C90" s="23" t="inlineStr">
         <is>
-          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
+          <t>Douchedeuren 0.70/0.71 (vochtbestendig, Trespa o.g.)</t>
         </is>
       </c>
       <c r="D90" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.1</t>
+          <t>BBN 3.4.3</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -6064,10 +6090,10 @@
         </is>
       </c>
       <c r="F90" s="24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="25" t="n">
-        <v>1500</v>
+        <v>680</v>
       </c>
       <c r="H90" s="26">
         <f>F90*G90</f>
@@ -6083,37 +6109,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K90" s="23" t="inlineStr"/>
+      <c r="K90" s="23" t="inlineStr">
+        <is>
+          <t>Deuren van de cabines in 0.37/0.42 zitten in de HPL-post</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B91" s="23" t="inlineStr">
         <is>
-          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
+          <t>Realiseren hekwerk terrein</t>
         </is>
       </c>
       <c r="C91" s="23" t="inlineStr">
         <is>
-          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
+          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
         </is>
       </c>
       <c r="D91" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.1</t>
+          <t>BBN 3.8.2</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F91" s="24" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G91" s="25" t="n">
-        <v>4300</v>
+        <v>225</v>
       </c>
       <c r="H91" s="26">
         <f>F91*G91</f>
@@ -6121,7 +6151,7 @@
       </c>
       <c r="I91" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA hekwerk</t>
         </is>
       </c>
       <c r="J91" s="23" t="inlineStr">
@@ -6129,37 +6159,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K91" s="23" t="inlineStr"/>
+      <c r="K91" s="23" t="inlineStr">
+        <is>
+          <t>Lengte uitmeten</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B92" s="23" t="inlineStr">
         <is>
-          <t>Realiseren fietsenstalling</t>
+          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
         </is>
       </c>
       <c r="C92" s="23" t="inlineStr">
         <is>
-          <t>Beloopbare vloerroosters Dejo o.g. over ventilatiekuil, incl. onderconstructie, thermisch verzinkt, demontabel</t>
+          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
         </is>
       </c>
       <c r="D92" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.3</t>
+          <t>BBN 3.8.1</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F92" s="24" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G92" s="25" t="n">
-        <v>460</v>
+        <v>1500</v>
       </c>
       <c r="H92" s="26">
         <f>F92*G92</f>
@@ -6167,7 +6201,7 @@
       </c>
       <c r="I92" s="23" t="inlineStr">
         <is>
-          <t>OA staalbouw</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J92" s="23" t="inlineStr">
@@ -6175,29 +6209,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K92" s="23" t="inlineStr">
-        <is>
-          <t>m² uitmeten; fietsenrekken niet genoemd</t>
-        </is>
-      </c>
+      <c r="K92" s="23" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B93" s="23" t="inlineStr">
         <is>
-          <t>Realiseren fietsenstalling</t>
+          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
         </is>
       </c>
       <c r="C93" s="23" t="inlineStr">
         <is>
-          <t>Constructieve berekening roosters/oplegging</t>
+          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
         </is>
       </c>
       <c r="D93" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.3</t>
+          <t>BBN 3.8.1</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
@@ -6209,7 +6239,7 @@
         <v>1</v>
       </c>
       <c r="G93" s="25" t="n">
-        <v>1500</v>
+        <v>4300</v>
       </c>
       <c r="H93" s="26">
         <f>F93*G93</f>
@@ -6217,7 +6247,7 @@
       </c>
       <c r="I93" s="23" t="inlineStr">
         <is>
-          <t>Constructeur</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J93" s="23" t="inlineStr">
@@ -6229,33 +6259,33 @@
     </row>
     <row r="94">
       <c r="A94" s="23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" s="23" t="inlineStr">
         <is>
-          <t>Doorvoeringen inbranden voor de installaties</t>
+          <t>Realiseren fietsenstalling</t>
         </is>
       </c>
       <c r="C94" s="23" t="inlineStr">
         <is>
-          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
+          <t>Fietsenstalling: buiten beschouwing volgens NvI vraag 3/29</t>
         </is>
       </c>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
+          <t>NvI vraag 3/29</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F94" s="24" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="G94" s="25" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H94" s="26">
         <f>F94*G94</f>
@@ -6263,49 +6293,49 @@
       </c>
       <c r="I94" s="23" t="inlineStr">
         <is>
-          <t>VMT Brandpreventie</t>
+          <t>n.v.t.</t>
         </is>
       </c>
       <c r="J94" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K94" s="23" t="inlineStr">
         <is>
-          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
+          <t>NvI: fietsenstalling wordt buiten beschouwing gelaten → € 0 in het formulier</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
+          <t>Doorvoeringen inbranden voor de installaties</t>
         </is>
       </c>
       <c r="C95" s="23" t="inlineStr">
         <is>
-          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
+          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
         </is>
       </c>
       <c r="D95" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.1</t>
+          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F95" s="24" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="G95" s="25" t="n">
-        <v>5000</v>
+        <v>48</v>
       </c>
       <c r="H95" s="26">
         <f>F95*G95</f>
@@ -6313,15 +6343,19 @@
       </c>
       <c r="I95" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>VMT Brandpreventie</t>
         </is>
       </c>
       <c r="J95" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K95" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K95" s="23" t="inlineStr">
+        <is>
+          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="23" t="n">
@@ -6334,12 +6368,12 @@
       </c>
       <c r="C96" s="23" t="inlineStr">
         <is>
-          <t>Opleveringsschoonmaak</t>
+          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
         </is>
       </c>
       <c r="D96" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.2</t>
+          <t>BBN 6.1</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
@@ -6351,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="25" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="H96" s="26">
         <f>F96*G96</f>
@@ -6359,7 +6393,7 @@
       </c>
       <c r="I96" s="23" t="inlineStr">
         <is>
-          <t>OA schoonmaak</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J96" s="23" t="inlineStr">
@@ -6371,21 +6405,21 @@
     </row>
     <row r="97">
       <c r="A97" s="23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B97" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
         </is>
       </c>
       <c r="C97" s="23" t="inlineStr">
         <is>
-          <t>Bouwkundige engineering, detaillering, constructeur</t>
+          <t>Opleveringsschoonmaak</t>
         </is>
       </c>
       <c r="D97" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.1</t>
+          <t>BBN 6.2</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -6397,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="25" t="n">
-        <v>12000</v>
+        <v>3500</v>
       </c>
       <c r="H97" s="26">
         <f>F97*G97</f>
@@ -6405,7 +6439,7 @@
       </c>
       <c r="I97" s="23" t="inlineStr">
         <is>
-          <t>VDL / adviseur</t>
+          <t>OA schoonmaak</t>
         </is>
       </c>
       <c r="J97" s="23" t="inlineStr">
@@ -6426,12 +6460,12 @@
       </c>
       <c r="C98" s="23" t="inlineStr">
         <is>
-          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
+          <t>Bouwkundige engineering, detaillering, constructeur</t>
         </is>
       </c>
       <c r="D98" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.7/3.9</t>
+          <t>BBN 4.1</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
@@ -6443,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="25" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H98" s="26">
         <f>F98*G98</f>
@@ -6451,7 +6485,7 @@
       </c>
       <c r="I98" s="23" t="inlineStr">
         <is>
-          <t>OA installateurs</t>
+          <t>VDL / adviseur</t>
         </is>
       </c>
       <c r="J98" s="23" t="inlineStr">
@@ -6459,11 +6493,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K98" s="23" t="inlineStr">
-        <is>
-          <t>Reken op 5 weken review-cyclus met Winkelman</t>
-        </is>
-      </c>
+      <c r="K98" s="23" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="23" t="n">
@@ -6476,12 +6506,12 @@
       </c>
       <c r="C99" s="23" t="inlineStr">
         <is>
-          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
+          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
         </is>
       </c>
       <c r="D99" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9 / E&amp;W 3.3</t>
+          <t>E&amp;W 3.7/3.9</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
@@ -6493,7 +6523,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="25" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="H99" s="26">
         <f>F99*G99</f>
@@ -6501,7 +6531,7 @@
       </c>
       <c r="I99" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA installateurs</t>
         </is>
       </c>
       <c r="J99" s="23" t="inlineStr">
@@ -6509,25 +6539,29 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K99" s="23" t="inlineStr"/>
+      <c r="K99" s="23" t="inlineStr">
+        <is>
+          <t>Reken op 5 weken review-cyclus met Winkelman</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B100" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C100" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
+          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
         </is>
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.6 / E&amp;W 3.9</t>
+          <t>BBN 3.9 / E&amp;W 3.3</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -6539,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="25" t="n">
-        <v>6500</v>
+        <v>16000</v>
       </c>
       <c r="H100" s="26">
         <f>F100*G100</f>
@@ -6547,7 +6581,7 @@
       </c>
       <c r="I100" s="23" t="inlineStr">
         <is>
-          <t>VDL + OA</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J100" s="23" t="inlineStr">
@@ -6559,33 +6593,33 @@
     </row>
     <row r="101">
       <c r="A101" s="23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B101" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Revisietekeningen</t>
         </is>
       </c>
       <c r="C101" s="23" t="inlineStr">
         <is>
-          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
+          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9</t>
+          <t>BBN 4.6 / E&amp;W 3.9</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>week</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F101" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G101" s="25" t="n">
-        <v>2600</v>
+        <v>6500</v>
       </c>
       <c r="H101" s="26">
         <f>F101*G101</f>
@@ -6593,7 +6627,7 @@
       </c>
       <c r="I101" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>VDL + OA</t>
         </is>
       </c>
       <c r="J101" s="23" t="inlineStr">
@@ -6601,11 +6635,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K101" s="23" t="inlineStr">
-        <is>
-          <t>Doorlooptijd ca. 12 weken</t>
-        </is>
-      </c>
+      <c r="K101" s="23" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="23" t="n">
@@ -6618,24 +6648,24 @@
       </c>
       <c r="C102" s="23" t="inlineStr">
         <is>
-          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
+          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
         </is>
       </c>
       <c r="D102" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3</t>
+          <t>BBN 3.9</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>week</t>
         </is>
       </c>
       <c r="F102" s="24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G102" s="25" t="n">
-        <v>5500</v>
+        <v>2600</v>
       </c>
       <c r="H102" s="26">
         <f>F102*G102</f>
@@ -6651,7 +6681,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K102" s="23" t="inlineStr"/>
+      <c r="K102" s="23" t="inlineStr">
+        <is>
+          <t>Start ca. 9 nov; NvI vraag 8: uitloop maximaal 6 weken toegestaan</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="23" t="n">
@@ -6664,24 +6698,24 @@
       </c>
       <c r="C103" s="23" t="inlineStr">
         <is>
-          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
+          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
         </is>
       </c>
       <c r="D103" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3/6.2</t>
+          <t>BBN 4.3</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F103" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G103" s="25" t="n">
-        <v>475</v>
+        <v>5500</v>
       </c>
       <c r="H103" s="26">
         <f>F103*G103</f>
@@ -6689,7 +6723,7 @@
       </c>
       <c r="I103" s="23" t="inlineStr">
         <is>
-          <t>OA afval</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J103" s="23" t="inlineStr">
@@ -6710,24 +6744,24 @@
       </c>
       <c r="C104" s="23" t="inlineStr">
         <is>
-          <t>V&amp;G-plan uitvoeringsfase, werkplan, bouwplaatsinrichting, afzettingen</t>
+          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
         </is>
       </c>
       <c r="D104" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9/4.3/6.3</t>
+          <t>BBN 4.3/6.2</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F104" s="24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G104" s="25" t="n">
-        <v>3500</v>
+        <v>475</v>
       </c>
       <c r="H104" s="26">
         <f>F104*G104</f>
@@ -6735,7 +6769,7 @@
       </c>
       <c r="I104" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA afval</t>
         </is>
       </c>
       <c r="J104" s="23" t="inlineStr">
@@ -6756,12 +6790,12 @@
       </c>
       <c r="C105" s="23" t="inlineStr">
         <is>
-          <t>Klein materieel, steigers/rolsteigers, transport</t>
+          <t>V&amp;G-plan uitvoeringsfase (concept 2 weken voor start), werkplan, bouwplaatsinrichting, afzettingen</t>
         </is>
       </c>
       <c r="D105" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.2</t>
+          <t>BBN 3.9/4.3/6.3 + NvI vraag 8</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
@@ -6773,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="G105" s="25" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="H105" s="26">
         <f>F105*G105</f>
@@ -6802,24 +6836,24 @@
       </c>
       <c r="C106" s="23" t="inlineStr">
         <is>
-          <t>Parkeerkosten (betaald parkeren, 2 voertuigen, ca. 60 werkdagen)</t>
+          <t>Klein materieel, steigers/rolsteigers, transport</t>
         </is>
       </c>
       <c r="D106" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 9</t>
+          <t>BBN 4.2</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
         <is>
-          <t>dag</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F106" s="24" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="G106" s="25" t="n">
-        <v>15</v>
+        <v>4500</v>
       </c>
       <c r="H106" s="26">
         <f>F106*G106</f>
@@ -6835,11 +6869,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K106" s="23" t="inlineStr">
-        <is>
-          <t>NvI vraag 9: betaald parkeren; regeling niet beantwoord</t>
-        </is>
-      </c>
+      <c r="K106" s="23" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="23" t="n">
@@ -6852,24 +6882,24 @@
       </c>
       <c r="C107" s="23" t="inlineStr">
         <is>
-          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+          <t>Parkeerkosten openbare weg (2 voertuigen × ca. 65 werkdagen)</t>
         </is>
       </c>
       <c r="D107" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.2 / BBN 4.4</t>
+          <t>NvI vraag 9</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>dag</t>
         </is>
       </c>
       <c r="F107" s="24" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="G107" s="25" t="n">
-        <v>3000</v>
+        <v>20</v>
       </c>
       <c r="H107" s="26">
         <f>F107*G107</f>
@@ -6885,29 +6915,79 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K107" s="23" t="inlineStr"/>
-    </row>
-    <row r="108"/>
-    <row r="109">
-      <c r="C109" s="16" t="inlineStr">
+      <c r="K107" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 9: geen plekken op terrein, openbare weg is betaald parkeren</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B108" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C108" s="23" t="inlineStr">
+        <is>
+          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+        </is>
+      </c>
+      <c r="D108" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 3.2 / BBN 4.4</t>
+        </is>
+      </c>
+      <c r="E108" s="23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F108" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H108" s="26">
+        <f>F108*G108</f>
+        <v/>
+      </c>
+      <c r="I108" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J108" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K108" s="23" t="inlineStr"/>
+    </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>Totaal directe kosten (excl. opslagen AK/W&amp;R/CAR en risico's)</t>
         </is>
       </c>
-      <c r="H109" s="28">
-        <f>SUM(H2:H107)</f>
+      <c r="H110" s="28">
+        <f>SUM(H2:H108)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K107"/>
-  <conditionalFormatting sqref="J2:J107">
+  <autoFilter ref="A1:K108"/>
+  <conditionalFormatting sqref="J2:J108">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J2="Richtprijs"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Richtprijs,Offerte aanvragen,Offerte ontvangen,Eigen norm,Stelpost (voorgeschreven)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6921,7 +7001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7242,16 +7322,16 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>Productiviteitsverlies in bewoond gebouw (lawaaiig werk alleen 08–16 uur)</t>
+          <t>Productiviteitsverlies in bewoond gebouw (08–16 uur; afbouw ±1 uur ruimer toegestaan)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.2</t>
+          <t>E&amp;W 3.2 + NvI vraag 15</t>
         </is>
       </c>
       <c r="D8" s="29" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>5000</v>
@@ -7280,19 +7360,19 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Versnelling om vóór eind 2026 op te leveren: start ca. 9 nov volgens NvI vraag 8 (overwerk, extra ploegen, kerstperiode)</t>
+          <t>Versnelling / uitloop: start ca. 9 nov, oplevering eind 2026 met max. 6 weken uitloop (NvI vraag 8/28)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Offerteaanvraag / NvI vraag 8/15</t>
+          <t>Offerteaanvraag + NvI vraag 8/28</t>
         </is>
       </c>
       <c r="D9" s="29" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="26">
         <f>D9*E9</f>
@@ -7322,19 +7402,19 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Pantry's slaapkamers: water en afvoer staan niet in E&amp;W en niet op T.0.01/R.0.01</t>
+          <t>Pantry's slaapkamers met water: close-in boiler, sifon en aansluitingen zoals op de verdiepingen (29 kamers)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.3 vs E&amp;W 6.1/6.2 + T.0.01</t>
+          <t>BBN 3.7.3 + Componentenboek nr. 1–3 vs E&amp;W 6.1/6.2 + T.0.01</t>
         </is>
       </c>
       <c r="D10" s="29" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>25000</v>
+        <v>45000</v>
       </c>
       <c r="F10" s="26">
         <f>D10*E10</f>
@@ -7354,7 +7434,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Tekeningen bevestigen: alleen koelkast (kk) per kamer, geen tappunt. Niet meegeprijsd; uitgangspunt vastleggen.</t>
+          <t>Componentenboek (verdiepingen 2022) heeft per kamer een Inventum Q10 close-in boiler + sifon; E&amp;W en T.0.01/R.0.01 tonen voor de BG geen water naar de kamers. Niet meegeprijsd.</t>
         </is>
       </c>
     </row>
@@ -7364,19 +7444,19 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Kernboringen door BG-vloer boven parkeergarage: vloerverwarming en brandwerend dichten</t>
+          <t>Constant-volumeregelaars Solid Air VCMHAR per kamer zoals op verdiepingen</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>R.-1.01 / E&amp;W 6.1.1</t>
+          <t>Componentenboek nr. 14 vs L.0.01</t>
         </is>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="F11" s="26">
         <f>D11*E11</f>
@@ -7384,11 +7464,11 @@
       </c>
       <c r="G11" s="31" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nee</t>
         </is>
       </c>
       <c r="H11" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="26">
         <f>IF(G11="Ja",F11,0)</f>
@@ -7396,7 +7476,7 @@
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>Ca. 12 doorboringen; garage is apart brandcompartiment.</t>
+          <t>Niet in E&amp;W/L.0.01 (handbediende inregelkleppen). Niet meegeprijsd.</t>
         </is>
       </c>
     </row>
@@ -7406,19 +7486,19 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Tellingen uit PDF-tekeningen wijken af van de werkelijke aantallen</t>
+          <t>Kernboringen door BG-vloer boven parkeergarage: vloerverwarming en brandwerend dichten</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>Tekeningen E.001, L.0.01, T.0.01</t>
+          <t>R.-1.01 / E&amp;W 6.1.1</t>
         </is>
       </c>
       <c r="D12" s="29" t="n">
         <v>0.3</v>
       </c>
       <c r="E12" s="30" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="F12" s="26">
         <f>D12*E12</f>
@@ -7430,7 +7510,7 @@
         </is>
       </c>
       <c r="H12" s="31" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I12" s="26">
         <f>IF(G12="Ja",F12,0)</f>
@@ -7438,7 +7518,7 @@
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>Tellingen zijn visueel/uit tekstlabels. Laat installateurs natellen op DWG (NvI vraag 2).</t>
+          <t>Ca. 12 doorboringen; garage is apart brandcompartiment.</t>
         </is>
       </c>
     </row>
@@ -7448,19 +7528,19 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+          <t>Tellingen uit PDF-tekeningen wijken af van de werkelijke aantallen</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 4.2.2/7.1</t>
+          <t>Tekeningen E.001, L.0.01, T.0.01</t>
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F13" s="26">
         <f>D13*E13</f>
@@ -7468,11 +7548,11 @@
       </c>
       <c r="G13" s="31" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H13" s="31" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I13" s="26">
         <f>IF(G13="Ja",F13,0)</f>
@@ -7480,36 +7560,78 @@
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
+          <t>Tellingen zijn visueel/uit tekstlabels. Laat installateurs natellen op DWG (NvI vraag 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 4.2.2/7.1</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F14" s="26">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="H14" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" s="26">
+        <f>IF(G14="Ja",F14,0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
           <t>Het bestek stelt dat de aannemer mag uitgaan van voldoende capaciteit, dus dit risico ligt bij de opdrachtgever.</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Totaal meegeprijsde risico's</t>
         </is>
       </c>
-      <c r="I15" s="28">
-        <f>SUM(I2:I13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="32" t="inlineStr">
+      <c r="I16" s="28">
+        <f>SUM(I2:I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Totaal verwachte waarde alle risico's (ter info)</t>
         </is>
       </c>
-      <c r="I16" s="20">
-        <f>SUM(F2:F13)</f>
+      <c r="I17" s="20">
+        <f>SUM(F2:F14)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G2:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Ja,Nee"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7754,7 +7876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7835,85 +7957,13 @@
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Bestaande plafondprofielen hergebruiken waar ze in goede staat zijn, alleen platen vervangen</t>
+          <t>Planningsvoorstel: gefaseerde oplevering (eerst zuidvleugel, dan noord)</t>
         </is>
       </c>
       <c r="C6" s="36" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="D6" s="35" t="inlineStr">
-        <is>
-          <t>BBN 3.5 gaat uit van volledige vervanging. Alleen in overleg en na opname.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>HPL-douchecabines zoals op de verdiepingen i.p.v. metal-stud + tegelwerk (NvI vraag 14)</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="n">
-        <v>-9000</v>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>Sneller en goedkoper; privacy blijft gewaarborgd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>Marmoleum naadloos doorzetten in woonkamers i.p.v. combinatie met tapijttegels (NvI vraag 11)</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>-1500</v>
-      </c>
-      <c r="D8" s="35" t="inlineStr">
-        <is>
-          <t>Minder overgangen, beter reinigbaar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>RVS-onderkasten en -werkblad in keuken 0.24 (64 personen) (NvI vraag 12)</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="35" t="inlineStr">
-        <is>
-          <t>Meerprijs, maar HPL is niet hittebestendig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="35" t="inlineStr">
-        <is>
-          <t>Planningsvoorstel: gefaseerde oplevering (eerst zuidvleugel, dan noord)</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>Geen kostenverschil, wel eerder bewoonbaar en minder planningsrisico.</t>
         </is>
@@ -7930,7 +7980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7942,14 +7992,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Nota van Inlichtingen 21-09-2026 (TN-606498) – verwerking in het model</t>
+          <t>Nota van Inlichtingen TN-606498 (21-09-2026) – antwoorden en verwerking in het model</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="35" t="inlineStr">
         <is>
-          <t>Let op: het document bevat alleen de vragen. De antwoorden zijn 'naar individuele vragen en antwoorden vertaald' en het componentenboek staat als bijlage op TenderNed. Download deze en controleer onderstaande aannames.</t>
+          <t>Bron: NvI met antwoorden (14 pagina's, vragen 3–17 en 19–30). Vraag 1 verwijst naar het componentenboek (zie tabblad Componentenboek). Vraag 2 (DWG) en vraag 18 staan niet in het ontvangen document.</t>
         </is>
       </c>
     </row>
@@ -7967,7 +8017,7 @@
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>Antwoord in dit document</t>
+          <t>Antwoord opdrachtgever</t>
         </is>
       </c>
       <c r="D4" s="33" t="inlineStr">
@@ -7982,17 +8032,17 @@
       </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
-          <t>Materiaalboek SPIE 2022 en sanitairboek ontbreken</t>
+          <t>Materiaalboek SPIE / sanitairboek ontbreekt</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>Componentenboek toegevoegd als bijlage (niet ontvangen)</t>
+          <t>Componentenboek toegevoegd</t>
         </is>
       </c>
       <c r="D5" s="37" t="inlineStr">
         <is>
-          <t>Fabricaten conform E&amp;W aangehouden; controleren tegen componentenboek.</t>
+          <t>Fabricaten verwerkt, zie tabblad Componentenboek.</t>
         </is>
       </c>
     </row>
@@ -8002,17 +8052,17 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>DWG-bestanden voor revisie?</t>
+          <t>DWG-bestanden?</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>Verwezen naar afzonderlijk antwoord</t>
+          <t>Niet in ontvangen document</t>
         </is>
       </c>
       <c r="D6" s="37" t="inlineStr">
         <is>
-          <t>Revisiepost ongewijzigd. Met DWG kunnen aantallen exact worden geteld.</t>
+          <t>Tellingen blijven uit PDF; risicopost € 10.000 gehandhaafd.</t>
         </is>
       </c>
     </row>
@@ -8022,17 +8072,17 @@
       </c>
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>Afprijzen van posten die van een voorstel afhangen (lichtplan, warmteverlies, fietsenstalling)</t>
+          <t>Afprijzen lichtplan, warmteverlies, fietsenstalling</t>
         </is>
       </c>
       <c r="C7" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Lichtplan en warmteverliesberekening horen bij de engineering. Fietsenstalling buiten beschouwing.</t>
         </is>
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>Als vaste prijs op basis van het bestek; engineering in post E36.</t>
+          <t>E32 = € 0; engineering in E36 ongewijzigd.</t>
         </is>
       </c>
     </row>
@@ -8042,17 +8092,17 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>Stoot- of inbraakwerendheidsklasse wanden?</t>
+          <t>Stoot-/inbraakwerendheid wanden</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Hotelstandaard; geen extra inbraakwerendheid wanden; nieuw hang- en sluitwerk SKG2.</t>
         </is>
       </c>
       <c r="D8" s="37" t="inlineStr">
         <is>
-          <t>Geen extra klasse meegeprijsd.</t>
+          <t>Sluitwerk verhoogd naar € 150/st (SKG2).</t>
         </is>
       </c>
     </row>
@@ -8062,17 +8112,17 @@
       </c>
       <c r="B9" s="37" t="inlineStr">
         <is>
-          <t>59 dB: DnT,A of Rw? Vraagt dubbele frames 155–170 mm</t>
+          <t>59 dB: DnT,A of Rw?</t>
         </is>
       </c>
       <c r="C9" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Alleen bij kantoor- en overlegplekken, zoals omschreven.</t>
         </is>
       </c>
       <c r="D9" s="37" t="inlineStr">
         <is>
-          <t>Dubbele frame wand meegeprijsd voor kantoor/gespreksruimten (60 m²).</t>
+          <t>Dubbele frame wand alleen 0.04/0.05/0.62/0.63 (60 m²) – ongewijzigd.</t>
         </is>
       </c>
     </row>
@@ -8082,17 +8132,17 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>Alle kamerscheidende wanden volledig nieuw, plafond eruit</t>
+          <t>Alle kamerscheidende wanden volledig nieuw?</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Ja, opdrachtgever is zich hiervan bewust.</t>
         </is>
       </c>
       <c r="D10" s="37" t="inlineStr">
         <is>
-          <t>Zo meegeprijsd: 300 m1 nieuwe wand tot betondek.</t>
+          <t>300 m1 nieuwe wand tot betondek – ongewijzigd.</t>
         </is>
       </c>
     </row>
@@ -8102,17 +8152,17 @@
       </c>
       <c r="B11" s="37" t="inlineStr">
         <is>
-          <t>Brandklasse gordijnen en tapijt?</t>
+          <t>Brandklasse gordijnen en tapijt</t>
         </is>
       </c>
       <c r="C11" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Wat gebruikelijk is voor hotelfunctie.</t>
         </is>
       </c>
       <c r="D11" s="37" t="inlineStr">
         <is>
-          <t>Standaard brandklasse (Cfl-s1 / B1) in richtprijs; controleren.</t>
+          <t>Gordijnen brandvertragend: € 110/m1.</t>
         </is>
       </c>
     </row>
@@ -8122,17 +8172,17 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>Planning krap: gunning 12 okt, start 9 nov, V&amp;G 4 weken vooraf</t>
+          <t>Planning krap, V&amp;G 4 weken vooraf</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>V&amp;G-plan 2 weken vooraf in concept. Uitloop maximaal 6 weken.</t>
         </is>
       </c>
       <c r="D12" s="37" t="inlineStr">
         <is>
-          <t>Versnellingsrisico verhoogd naar 70% × € 15.000.</t>
+          <t>Versnellingsrisico verlaagd (40% × € 10.000); uitvoerder 13 weken.</t>
         </is>
       </c>
     </row>
@@ -8142,17 +8192,17 @@
       </c>
       <c r="B13" s="37" t="inlineStr">
         <is>
-          <t>Betaald parkeren: regie, plek of kaart?</t>
+          <t>Parkeren</t>
         </is>
       </c>
       <c r="C13" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Geen plekken op terrein; openbare weg is betaald parkeren.</t>
         </is>
       </c>
       <c r="D13" s="37" t="inlineStr">
         <is>
-          <t>Parkeerkosten opgenomen in ABK (€ 1.800).</t>
+          <t>Parkeerkosten € 2.600 in ABK.</t>
         </is>
       </c>
     </row>
@@ -8162,17 +8212,17 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>Type systeemplafond of standaard 60x60 wit?</t>
+          <t>Type plafond</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>60x60 witte tegels.</t>
         </is>
       </c>
       <c r="D14" s="37" t="inlineStr">
         <is>
-          <t>Standaard 600x600 wit aangehouden.</t>
+          <t>Ongewijzigd.</t>
         </is>
       </c>
     </row>
@@ -8182,17 +8232,17 @@
       </c>
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>Naadloos marmoleum i.p.v. tapijt/marmoleum per kamer?</t>
+          <t>Tapijt + marmoleum combineren?</t>
         </is>
       </c>
       <c r="C15" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Al het tapijt eruit; alle ruimten naadloze marmoleum-achtige afwerking.</t>
         </is>
       </c>
       <c r="D15" s="37" t="inlineStr">
         <is>
-          <t>Basis volgens bestek; genoemd als optimalisatie.</t>
+          <t>Tapijttegels vervallen; marmoleum 1.050 m².</t>
         </is>
       </c>
     </row>
@@ -8202,17 +8252,17 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>RVS-kasten in keuken (64 personen) i.p.v. HPL?</t>
+          <t>RVS-keukenkasten i.p.v. HPL?</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Uitgaan van de vraagspecificatie (HPL).</t>
         </is>
       </c>
       <c r="D16" s="37" t="inlineStr">
         <is>
-          <t>Basis HPL volgens bestek; RVS als optimalisatie met meerprijs.</t>
+          <t>Ongewijzigd; optimalisatie vervallen.</t>
         </is>
       </c>
     </row>
@@ -8222,17 +8272,17 @@
       </c>
       <c r="B17" s="37" t="inlineStr">
         <is>
-          <t>Meubilair en inrichting door aannemer?</t>
+          <t>Meubilair en inrichting?</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Nee.</t>
         </is>
       </c>
       <c r="D17" s="37" t="inlineStr">
         <is>
-          <t>Niet meegeprijsd (niet in scope BBN).</t>
+          <t>Niet meegeprijsd.</t>
         </is>
       </c>
     </row>
@@ -8242,17 +8292,17 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>HPL-douchecabines zoals boven i.p.v. metal-stud + tegels?</t>
+          <t>HPL-douchecabines i.p.v. metal-stud + tegels?</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Mag in HPL-cabines en -wanden.</t>
         </is>
       </c>
       <c r="D18" s="37" t="inlineStr">
         <is>
-          <t>Basis volgens bestek; HPL-cabines als optimalisatie.</t>
+          <t>8 HPL-cabines; metal-stud douchewanden en veel tegelwerk vervallen.</t>
         </is>
       </c>
     </row>
@@ -8262,31 +8312,311 @@
       </c>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>08:00–16:00 hard of afbouw een uur eerder/later?</t>
+          <t>08:00–16:00 hard?</t>
         </is>
       </c>
       <c r="C19" s="37" t="inlineStr">
         <is>
-          <t>Niet in dit document</t>
+          <t>Eerder/later toegestaan mits beperkte geluidsoverlast.</t>
         </is>
       </c>
       <c r="D19" s="37" t="inlineStr">
         <is>
-          <t>Uitgegaan van 08:00–16:00 voor lawaaiig werk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="35" t="inlineStr">
-        <is>
-          <t>Opvallend: de NvI noemt Gemeente Wijdemeren als aanbestedende dienst en is gedateerd na de oorspronkelijke sluitingsdatum (18-09). Controleer de actuele sluitingsdatum op TenderNed.</t>
+          <t>Productiviteitsrisico verlaagd naar 40%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Wandtegels douches</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>Gebruikelijke kwaliteit, geglazuurd wit.</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>€ 92/m², 70 m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>Type en merk vloerafwerking</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>Volgens technische omschrijving; merk en type door aannemer.</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>Ongewijzigd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>Herstel aansluitingen na sloop wanden</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>Beperkt; inschatting door aannemer meenemen in de posten.</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>Post herstel € 3.500 toegevoegd in E25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Merk/type privacyfolie</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>Door aannemer.</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="inlineStr">
+        <is>
+          <t>Ongewijzigd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>Opslag en transport binnenwanden</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>Alleen glazen wanden voor hergebruik op locatie; opslag in overleg, mogelijk in gebouw.</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>Omschrijving aangepast; bedrag ongewijzigd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="37" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>Opbouw binnenwanden</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Kwaliteitseisen in de omschrijving; technische uitvoering aan aannemer.</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>Ongewijzigd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="37" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>Rc-waarden gevels</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="inlineStr">
+        <is>
+          <t>Na gunning beschikbaar.</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>Geen invloed op prijs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="37" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>NEN077 = NEN 5077?</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>Ja.</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>Ongewijzigd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="37" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>Type en merk plafond</t>
+        </is>
+      </c>
+      <c r="C28" s="37" t="inlineStr">
+        <is>
+          <t>60x60 wit; merk en type door aannemer.</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>Ongewijzigd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>Brandeis gordijnen</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>Zie vraag 7.</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="inlineStr">
+        <is>
+          <t>Zie vraag 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="37" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>Post voor keuzes in overleg?</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>Basiskeuzes en standaard-RAL in de prijs; bijzondere keuzes kunnen meerkosten geven.</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="inlineStr">
+        <is>
+          <t>Geen aparte post; standaard-RAL aangehouden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="37" t="inlineStr">
+        <is>
+          <t>Uitvoeringstermijn 3 maanden te kort</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>Zie vraag 8.</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="inlineStr">
+        <is>
+          <t>Zie vraag 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="37" t="inlineStr">
+        <is>
+          <t>Als vraag 3 (herhaald, 21-09)</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>Definitief: lichtplan en warmteverlies in engineering; fietsenstalling buiten beschouwing.</t>
+        </is>
+      </c>
+      <c r="D32" s="37" t="inlineStr">
+        <is>
+          <t>Zie vraag 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="37" t="inlineStr">
+        <is>
+          <t>Omschrijving nieuw sanitair</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>2 standaard wandclosets.</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="inlineStr">
+        <is>
+          <t>Post closets 0.66/0.67 aangepast naar € 4.000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="35" t="inlineStr">
+        <is>
+          <t>Let op: de NvI noemt Gemeente Wijdemeren als aanbestedende dienst en is gedateerd na de oorspronkelijke sluitingsdatum (18-09). Controleer de actuele sluitingsdatum op TenderNed.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8294,6 +8624,647 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Componentenboek W-installaties HILV-THEBE22-SPEC-001 rev. 1.0 (SPIE, 12-07-2022) – toepassing op de begane grond</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Opgesteld voor de verbouwing van de verdiepingen (2022). Volgens E&amp;W 3.6 gelden deze fabricaten ook voor de BG, tenzij de werkomschrijving anders voorschrijft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>Fabricaat / type</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>Verwerking</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Keukenmengkraan keukenblokjes kamer</t>
+        </is>
+      </c>
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>Levering bouwkundige aannemer</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>Alleen relevant als pantry's water krijgen – zie risico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
+          <t>Close-in boiler keukenblok kamers</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>Inventum Modesto Q10 (10 L, 2 kW)</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>Niet op BG-tekeningen; risico pantry's met water (€ 45.000, niet meegeprijsd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>Afvoer-sifoncombinatie keukenblok kamers</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>McAlpine o.g.</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>Idem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Douchepaneel douches</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>De Melker MC.501229 M-Check</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Prijs per douche verhoogd naar € 1.450 (compleet paneel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>Wastrog douches/wasruimte</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>Intersan Sanilav 3.0 RVS 1200 mm</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>4 wastroggen i.p.v. 8 wastafels (aanname: 2 tappunten per trog).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Afvoerput douches</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>Aquaberg 4815 RVS</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Opgenomen in douche-aansluiting (€ 1.600).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>Douchebak 120x90</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>Wisa Wavedesign o.g.</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>BBN schrijft tegelvloer met afschot voor → niet meegeprijsd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>MIVA-WC</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>Geberit 300 comfort verlengd + Duofix + Linido</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>MIVA-toiletruimte 0.72 (WC-02 op T.0.01).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>MIVA-douche</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>De Melker + Grohe Relexa + Linido douchezit</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>Geen MIVA-douche op BG-tekeningen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>MIVA-wastafel</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t>Geberit 300 comfort + Hansgrohe Care</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>MIVA-toiletruimte 0.72 (WT-02 op T.0.01).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>Uitstortgootsteen</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>Alape AG.Contra 505 + Daalderop</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>3e verdieping; UG-01 op BG bestaand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>Centrale tapwateropstelling</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>2× Mitsubishi Q-Ton 30 kW + 3× Lapesa 1500 L</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>Bestaand, blijft gehandhaafd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>Constant-volumeregelaar</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>Solid Air VCMHAR dubbelwandig</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
+        <is>
+          <t>Niet in E&amp;W/L.0.01 → risico (niet meegeprijsd).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>Toevoerrooster fancoils</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>Solid Air RTBMOR 450</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>In roosterpost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>Recirculatierooster fancoils</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>Solid Air RRBMOR 450</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>In roosterpost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Verlaagde plenumbox fancoils</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>Solid Air model 450</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="inlineStr">
+        <is>
+          <t>Nieuwe post: 34 × € 260.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>Toevoerrooster LBK</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>Solid Air CTVM</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="E21" s="37" t="inlineStr">
+        <is>
+          <t>In roosterpost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>Afvoerrooster LBK</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>Solid Air CRVM</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="inlineStr">
+        <is>
+          <t>In roosterpost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Akoestische slang</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>Sonodec 25</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="E23" s="37" t="inlineStr">
+        <is>
+          <t>In roosterpost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>Brandklep motorbediend</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>Solid Air FDC25 24 V DC</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="inlineStr">
+        <is>
+          <t>Typeconflict E&amp;W opgelost: FDC25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="37" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>Binnenriolering geluidgedempt</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Dyka Sono</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="inlineStr">
+        <is>
+          <t>Conform E&amp;W 6.1.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="37" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>Tapkraan wasmachine</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="inlineStr">
+        <is>
+          <t>Springer N300A034T</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="inlineStr">
+        <is>
+          <t>In wasmachine-aansluiting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="37" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>Ruimtebedienapparaat fancoil</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>CIAT RTR-E 7203</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
+        <is>
+          <t>Conflict met E&amp;W (99DAsei) – prijs gelijk gehouden.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/calculatie/Thebe22_calculatiemodel_VDL.xlsx
+++ b/calculatie/Thebe22_calculatiemodel_VDL.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Tellingen" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -697,7 +697,7 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Versie 3 (30-09-2026): antwoorden NvI en componentenboek verwerkt (tabbladen NvI en Componentenboek). Versie 2: installatie-aantallen zijn geteld op de tekeningen E.001, L.0.01-A/B, D.0.01-A/B, T.0.01, T.0.02, R.0.01 en R.-1.01 (zie tabblad 'Tellingen'). De Nota van Inlichtingen van 21-09-2026 is verwerkt (zie tabblad 'NvI'). De bouwkundige tekeningen (BBN bijlage 1 t/m 4) ontbreken nog: wandlengtes en vloeroppervlakken zijn afgeleid uit het stramien van 7,2 m. Tel alles na op DWG.</t>
+          <t>Versie 4 (30-09-2026): bouwkundige Bijlagen 1 t/m 4 verwerkt (vloeroppervlakken, brandscheidingen, extra scope verdiepingen en terrein). Versie 3: antwoorden NvI en componentenboek verwerkt (tabbladen NvI en Componentenboek). Versie 2: installatie-aantallen zijn geteld op de tekeningen E.001, L.0.01-A/B, D.0.01-A/B, T.0.01, T.0.02, R.0.01 en R.-1.01 (zie tabblad 'Tellingen'). De Nota van Inlichtingen van 21-09-2026 is verwerkt (zie tabblad 'NvI'). De bouwkundige tekeningen (BBN bijlage 1 t/m 4) ontbreken nog: wandlengtes en vloeroppervlakken zijn afgeleid uit het stramien van 7,2 m. Tel alles na op DWG.</t>
         </is>
       </c>
     </row>
@@ -850,11 +850,11 @@
       </c>
       <c r="C5" s="11" t="n"/>
       <c r="D5" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,13)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,13)</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,13)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,13)</f>
         <v/>
       </c>
       <c r="F5" s="13">
@@ -879,11 +879,11 @@
       </c>
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,14)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,14)</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,14)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,14)</f>
         <v/>
       </c>
       <c r="F6" s="13">
@@ -908,11 +908,11 @@
       </c>
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,15)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,15)</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,15)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,15)</f>
         <v/>
       </c>
       <c r="F7" s="13">
@@ -937,11 +937,11 @@
       </c>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,16)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,16)</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,16)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,16)</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -966,11 +966,11 @@
       </c>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,17)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,17)</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,17)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,17)</f>
         <v/>
       </c>
       <c r="F9" s="13">
@@ -995,11 +995,11 @@
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,18)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,18)</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,18)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,18)</f>
         <v/>
       </c>
       <c r="F10" s="13">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,19)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,19)</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,19)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,19)</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1053,11 +1053,11 @@
       </c>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,20)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,20)</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,20)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,20)</f>
         <v/>
       </c>
       <c r="F12" s="13">
@@ -1082,11 +1082,11 @@
       </c>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,21)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,21)</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,21)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,21)</f>
         <v/>
       </c>
       <c r="F13" s="13">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,23)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,23)</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,23)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,23)</f>
         <v/>
       </c>
       <c r="F15" s="13">
@@ -1156,11 +1156,11 @@
       </c>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,24)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,24)</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,24)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,24)</f>
         <v/>
       </c>
       <c r="F16" s="13">
@@ -1185,11 +1185,11 @@
       </c>
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,25)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,25)</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,25)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,25)</f>
         <v/>
       </c>
       <c r="F17" s="13">
@@ -1214,11 +1214,11 @@
       </c>
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,26)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,26)</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,26)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,26)</f>
         <v/>
       </c>
       <c r="F18" s="13">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,27)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,27)</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,27)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,27)</f>
         <v/>
       </c>
       <c r="F19" s="13">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,28)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,28)</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,28)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,28)</f>
         <v/>
       </c>
       <c r="F20" s="13">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,29)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,29)</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,29)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,29)</f>
         <v/>
       </c>
       <c r="F21" s="13">
@@ -1330,11 +1330,11 @@
       </c>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,30)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,30)</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,30)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,30)</f>
         <v/>
       </c>
       <c r="F22" s="13">
@@ -1359,11 +1359,11 @@
       </c>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,31)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,31)</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,31)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,31)</f>
         <v/>
       </c>
       <c r="F23" s="13">
@@ -1388,11 +1388,11 @@
       </c>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,32)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,32)</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,32)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,32)</f>
         <v/>
       </c>
       <c r="F24" s="13">
@@ -1418,11 +1418,11 @@
       </c>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,33)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,33)</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,33)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,33)</f>
         <v/>
       </c>
       <c r="F25" s="13">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,34)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,34)</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,34)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,34)</f>
         <v/>
       </c>
       <c r="F26" s="13">
@@ -1492,11 +1492,11 @@
       </c>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,36)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,36)</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,36)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,36)</f>
         <v/>
       </c>
       <c r="F28" s="13">
@@ -1521,11 +1521,11 @@
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,37)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,37)</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,37)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,37)</f>
         <v/>
       </c>
       <c r="F29" s="13">
@@ -1550,11 +1550,11 @@
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$108,Begroting!$A$2:$A$108,38)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,38)</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$14,Risicos!$H$2:$H$14,38)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,38)</f>
         <v/>
       </c>
       <c r="F30" s="13">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="F44" s="21">
-        <f>Risicos!I16/F35</f>
+        <f>Risicos!I19/F35</f>
         <v/>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D63" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.2/3.2.4 + NvI vraag 11/17</t>
+          <t>BBN 3.2.2/3.2.4 + NvI vraag 11/17 + Bijlage 3</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="F63" s="24" t="n">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>44</v>
@@ -4815,7 +4815,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K63" s="23" t="inlineStr"/>
+      <c r="K63" s="23" t="inlineStr">
+        <is>
+          <t>Gemeten op Bijlage 3: tapijt 939 m² (wordt marmoleum) + marmoleum 103 m². Hal 0.01 valt buiten scope; terrazzo 32 m² blijft</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="23" t="n">
@@ -5117,7 +5121,7 @@
       </c>
       <c r="D70" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1/3.3.3 + NvI vraag 6</t>
+          <t>BBN 3.3.1/3.3.3 + NvI vraag 6 + Bijlage 4</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
@@ -5126,7 +5130,7 @@
         </is>
       </c>
       <c r="F70" s="24" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="25" t="n">
         <v>105</v>
@@ -5147,7 +5151,7 @@
       </c>
       <c r="K70" s="23" t="inlineStr">
         <is>
-          <t>Afgeleid uit stramien 7,2 m op L.0.01/E.001: ca. 300 m1 nieuwe wand (kamerscheidend + gangwanden) × 3,3 m. NvI vraag 6: alle kamerscheidende wanden volledig nieuw. Hoogte tot betondek nameten</t>
+          <t>Gemeten op Bijlage 4: ca. 329 m1 scheiding 30 min WBDBO, waarvan ca. 320 m1 nieuwe wand × 3,3 m. Opbouw volgens Bijlage 4: 2× 12,5 mm gips beide zijden + minerale wol. Hoogte tot betondek nameten</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5280,7 @@
         </is>
       </c>
       <c r="F73" s="24" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G73" s="25" t="n">
         <v>14</v>
@@ -5404,12 +5408,12 @@
       </c>
       <c r="C76" s="23" t="inlineStr">
         <is>
-          <t>Sluitplan / cilinders met moedersleutelsysteem, hang- en sluitwerk SKG2</t>
+          <t>Zelfsluitende deurstellen EI60 in 60-min compartimentsgrenzen</t>
         </is>
       </c>
       <c r="D76" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1 + NvI vraag 4</t>
+          <t>Bijlage 4</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
@@ -5418,10 +5422,10 @@
         </is>
       </c>
       <c r="F76" s="24" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="G76" s="25" t="n">
-        <v>150</v>
+        <v>2800</v>
       </c>
       <c r="H76" s="26">
         <f>F76*G76</f>
@@ -5429,7 +5433,7 @@
       </c>
       <c r="I76" s="23" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>VDL / OA leverancier</t>
         </is>
       </c>
       <c r="J76" s="23" t="inlineStr">
@@ -5439,7 +5443,7 @@
       </c>
       <c r="K76" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 4: nieuw hang- en sluitwerk SKG2; wanden hotelstandaard, geen extra inbraakwerendheid</t>
+          <t>Aantal inschatten; Bijlage 4 toont ca. 96 m1 scheiding 60 min, grotendeels bestaand</t>
         </is>
       </c>
     </row>
@@ -5454,24 +5458,24 @@
       </c>
       <c r="C77" s="23" t="inlineStr">
         <is>
-          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
+          <t>Aansluiten nieuwe wanden op bestaande 60-min scheidingen, controle en herstel</t>
         </is>
       </c>
       <c r="D77" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1</t>
+          <t>Bijlage 4 / BBN 4.1</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F77" s="24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G77" s="25" t="n">
-        <v>260</v>
+        <v>3500</v>
       </c>
       <c r="H77" s="26">
         <f>F77*G77</f>
@@ -5491,21 +5495,21 @@
     </row>
     <row r="78">
       <c r="A78" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B78" s="23" t="inlineStr">
         <is>
-          <t>Vervangen plafondafwerking</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C78" s="23" t="inlineStr">
         <is>
-          <t>Verwijderen bestaand plafond incl. constructie</t>
+          <t>Ondoorzichtige folie op hergebruikte glazen puien (0.44, 0.45, 0.62, 0.63, 0.64)</t>
         </is>
       </c>
       <c r="D78" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.5</t>
+          <t>Bijlage 4</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
@@ -5514,10 +5518,10 @@
         </is>
       </c>
       <c r="F78" s="24" t="n">
-        <v>1250</v>
+        <v>90</v>
       </c>
       <c r="G78" s="25" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="H78" s="26">
         <f>F78*G78</f>
@@ -5525,7 +5529,7 @@
       </c>
       <c r="I78" s="23" t="inlineStr">
         <is>
-          <t>OA plafondmonteur</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J78" s="23" t="inlineStr">
@@ -5533,37 +5537,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K78" s="23" t="inlineStr"/>
+      <c r="K78" s="23" t="inlineStr">
+        <is>
+          <t>Bijlage 4: glazen puien hergebruiken en voorzien van ondoorzichtige folie</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>Vervangen plafondafwerking</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
         <is>
-          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
+          <t>Sluitplan / cilinders met moedersleutelsysteem, hang- en sluitwerk SKG2</t>
         </is>
       </c>
       <c r="D79" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.5</t>
+          <t>BBN 3.4.1 + NvI vraag 4</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F79" s="24" t="n">
-        <v>1200</v>
+        <v>45</v>
       </c>
       <c r="G79" s="25" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="H79" s="26">
         <f>F79*G79</f>
@@ -5571,7 +5579,7 @@
       </c>
       <c r="I79" s="23" t="inlineStr">
         <is>
-          <t>OA plafondmonteur</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J79" s="23" t="inlineStr">
@@ -5579,37 +5587,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K79" s="23" t="inlineStr"/>
+      <c r="K79" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 4: nieuw hang- en sluitwerk SKG2; wanden hotelstandaard, geen extra inbraakwerendheid</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B80" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen zonwering</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C80" s="23" t="inlineStr">
         <is>
-          <t>Demonteren bestaande binnenzonwering</t>
+          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
         </is>
       </c>
       <c r="D80" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.1</t>
+          <t>BBN 3.4.1</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F80" s="24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G80" s="25" t="n">
-        <v>1500</v>
+        <v>260</v>
       </c>
       <c r="H80" s="26">
         <f>F80*G80</f>
@@ -5625,41 +5637,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K80" s="23" t="inlineStr">
-        <is>
-          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
-        </is>
-      </c>
+      <c r="K80" s="23" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen zonwering</t>
+          <t>Vervangen plafondafwerking</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
         <is>
-          <t>Verduisterende gordijnen brandvertragend (hotelfunctie) incl. rails, gelijk aan verdiepingen</t>
+          <t>Verwijderen bestaand plafond incl. constructie</t>
         </is>
       </c>
       <c r="D81" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.1 + NvI vraag 7/26</t>
+          <t>BBN 3.5</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F81" s="24" t="n">
-        <v>150</v>
+        <v>1250</v>
       </c>
       <c r="G81" s="25" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="H81" s="26">
         <f>F81*G81</f>
@@ -5667,7 +5675,7 @@
       </c>
       <c r="I81" s="23" t="inlineStr">
         <is>
-          <t>OA stoffeerder</t>
+          <t>OA plafondmonteur</t>
         </is>
       </c>
       <c r="J81" s="23" t="inlineStr">
@@ -5675,41 +5683,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K81" s="23" t="inlineStr">
-        <is>
-          <t>Raamlengtes uitmeten</t>
-        </is>
-      </c>
+      <c r="K81" s="23" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B82" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Vervangen plafondafwerking</t>
         </is>
       </c>
       <c r="C82" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
+          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
         </is>
       </c>
       <c r="D82" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.5</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F82" s="24" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="G82" s="25" t="n">
-        <v>780</v>
+        <v>42</v>
       </c>
       <c r="H82" s="26">
         <f>F82*G82</f>
@@ -5717,7 +5721,7 @@
       </c>
       <c r="I82" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>OA plafondmonteur</t>
         </is>
       </c>
       <c r="J82" s="23" t="inlineStr">
@@ -5729,33 +5733,33 @@
     </row>
     <row r="83">
       <c r="A83" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B83" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Aanpassen zonwering</t>
         </is>
       </c>
       <c r="C83" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok eetruimte</t>
+          <t>Demonteren bestaande binnenzonwering</t>
         </is>
       </c>
       <c r="D83" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.7.1</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F83" s="24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G83" s="25" t="n">
-        <v>780</v>
+        <v>1500</v>
       </c>
       <c r="H83" s="26">
         <f>F83*G83</f>
@@ -5763,7 +5767,7 @@
       </c>
       <c r="I83" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J83" s="23" t="inlineStr">
@@ -5771,37 +5775,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K83" s="23" t="inlineStr"/>
+      <c r="K83" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B84" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Aanpassen zonwering</t>
         </is>
       </c>
       <c r="C84" s="23" t="inlineStr">
         <is>
-          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
+          <t>Verduisterende gordijnen brandvertragend (hotelfunctie) incl. rails, gelijk aan verdiepingen</t>
         </is>
       </c>
       <c r="D84" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.7.1 + NvI vraag 7/26</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F84" s="24" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="G84" s="25" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="H84" s="26">
         <f>F84*G84</f>
@@ -5809,7 +5817,7 @@
       </c>
       <c r="I84" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>OA stoffeerder</t>
         </is>
       </c>
       <c r="J84" s="23" t="inlineStr">
@@ -5819,7 +5827,7 @@
       </c>
       <c r="K84" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
+          <t>Raamlengtes uitmeten</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5842,7 @@
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
+          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
         </is>
       </c>
       <c r="D85" s="23" t="inlineStr">
@@ -5844,14 +5852,14 @@
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F85" s="24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G85" s="25" t="n">
-        <v>520</v>
+        <v>780</v>
       </c>
       <c r="H85" s="26">
         <f>F85*G85</f>
@@ -5880,24 +5888,24 @@
       </c>
       <c r="C86" s="23" t="inlineStr">
         <is>
-          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+          <t>Keukenblok eetruimte</t>
         </is>
       </c>
       <c r="D86" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.3</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F86" s="24" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G86" s="25" t="n">
-        <v>1350</v>
+        <v>780</v>
       </c>
       <c r="H86" s="26">
         <f>F86*G86</f>
@@ -5913,29 +5921,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K86" s="23" t="inlineStr">
-        <is>
-          <t>29 kamers (kk op alle plattegronden). LET OP: T.0.01/R.0.01 tonen GEEN water/afvoer naar de kamers; BBN 3.7.3 vraagt wel RVS-spoelbak + kraan</t>
-        </is>
-      </c>
+      <c r="K86" s="23" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B87" s="23" t="inlineStr">
         <is>
-          <t>Realiseren douchevoorzieningen</t>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
         </is>
       </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>HPL-douchecabines incl. scheidingswanden, deuren en beslag (0.37 en 0.42)</t>
+          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
         </is>
       </c>
       <c r="D87" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 14</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
@@ -5944,10 +5948,10 @@
         </is>
       </c>
       <c r="F87" s="24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G87" s="25" t="n">
-        <v>1650</v>
+        <v>950</v>
       </c>
       <c r="H87" s="26">
         <f>F87*G87</f>
@@ -5955,49 +5959,49 @@
       </c>
       <c r="I87" s="23" t="inlineStr">
         <is>
-          <t>OA leverancier cabines</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J87" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K87" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 14: HPL-cabines en -wanden toegestaan, zoals op de verdiepingen</t>
+          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B88" s="23" t="inlineStr">
         <is>
-          <t>Realiseren douchevoorzieningen</t>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
         </is>
       </c>
       <c r="C88" s="23" t="inlineStr">
         <is>
-          <t>Wandtegelwerk wit geglazuurd op buitenwanden douche-/badruimten incl. afdichtingssysteem</t>
+          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
         </is>
       </c>
       <c r="D88" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.4 + NvI vraag 16</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F88" s="24" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="G88" s="25" t="n">
-        <v>92</v>
+        <v>520</v>
       </c>
       <c r="H88" s="26">
         <f>F88*G88</f>
@@ -6005,7 +6009,7 @@
       </c>
       <c r="I88" s="23" t="inlineStr">
         <is>
-          <t>OA tegelzetter</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J88" s="23" t="inlineStr">
@@ -6013,41 +6017,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K88" s="23" t="inlineStr">
-        <is>
-          <t>NvI vraag 16: gebruikelijke kwaliteit, geglazuurd wit. Minder m² door HPL-cabines</t>
-        </is>
-      </c>
+      <c r="K88" s="23" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+        </is>
+      </c>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+        </is>
+      </c>
+      <c r="D89" s="23" t="inlineStr">
+        <is>
+          <t>BBN 3.7.3</t>
+        </is>
+      </c>
+      <c r="E89" s="23" t="inlineStr">
+        <is>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>Realiseren douchevoorzieningen</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="inlineStr">
-        <is>
-          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
-        </is>
-      </c>
-      <c r="D89" s="23" t="inlineStr">
-        <is>
-          <t>BBN 3.2.3</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="F89" s="24" t="n">
-        <v>45</v>
-      </c>
       <c r="G89" s="25" t="n">
-        <v>145</v>
+        <v>1350</v>
       </c>
       <c r="H89" s="26">
         <f>F89*G89</f>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="I89" s="23" t="inlineStr">
         <is>
-          <t>OA tegelzetter</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J89" s="23" t="inlineStr">
@@ -6063,7 +6063,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K89" s="23" t="inlineStr"/>
+      <c r="K89" s="23" t="inlineStr">
+        <is>
+          <t>29 kamers (kk op alle plattegronden). LET OP: T.0.01/R.0.01 tonen GEEN water/afvoer naar de kamers; BBN 3.7.3 vraagt wel RVS-spoelbak + kraan</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="23" t="n">
@@ -6076,12 +6080,12 @@
       </c>
       <c r="C90" s="23" t="inlineStr">
         <is>
-          <t>Douchedeuren 0.70/0.71 (vochtbestendig, Trespa o.g.)</t>
+          <t>HPL-douchecabines incl. scheidingswanden, deuren en beslag (0.37 en 0.42)</t>
         </is>
       </c>
       <c r="D90" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.3</t>
+          <t>NvI vraag 14</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -6090,10 +6094,10 @@
         </is>
       </c>
       <c r="F90" s="24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G90" s="25" t="n">
-        <v>680</v>
+        <v>1650</v>
       </c>
       <c r="H90" s="26">
         <f>F90*G90</f>
@@ -6101,49 +6105,49 @@
       </c>
       <c r="I90" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA leverancier cabines</t>
         </is>
       </c>
       <c r="J90" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K90" s="23" t="inlineStr">
         <is>
-          <t>Deuren van de cabines in 0.37/0.42 zitten in de HPL-post</t>
+          <t>NvI vraag 14: HPL-cabines en -wanden toegestaan, zoals op de verdiepingen</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B91" s="23" t="inlineStr">
         <is>
-          <t>Realiseren hekwerk terrein</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C91" s="23" t="inlineStr">
         <is>
-          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
+          <t>Wandtegelwerk wit geglazuurd op buitenwanden douche-/badruimten incl. afdichtingssysteem</t>
         </is>
       </c>
       <c r="D91" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.2</t>
+          <t>BBN 3.3.4 + NvI vraag 16</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F91" s="24" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="G91" s="25" t="n">
-        <v>225</v>
+        <v>92</v>
       </c>
       <c r="H91" s="26">
         <f>F91*G91</f>
@@ -6151,7 +6155,7 @@
       </c>
       <c r="I91" s="23" t="inlineStr">
         <is>
-          <t>OA hekwerk</t>
+          <t>OA tegelzetter</t>
         </is>
       </c>
       <c r="J91" s="23" t="inlineStr">
@@ -6161,39 +6165,39 @@
       </c>
       <c r="K91" s="23" t="inlineStr">
         <is>
-          <t>Lengte uitmeten</t>
+          <t>NvI vraag 16: gebruikelijke kwaliteit, geglazuurd wit. Minder m² door HPL-cabines</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B92" s="23" t="inlineStr">
         <is>
-          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C92" s="23" t="inlineStr">
         <is>
-          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
+          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
         </is>
       </c>
       <c r="D92" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.1</t>
+          <t>BBN 3.2.3</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F92" s="24" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="G92" s="25" t="n">
-        <v>1500</v>
+        <v>145</v>
       </c>
       <c r="H92" s="26">
         <f>F92*G92</f>
@@ -6201,7 +6205,7 @@
       </c>
       <c r="I92" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA tegelzetter</t>
         </is>
       </c>
       <c r="J92" s="23" t="inlineStr">
@@ -6213,33 +6217,33 @@
     </row>
     <row r="93">
       <c r="A93" s="23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B93" s="23" t="inlineStr">
         <is>
-          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C93" s="23" t="inlineStr">
         <is>
-          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
+          <t>Douchedeuren 0.70/0.71 (vochtbestendig, Trespa o.g.)</t>
         </is>
       </c>
       <c r="D93" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.1</t>
+          <t>BBN 3.4.3</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F93" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G93" s="25" t="n">
-        <v>4300</v>
+        <v>680</v>
       </c>
       <c r="H93" s="26">
         <f>F93*G93</f>
@@ -6255,37 +6259,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K93" s="23" t="inlineStr"/>
+      <c r="K93" s="23" t="inlineStr">
+        <is>
+          <t>Deuren van de cabines in 0.37/0.42 zitten in de HPL-post</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B94" s="23" t="inlineStr">
         <is>
-          <t>Realiseren fietsenstalling</t>
+          <t>Realiseren hekwerk terrein</t>
         </is>
       </c>
       <c r="C94" s="23" t="inlineStr">
         <is>
-          <t>Fietsenstalling: buiten beschouwing volgens NvI vraag 3/29</t>
+          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
         </is>
       </c>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 3/29</t>
+          <t>BBN 3.8.2</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F94" s="24" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G94" s="25" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="H94" s="26">
         <f>F94*G94</f>
@@ -6293,7 +6301,7 @@
       </c>
       <c r="I94" s="23" t="inlineStr">
         <is>
-          <t>n.v.t.</t>
+          <t>OA hekwerk</t>
         </is>
       </c>
       <c r="J94" s="23" t="inlineStr">
@@ -6303,27 +6311,27 @@
       </c>
       <c r="K94" s="23" t="inlineStr">
         <is>
-          <t>NvI: fietsenstalling wordt buiten beschouwing gelaten → € 0 in het formulier</t>
+          <t>Bijlage 1: aluminium balustrade gelijk aan uitvoering bij de trappen. Lengte uitmeten</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="23" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B95" s="23" t="inlineStr">
         <is>
-          <t>Doorvoeringen inbranden voor de installaties</t>
+          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
         </is>
       </c>
       <c r="C95" s="23" t="inlineStr">
         <is>
-          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
+          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
         </is>
       </c>
       <c r="D95" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
+          <t>BBN 3.8.1</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
@@ -6332,10 +6340,10 @@
         </is>
       </c>
       <c r="F95" s="24" t="n">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="G95" s="25" t="n">
-        <v>48</v>
+        <v>1500</v>
       </c>
       <c r="H95" s="26">
         <f>F95*G95</f>
@@ -6343,37 +6351,33 @@
       </c>
       <c r="I95" s="23" t="inlineStr">
         <is>
-          <t>VMT Brandpreventie</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J95" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
-        </is>
-      </c>
-      <c r="K95" s="23" t="inlineStr">
-        <is>
-          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
-        </is>
-      </c>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K95" s="23" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="23" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B96" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
+          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
         </is>
       </c>
       <c r="C96" s="23" t="inlineStr">
         <is>
-          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
+          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
         </is>
       </c>
       <c r="D96" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.1</t>
+          <t>BBN 3.8.1</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
@@ -6385,7 +6389,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="25" t="n">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="H96" s="26">
         <f>F96*G96</f>
@@ -6405,21 +6409,21 @@
     </row>
     <row r="97">
       <c r="A97" s="23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B97" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
+          <t>Realiseren fietsenstalling</t>
         </is>
       </c>
       <c r="C97" s="23" t="inlineStr">
         <is>
-          <t>Opleveringsschoonmaak</t>
+          <t>Fietsenstalling: buiten beschouwing volgens NvI vraag 3/29</t>
         </is>
       </c>
       <c r="D97" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.2</t>
+          <t>NvI vraag 3/29</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
@@ -6428,10 +6432,10 @@
         </is>
       </c>
       <c r="F97" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="25" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H97" s="26">
         <f>F97*G97</f>
@@ -6439,7 +6443,7 @@
       </c>
       <c r="I97" s="23" t="inlineStr">
         <is>
-          <t>OA schoonmaak</t>
+          <t>n.v.t.</t>
         </is>
       </c>
       <c r="J97" s="23" t="inlineStr">
@@ -6447,37 +6451,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K97" s="23" t="inlineStr"/>
+      <c r="K97" s="23" t="inlineStr">
+        <is>
+          <t>NvI: fietsenstalling wordt buiten beschouwing gelaten → € 0 in het formulier</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="23" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B98" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Doorvoeringen inbranden voor de installaties</t>
         </is>
       </c>
       <c r="C98" s="23" t="inlineStr">
         <is>
-          <t>Bouwkundige engineering, detaillering, constructeur</t>
+          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
         </is>
       </c>
       <c r="D98" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.1</t>
+          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F98" s="24" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="G98" s="25" t="n">
-        <v>12000</v>
+        <v>48</v>
       </c>
       <c r="H98" s="26">
         <f>F98*G98</f>
@@ -6485,33 +6493,37 @@
       </c>
       <c r="I98" s="23" t="inlineStr">
         <is>
-          <t>VDL / adviseur</t>
+          <t>VMT Brandpreventie</t>
         </is>
       </c>
       <c r="J98" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K98" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K98" s="23" t="inlineStr">
+        <is>
+          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B99" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
         </is>
       </c>
       <c r="C99" s="23" t="inlineStr">
         <is>
-          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
+          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
         </is>
       </c>
       <c r="D99" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.7/3.9</t>
+          <t>BBN 6.1</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
@@ -6523,7 +6535,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="25" t="n">
-        <v>18000</v>
+        <v>5000</v>
       </c>
       <c r="H99" s="26">
         <f>F99*G99</f>
@@ -6531,7 +6543,7 @@
       </c>
       <c r="I99" s="23" t="inlineStr">
         <is>
-          <t>OA installateurs</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J99" s="23" t="inlineStr">
@@ -6539,29 +6551,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K99" s="23" t="inlineStr">
-        <is>
-          <t>Reken op 5 weken review-cyclus met Winkelman</t>
-        </is>
-      </c>
+      <c r="K99" s="23" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B100" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
         </is>
       </c>
       <c r="C100" s="23" t="inlineStr">
         <is>
-          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
+          <t>Opleveringsschoonmaak</t>
         </is>
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9 / E&amp;W 3.3</t>
+          <t>BBN 6.2</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -6573,7 +6581,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="25" t="n">
-        <v>16000</v>
+        <v>3500</v>
       </c>
       <c r="H100" s="26">
         <f>F100*G100</f>
@@ -6581,7 +6589,7 @@
       </c>
       <c r="I100" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA schoonmaak</t>
         </is>
       </c>
       <c r="J100" s="23" t="inlineStr">
@@ -6593,21 +6601,21 @@
     </row>
     <row r="101">
       <c r="A101" s="23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B101" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C101" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
+          <t>Bouwkundige engineering, detaillering, constructeur</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.6 / E&amp;W 3.9</t>
+          <t>BBN 4.1</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
@@ -6619,7 +6627,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="25" t="n">
-        <v>6500</v>
+        <v>12000</v>
       </c>
       <c r="H101" s="26">
         <f>F101*G101</f>
@@ -6627,7 +6635,7 @@
       </c>
       <c r="I101" s="23" t="inlineStr">
         <is>
-          <t>VDL + OA</t>
+          <t>VDL / adviseur</t>
         </is>
       </c>
       <c r="J101" s="23" t="inlineStr">
@@ -6639,33 +6647,33 @@
     </row>
     <row r="102">
       <c r="A102" s="23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B102" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C102" s="23" t="inlineStr">
         <is>
-          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
+          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
         </is>
       </c>
       <c r="D102" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9</t>
+          <t>E&amp;W 3.7/3.9</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
         <is>
-          <t>week</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F102" s="24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G102" s="25" t="n">
-        <v>2600</v>
+        <v>18000</v>
       </c>
       <c r="H102" s="26">
         <f>F102*G102</f>
@@ -6673,7 +6681,7 @@
       </c>
       <c r="I102" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA installateurs</t>
         </is>
       </c>
       <c r="J102" s="23" t="inlineStr">
@@ -6683,27 +6691,27 @@
       </c>
       <c r="K102" s="23" t="inlineStr">
         <is>
-          <t>Start ca. 9 nov; NvI vraag 8: uitloop maximaal 6 weken toegestaan</t>
+          <t>Reken op 5 weken review-cyclus met Winkelman</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B103" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C103" s="23" t="inlineStr">
         <is>
-          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
+          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
         </is>
       </c>
       <c r="D103" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3</t>
+          <t>BBN 3.9 / E&amp;W 3.3</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
@@ -6715,7 +6723,7 @@
         <v>1</v>
       </c>
       <c r="G103" s="25" t="n">
-        <v>5500</v>
+        <v>16000</v>
       </c>
       <c r="H103" s="26">
         <f>F103*G103</f>
@@ -6735,33 +6743,33 @@
     </row>
     <row r="104">
       <c r="A104" s="23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B104" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Revisietekeningen</t>
         </is>
       </c>
       <c r="C104" s="23" t="inlineStr">
         <is>
-          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
+          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
         </is>
       </c>
       <c r="D104" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3/6.2</t>
+          <t>BBN 4.6 / E&amp;W 3.9</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F104" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G104" s="25" t="n">
-        <v>475</v>
+        <v>6500</v>
       </c>
       <c r="H104" s="26">
         <f>F104*G104</f>
@@ -6769,7 +6777,7 @@
       </c>
       <c r="I104" s="23" t="inlineStr">
         <is>
-          <t>OA afval</t>
+          <t>VDL + OA</t>
         </is>
       </c>
       <c r="J104" s="23" t="inlineStr">
@@ -6790,24 +6798,24 @@
       </c>
       <c r="C105" s="23" t="inlineStr">
         <is>
-          <t>V&amp;G-plan uitvoeringsfase (concept 2 weken voor start), werkplan, bouwplaatsinrichting, afzettingen</t>
+          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
         </is>
       </c>
       <c r="D105" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9/4.3/6.3 + NvI vraag 8</t>
+          <t>BBN 3.9</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>week</t>
         </is>
       </c>
       <c r="F105" s="24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G105" s="25" t="n">
-        <v>3500</v>
+        <v>2600</v>
       </c>
       <c r="H105" s="26">
         <f>F105*G105</f>
@@ -6823,7 +6831,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K105" s="23" t="inlineStr"/>
+      <c r="K105" s="23" t="inlineStr">
+        <is>
+          <t>Start ca. 9 nov; NvI vraag 8: uitloop maximaal 6 weken toegestaan</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="23" t="n">
@@ -6836,12 +6848,12 @@
       </c>
       <c r="C106" s="23" t="inlineStr">
         <is>
-          <t>Klein materieel, steigers/rolsteigers, transport</t>
+          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
         </is>
       </c>
       <c r="D106" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.2</t>
+          <t>BBN 4.3</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
@@ -6853,7 +6865,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="25" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="H106" s="26">
         <f>F106*G106</f>
@@ -6882,24 +6894,24 @@
       </c>
       <c r="C107" s="23" t="inlineStr">
         <is>
-          <t>Parkeerkosten openbare weg (2 voertuigen × ca. 65 werkdagen)</t>
+          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
         </is>
       </c>
       <c r="D107" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 9</t>
+          <t>BBN 4.3/6.2</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>dag</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F107" s="24" t="n">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="G107" s="25" t="n">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="H107" s="26">
         <f>F107*G107</f>
@@ -6907,7 +6919,7 @@
       </c>
       <c r="I107" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA afval</t>
         </is>
       </c>
       <c r="J107" s="23" t="inlineStr">
@@ -6915,11 +6927,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K107" s="23" t="inlineStr">
-        <is>
-          <t>NvI vraag 9: geen plekken op terrein, openbare weg is betaald parkeren</t>
-        </is>
-      </c>
+      <c r="K107" s="23" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="23" t="n">
@@ -6932,12 +6940,12 @@
       </c>
       <c r="C108" s="23" t="inlineStr">
         <is>
-          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+          <t>V&amp;G-plan uitvoeringsfase (concept 2 weken voor start), werkplan, bouwplaatsinrichting, afzettingen</t>
         </is>
       </c>
       <c r="D108" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.2 / BBN 4.4</t>
+          <t>BBN 3.9/4.3/6.3 + NvI vraag 8</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
@@ -6949,7 +6957,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="25" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="H108" s="26">
         <f>F108*G108</f>
@@ -6967,27 +6975,169 @@
       </c>
       <c r="K108" s="23" t="inlineStr"/>
     </row>
-    <row r="109"/>
+    <row r="109">
+      <c r="A109" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B109" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>Klein materieel, steigers/rolsteigers, transport</t>
+        </is>
+      </c>
+      <c r="D109" s="23" t="inlineStr">
+        <is>
+          <t>BBN 4.2</t>
+        </is>
+      </c>
+      <c r="E109" s="23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F109" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="25" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H109" s="26">
+        <f>F109*G109</f>
+        <v/>
+      </c>
+      <c r="I109" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J109" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K109" s="23" t="inlineStr"/>
+    </row>
     <row r="110">
-      <c r="C110" s="16" t="inlineStr">
+      <c r="A110" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B110" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>Parkeerkosten openbare weg (2 voertuigen × ca. 65 werkdagen)</t>
+        </is>
+      </c>
+      <c r="D110" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 9</t>
+        </is>
+      </c>
+      <c r="E110" s="23" t="inlineStr">
+        <is>
+          <t>dag</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="G110" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H110" s="26">
+        <f>F110*G110</f>
+        <v/>
+      </c>
+      <c r="I110" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J110" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K110" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 9: geen plekken op terrein, openbare weg is betaald parkeren</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
+        <is>
+          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+        </is>
+      </c>
+      <c r="D111" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 3.2 / BBN 4.4</t>
+        </is>
+      </c>
+      <c r="E111" s="23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H111" s="26">
+        <f>F111*G111</f>
+        <v/>
+      </c>
+      <c r="I111" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J111" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K111" s="23" t="inlineStr"/>
+    </row>
+    <row r="112"/>
+    <row r="113">
+      <c r="C113" s="16" t="inlineStr">
         <is>
           <t>Totaal directe kosten (excl. opslagen AK/W&amp;R/CAR en risico's)</t>
         </is>
       </c>
-      <c r="H110" s="28">
-        <f>SUM(H2:H108)</f>
+      <c r="H113" s="28">
+        <f>SUM(H2:H111)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K108"/>
-  <conditionalFormatting sqref="J2:J108">
+  <autoFilter ref="A1:K111"/>
+  <conditionalFormatting sqref="J2:J111">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J2="Richtprijs"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Richtprijs,Offerte aanvragen,Offerte ontvangen,Eigen norm,Stelpost (voorgeschreven)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7001,7 +7151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7528,19 +7678,19 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Tellingen uit PDF-tekeningen wijken af van de werkelijke aantallen</t>
+          <t>Werk op 1e en 2e verdieping volgens Bijlage 1 (DO-11): 3 personeelstoiletten 1e verd. incl. W/E; herplaatsen glaswand + deuren, OSB-passtukken en voorzetwand 2e verd.</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>Tekeningen E.001, L.0.01, T.0.01</t>
+          <t>Bijlage 1 blad 3 + NvI vraag 21</t>
         </is>
       </c>
       <c r="D13" s="29" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>10000</v>
+        <v>24500</v>
       </c>
       <c r="F13" s="26">
         <f>D13*E13</f>
@@ -7552,7 +7702,7 @@
         </is>
       </c>
       <c r="H13" s="31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I13" s="26">
         <f>IF(G13="Ja",F13,0)</f>
@@ -7560,7 +7710,7 @@
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>Tellingen zijn visueel/uit tekstlabels. Laat installateurs natellen op DWG (NvI vraag 2).</t>
+          <t>Staat niet in BBN/E&amp;W, maar wel in de bijlage die integraal onderdeel is. NvI 21: glazen wanden hergebruiken op deze locatie.</t>
         </is>
       </c>
     </row>
@@ -7570,19 +7720,19 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+          <t>Terreininrichting volgens Bijlage 1: taxushaag in plantenbakken (2,3 m), ACP-scheidingswanden, verplaatsen plantenbakken, zeecontainer als rookruimte; sportveld n.t.b.</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 4.2.2/7.1</t>
+          <t>Bijlage 1 blad 1</t>
         </is>
       </c>
       <c r="D14" s="29" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>8000</v>
+        <v>45000</v>
       </c>
       <c r="F14" s="26">
         <f>D14*E14</f>
@@ -7594,7 +7744,7 @@
         </is>
       </c>
       <c r="H14" s="31" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I14" s="26">
         <f>IF(G14="Ja",F14,0)</f>
@@ -7602,36 +7752,162 @@
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
+          <t>Niet in BBN 3.8 (alleen entrees, hekwerk, fietsenstalling). Niet meegeprijsd; sportveld expliciet n.t.b.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Twee versies plattegrond: Bijlage 1/3 (DO-01, 13-02) wijkt af van Bijlage 4 en installatietekeningen (BV-11, 28-04)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Bijlage 1/3 vs 4</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F15" s="26">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="26">
+        <f>IF(G15="Ja",F15,0)</f>
+        <v/>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>O.a. 0.64 (52 vs 33 m²), 0.44/0.45 douches vs gespreksruimten, 0.47. BBN noemt Bijlage 1 leidend voor te handhaven/slopen wanden. Prijs op BV-11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Tellingen uit PDF-tekeningen wijken af van de werkelijke aantallen</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Tekeningen E.001, L.0.01, T.0.01</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F16" s="26">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="I16" s="26">
+        <f>IF(G16="Ja",F16,0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>Tellingen zijn visueel/uit tekstlabels. Laat installateurs natellen op DWG (NvI vraag 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 4.2.2/7.1</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F17" s="26">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="31" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" s="26">
+        <f>IF(G17="Ja",F17,0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
           <t>Het bestek stelt dat de aannemer mag uitgaan van voldoende capaciteit, dus dit risico ligt bij de opdrachtgever.</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Totaal meegeprijsde risico's</t>
         </is>
       </c>
-      <c r="I16" s="28">
-        <f>SUM(I2:I14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="I19" s="28">
+        <f>SUM(I2:I17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Totaal verwachte waarde alle risico's (ter info)</t>
         </is>
       </c>
-      <c r="I17" s="20">
-        <f>SUM(F2:F14)</f>
+      <c r="I20" s="20">
+        <f>SUM(F2:F17)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G2:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Ja,Nee"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9270,7 +9546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9831,27 +10107,216 @@
     <row r="23">
       <c r="A23" s="37" t="inlineStr">
         <is>
-          <t>Nieuwe binnenwanden</t>
+          <t>Scheidingen 30 min WBDBO</t>
         </is>
       </c>
       <c r="B23" s="37" t="inlineStr">
         <is>
-          <t>ca. 300 m1</t>
+          <t>ca. 329 m1</t>
         </is>
       </c>
       <c r="C23" s="37" t="inlineStr">
         <is>
-          <t>Afgeleid uit stramien 7,2 m</t>
+          <t>Bijlage 4 (BV-11)</t>
         </is>
       </c>
       <c r="D23" s="37" t="inlineStr">
         <is>
-          <t>Kamers 3,6 m breed; bouwkundige tekeningen ontbreken</t>
+          <t>Gemeten op groene scheidingslijnen; ca. 320 m1 nieuwe wand</t>
         </is>
       </c>
       <c r="E23" s="37" t="inlineStr">
         <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>Scheidingen 60 min WBDBO</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>ca. 96 m1</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 4 (BV-11)</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>Grotendeels bestaand (kernen, compartimentsgrenzen)</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="37" t="inlineStr">
+        <is>
+          <t>Vloer: tapijt → marmoleum</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>939 m²</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 3</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>Gemeten op kleurvlakken; NvI 11: wordt marmoleum</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="37" t="inlineStr">
+        <is>
+          <t>Vloer: marmoleum</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>103 m²</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 3</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>Pantry's, keuken 0.64, wasruimte</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="37" t="inlineStr">
+        <is>
+          <t>Vloer: tegels</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>76 m²</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 3</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>Incl. bestaande toilettegels (blijven)</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>Vloer: terrazzo (behouden)</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>32 m²</t>
+        </is>
+      </c>
+      <c r="C28" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 3</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>Gangen 0.26 en 0.61</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>Glazen puien hergebruik + folie</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>ca. 90 m²</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 4</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="inlineStr">
+        <is>
+          <t>0.44/0.45, 0.62/0.63 (halzijde), 0.64</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="inlineStr">
+        <is>
           <t>Laag</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>Douches in 0.37/0.42</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>8 (waarvan 2 van 2,3 m²)</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 1</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="inlineStr">
+        <is>
+          <t>0.38–0.46; mogelijk 2 MIVA-douches (componentenboek nr. 10)</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
         </is>
       </c>
     </row>

--- a/calculatie/Thebe22_calculatiemodel_VDL.xlsx
+++ b/calculatie/Thebe22_calculatiemodel_VDL.xlsx
@@ -18,7 +18,7 @@
     <sheet name="Tellingen" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Begroting'!$A$1:$K$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -697,7 +697,7 @@
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Versie 4 (30-09-2026): bouwkundige Bijlagen 1 t/m 4 verwerkt (vloeroppervlakken, brandscheidingen, extra scope verdiepingen en terrein). Versie 3: antwoorden NvI en componentenboek verwerkt (tabbladen NvI en Componentenboek). Versie 2: installatie-aantallen zijn geteld op de tekeningen E.001, L.0.01-A/B, D.0.01-A/B, T.0.01, T.0.02, R.0.01 en R.-1.01 (zie tabblad 'Tellingen'). De Nota van Inlichtingen van 21-09-2026 is verwerkt (zie tabblad 'NvI'). De bouwkundige tekeningen (BBN bijlage 1 t/m 4) ontbreken nog: wandlengtes en vloeroppervlakken zijn afgeleid uit het stramien van 7,2 m. Tel alles na op DWG.</t>
+          <t>Versie 5: Bijlage 5 (Trigion), Bijlage 6 (afzuigkappen) en tekeningen toegangscontrole verwerkt. Versie 4 (30-09-2026): bouwkundige Bijlagen 1 t/m 4 verwerkt (vloeroppervlakken, brandscheidingen, extra scope verdiepingen en terrein). Versie 3: antwoorden NvI en componentenboek verwerkt (tabbladen NvI en Componentenboek). Versie 2: installatie-aantallen zijn geteld op de tekeningen E.001, L.0.01-A/B, D.0.01-A/B, T.0.01, T.0.02, R.0.01 en R.-1.01 (zie tabblad 'Tellingen'). De Nota van Inlichtingen van 21-09-2026 is verwerkt (zie tabblad 'NvI'). De bouwkundige tekeningen (BBN bijlage 1 t/m 4) ontbreken nog: wandlengtes en vloeroppervlakken zijn afgeleid uit het stramien van 7,2 m. Tel alles na op DWG.</t>
         </is>
       </c>
     </row>
@@ -850,11 +850,11 @@
       </c>
       <c r="C5" s="11" t="n"/>
       <c r="D5" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,13)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,13)</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,13)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,13)</f>
         <v/>
       </c>
       <c r="F5" s="13">
@@ -879,11 +879,11 @@
       </c>
       <c r="C6" s="11" t="n"/>
       <c r="D6" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,14)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,14)</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,14)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,14)</f>
         <v/>
       </c>
       <c r="F6" s="13">
@@ -908,11 +908,11 @@
       </c>
       <c r="C7" s="11" t="n"/>
       <c r="D7" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,15)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,15)</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,15)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,15)</f>
         <v/>
       </c>
       <c r="F7" s="13">
@@ -937,11 +937,11 @@
       </c>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,16)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,16)</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,16)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,16)</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -966,11 +966,11 @@
       </c>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,17)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,17)</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,17)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,17)</f>
         <v/>
       </c>
       <c r="F9" s="13">
@@ -995,11 +995,11 @@
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,18)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,18)</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,18)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,18)</f>
         <v/>
       </c>
       <c r="F10" s="13">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,19)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,19)</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,19)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,19)</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1053,11 +1053,11 @@
       </c>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,20)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,20)</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,20)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,20)</f>
         <v/>
       </c>
       <c r="F12" s="13">
@@ -1082,11 +1082,11 @@
       </c>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,21)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,21)</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,21)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,21)</f>
         <v/>
       </c>
       <c r="F13" s="13">
@@ -1127,11 +1127,11 @@
       </c>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,23)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,23)</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,23)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,23)</f>
         <v/>
       </c>
       <c r="F15" s="13">
@@ -1156,11 +1156,11 @@
       </c>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,24)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,24)</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,24)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,24)</f>
         <v/>
       </c>
       <c r="F16" s="13">
@@ -1185,11 +1185,11 @@
       </c>
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,25)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,25)</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,25)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,25)</f>
         <v/>
       </c>
       <c r="F17" s="13">
@@ -1214,11 +1214,11 @@
       </c>
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,26)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,26)</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,26)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,26)</f>
         <v/>
       </c>
       <c r="F18" s="13">
@@ -1243,11 +1243,11 @@
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,27)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,27)</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,27)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,27)</f>
         <v/>
       </c>
       <c r="F19" s="13">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,28)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,28)</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,28)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,28)</f>
         <v/>
       </c>
       <c r="F20" s="13">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,29)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,29)</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,29)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,29)</f>
         <v/>
       </c>
       <c r="F21" s="13">
@@ -1330,11 +1330,11 @@
       </c>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,30)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,30)</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,30)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,30)</f>
         <v/>
       </c>
       <c r="F22" s="13">
@@ -1359,11 +1359,11 @@
       </c>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,31)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,31)</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,31)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,31)</f>
         <v/>
       </c>
       <c r="F23" s="13">
@@ -1388,11 +1388,11 @@
       </c>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,32)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,32)</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,32)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,32)</f>
         <v/>
       </c>
       <c r="F24" s="13">
@@ -1418,11 +1418,11 @@
       </c>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,33)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,33)</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,33)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,33)</f>
         <v/>
       </c>
       <c r="F25" s="13">
@@ -1447,11 +1447,11 @@
       </c>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,34)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,34)</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,34)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,34)</f>
         <v/>
       </c>
       <c r="F26" s="13">
@@ -1492,11 +1492,11 @@
       </c>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,36)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,36)</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,36)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,36)</f>
         <v/>
       </c>
       <c r="F28" s="13">
@@ -1521,11 +1521,11 @@
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,37)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,37)</f>
         <v/>
       </c>
       <c r="E29" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,37)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,37)</f>
         <v/>
       </c>
       <c r="F29" s="13">
@@ -1550,11 +1550,11 @@
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="12">
-        <f>SUMIFS(Begroting!$H$2:$H$111,Begroting!$A$2:$A$111,38)</f>
+        <f>SUMIFS(Begroting!$H$2:$H$114,Begroting!$A$2:$A$114,38)</f>
         <v/>
       </c>
       <c r="E30" s="12">
-        <f>SUMIFS(Risicos!$I$2:$I$17,Risicos!$H$2:$H$17,38)</f>
+        <f>SUMIFS(Risicos!$I$2:$I$20,Risicos!$H$2:$H$20,38)</f>
         <v/>
       </c>
       <c r="F30" s="13">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="F44" s="21">
-        <f>Risicos!I19/F35</f>
+        <f>Risicos!I22/F35</f>
         <v/>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Recirculatie-afzuigkap Quattro Correto CW4090 + plasmafilter (4 st keuken 0.24, 4 st keuken 0.64)</t>
+          <t>Levering afzuigkap Quattro Corretto CW4090 + plasmafilter PlasGlAiry PGA 106 UM (Techno Horeca OV260801)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.4.6/8.4.7</t>
+          <t>E&amp;W 8.4.6/8.4.7 + Bijlage 6</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -3075,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="G27" s="25" t="n">
-        <v>4600</v>
+        <v>1774.08</v>
       </c>
       <c r="H27" s="26">
         <f>F27*G27</f>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>Techno Horeca / OA</t>
+          <t>Techno Horeca</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="K27" s="23" t="inlineStr">
         <is>
-          <t>Offerte Techno Horeca is bijgevoegd – bedrag overnemen. E.001 toont 7 AK-aansluitpunten, E&amp;W 8 kappen; BBN 3.7.2 noemt wasemschouw + wandkappen</t>
+          <t>Offerte: 4 st kap + filter = € 7.096,31 excl. BTW (15% korting), af magazijn. E&amp;W vraagt 4 per keuken = 8; E.001 toont 7 AK-punten. Offerte verlopen 15-05-2026: opnieuw aanvragen</t>
         </is>
       </c>
     </row>
@@ -3108,24 +3108,24 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>Luchtzijdig inregelen gehele BG + één gecombineerd meetrapport (Delta-P)</t>
+          <t>Montage afzuigkappen incl. telescopische ophanging, aansluiten, drukreferentieschakeling instellen</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 8.6</t>
+          <t>E&amp;W 8.4.6/8.4.7</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F28" s="24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>5000</v>
+        <v>450</v>
       </c>
       <c r="H28" s="26">
         <f>F28*G28</f>
@@ -3133,45 +3133,49 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>Delta-P (voorgeschreven)</t>
+          <t>OA W-installateur</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr"/>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>Offerte is excl. montage (af magazijn)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Verlichtingsinstallatie</t>
+          <t>Luchtbehandelingskast / ventilatie-installatie, incl. kanaalwerk</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>Verlichtingsarmaturen LED (downlights, inleg 600x600, plafonnière + hanglamp kamers) incl. aansluiting</t>
+          <t>Luchtzijdig inregelen gehele BG + één gecombineerd meetrapport (Delta-P)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.9</t>
+          <t>E&amp;W 8.6</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F29" s="24" t="n">
-        <v>215</v>
+        <v>1</v>
       </c>
       <c r="G29" s="25" t="n">
-        <v>210</v>
+        <v>5000</v>
       </c>
       <c r="H29" s="26">
         <f>F29*G29</f>
@@ -3179,19 +3183,15 @@
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>Delta-P (voorgeschreven)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>E.001: A1 60x60 (92), E1/E2 downlights (36), F (8), W (9), H hanglamp (1 per kamer); typische kamers doorgerekend naar 29</t>
-        </is>
-      </c>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="23" t="n">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>Noodverlichting en vluchtwegsignalering decentraal (autonoom)</t>
+          <t>Verlichtingsarmaturen LED (downlights, inleg 600x600, plafonnière + hanglamp kamers) incl. aansluiting</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.10 + E.001</t>
+          <t>E&amp;W 10.9</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="F30" s="24" t="n">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="G30" s="25" t="n">
-        <v>265</v>
+        <v>210</v>
       </c>
       <c r="H30" s="26">
         <f>F30*G30</f>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>E.001: 11 NV/NV1-punten getekend + pictogrammen; aantal volgt uit projectering NEN 1838</t>
+          <t>E.001: A1 60x60 (92), E1/E2 downlights (36), F (8), W (9), H hanglamp (1 per kamer); typische kamers doorgerekend naar 29</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Aanwezigheidsdetectie / DALI-dimmers / nachtbedrijf gangen en sanitair</t>
+          <t>Noodverlichting en vluchtwegsignalering decentraal (autonoom)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.11</t>
+          <t>E&amp;W 10.10 + E.001</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -3271,7 +3271,7 @@
         <v>25</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>160</v>
+        <v>265</v>
       </c>
       <c r="H31" s="26">
         <f>F31*G31</f>
@@ -3287,25 +3287,29 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K31" s="23" t="inlineStr"/>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>E.001: 11 NV/NV1-punten getekend + pictogrammen; aantal volgt uit projectering NEN 1838</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Centrale elektrotechnische voorzieningen</t>
+          <t>Verlichtingsinstallatie</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>Nieuwe verdeelinrichting keuken (LKK) incl. voedingskabel vanuit HSVI parkeergarage</t>
+          <t>Aanwezigheidsdetectie / DALI-dimmers / nachtbedrijf gangen en sanitair</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.6</t>
+          <t>E&amp;W 10.11</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
@@ -3314,10 +3318,10 @@
         </is>
       </c>
       <c r="F32" s="24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>9500</v>
+        <v>160</v>
       </c>
       <c r="H32" s="26">
         <f>F32*G32</f>
@@ -3333,11 +3337,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>Kabellengte parkeergarage → keuken bepalen</t>
-        </is>
-      </c>
+      <c r="K32" s="23" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="23" t="n">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen LK0-1 en LK0-2 (groepen, 20% reserve) incl. overspanningsbeveiliging + signaleringslamp</t>
+          <t>Nieuwe verdeelinrichting keuken (LKK) incl. voedingskabel vanuit HSVI parkeergarage</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.6.1/10.8</t>
+          <t>E&amp;W 10.6</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="F33" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="25" t="n">
-        <v>3800</v>
+        <v>9500</v>
       </c>
       <c r="H33" s="26">
         <f>F33*G33</f>
@@ -3383,7 +3383,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K33" s="23" t="inlineStr"/>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>Kabellengte parkeergarage → keuken bepalen</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="n">
@@ -3396,12 +3400,12 @@
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>Wandcontactdozen / aansluitpunten incl. leidingwerk in buis</t>
+          <t>Aanpassen LK0-1 en LK0-2 (groepen, 20% reserve) incl. overspanningsbeveiliging + signaleringslamp</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.7</t>
+          <t>E&amp;W 10.6.1/10.8</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -3410,10 +3414,10 @@
         </is>
       </c>
       <c r="F34" s="24" t="n">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="G34" s="25" t="n">
-        <v>135</v>
+        <v>3800</v>
       </c>
       <c r="H34" s="26">
         <f>F34*G34</f>
@@ -3429,11 +3433,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>E.001: KK per kamer + keukens (~32), 3O per kamer (29), Alg. (14), WM (4), DR (3), overig. Let op: punten die niet op tekening staan, horen er ook bij (10.7)</t>
-        </is>
-      </c>
+      <c r="K34" s="23" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="23" t="n">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>Krachtaansluitingen inductiekookplaten (6 st) en afzuigkappen</t>
+          <t>Wandcontactdozen / aansluitpunten incl. leidingwerk in buis</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.7.6</t>
+          <t>E&amp;W 10.7</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F35" s="24" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="G35" s="25" t="n">
-        <v>420</v>
+        <v>135</v>
       </c>
       <c r="H35" s="26">
         <f>F35*G35</f>
@@ -3479,7 +3479,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K35" s="23" t="inlineStr"/>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>E.001: KK per kamer + keukens (~32), 3O per kamer (29), Alg. (14), WM (4), DR (3), overig. Let op: punten die niet op tekening staan, horen er ook bij (10.7)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n">
@@ -3492,12 +3496,12 @@
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>Voedingen ventilatorconvectoren, brandkleppen, M-Check, boxventilator</t>
+          <t>Krachtaansluitingen inductiekookplaten (6 st) en afzuigkappen</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 9.2.1/9.4.1</t>
+          <t>E&amp;W 10.7.6</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
@@ -3506,10 +3510,10 @@
         </is>
       </c>
       <c r="F36" s="24" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G36" s="25" t="n">
-        <v>175</v>
+        <v>420</v>
       </c>
       <c r="H36" s="26">
         <f>F36*G36</f>
@@ -3538,24 +3542,24 @@
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>Aarding en potentiaalvereffening (incl. natte ruimten)</t>
+          <t>Voedingen ventilatorconvectoren, brandkleppen, M-Check, boxventilator</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.4</t>
+          <t>E&amp;W 9.2.1/9.4.1</t>
         </is>
       </c>
       <c r="E37" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F37" s="24" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G37" s="25" t="n">
-        <v>3200</v>
+        <v>175</v>
       </c>
       <c r="H37" s="26">
         <f>F37*G37</f>
@@ -3584,24 +3588,24 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Kabelgoten / kanalisatie + 35 m nieuw wandgootdeksel</t>
+          <t>230V-aansluitpunten binnen 1 m van Trigion-apparatuur (29 voedingen, 5 switches) in techniekruimten 0.27a en 0.59a</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.5</t>
+          <t>Bijlage 5 (Trigion)</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F38" s="24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G38" s="25" t="n">
-        <v>6200</v>
+        <v>260</v>
       </c>
       <c r="H38" s="26">
         <f>F38*G38</f>
@@ -3617,7 +3621,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K38" s="23" t="inlineStr"/>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>Uitgesloten in Trigion-offerte</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="23" t="n">
@@ -3630,12 +3638,12 @@
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>NEN 3140 / NEN 1010 metingen en rapportage</t>
+          <t>Aarding en potentiaalvereffening (incl. natte ruimten)</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.9.3</t>
+          <t>E&amp;W 10.4</t>
         </is>
       </c>
       <c r="E39" s="23" t="inlineStr">
@@ -3647,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="25" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="H39" s="26">
         <f>F39*G39</f>
@@ -3667,21 +3675,21 @@
     </row>
     <row r="40">
       <c r="A40" s="23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen regeltechniek</t>
+          <t>Centrale elektrotechnische voorzieningen</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>Demonteren vervallen I/O-punten, GBS-datapunten en bekabeling, opschonen regelkasten (Priva ongewijzigd)</t>
+          <t>Kabelgoten / kanalisatie + 35 m nieuw wandgootdeksel</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 5.9</t>
+          <t>E&amp;W 10.5</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
@@ -3693,7 +3701,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="25" t="n">
-        <v>3500</v>
+        <v>6200</v>
       </c>
       <c r="H40" s="26">
         <f>F40*G40</f>
@@ -3701,7 +3709,7 @@
       </c>
       <c r="I40" s="23" t="inlineStr">
         <is>
-          <t>OA W/regeltechniek</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
@@ -3709,29 +3717,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>Geen nul-prijs: deze post heeft wel inhoud</t>
-        </is>
-      </c>
+      <c r="K40" s="23" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen regeltechniek</t>
+          <t>Centrale elektrotechnische voorzieningen</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>Regeltechnische documentatie (processchema's, I/O-lijsten) + instructie ≥2 uur</t>
+          <t>NEN 3140 / NEN 1010 metingen en rapportage</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 9.5</t>
+          <t>E&amp;W 3.9.3</t>
         </is>
       </c>
       <c r="E41" s="23" t="inlineStr">
@@ -3743,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="25" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="H41" s="26">
         <f>F41*G41</f>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="I41" s="23" t="inlineStr">
         <is>
-          <t>OA W/regeltechniek</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J41" s="23" t="inlineStr">
@@ -3763,33 +3767,33 @@
     </row>
     <row r="42">
       <c r="A42" s="23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Communicatievoorzieningen</t>
+          <t>Aanpassen regeltechniek</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Data-aansluiting CAT6a LSZH incl. outlet en bekabeling</t>
+          <t>Demonteren vervallen I/O-punten, GBS-datapunten en bekabeling, opschonen regelkasten (Priva ongewijzigd)</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2 + E.001</t>
+          <t>E&amp;W 5.9</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F42" s="24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G42" s="25" t="n">
-        <v>195</v>
+        <v>3500</v>
       </c>
       <c r="H42" s="26">
         <f>F42*G42</f>
@@ -3797,7 +3801,7 @@
       </c>
       <c r="I42" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>OA W/regeltechniek</t>
         </is>
       </c>
       <c r="J42" s="23" t="inlineStr">
@@ -3807,39 +3811,39 @@
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>E.001: 8 D-punten (kantoor, gespreksruimten, beveiliging)</t>
+          <t>Geen nul-prijs: deze post heeft wel inhoud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Communicatievoorzieningen</t>
+          <t>Aanpassen regeltechniek</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>WLAN access point-aansluiting 2-voudig met PoE</t>
+          <t>Regeltechnische documentatie (processchema's, I/O-lijsten) + instructie ≥2 uur</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2 + E.001</t>
+          <t>E&amp;W 9.5</t>
         </is>
       </c>
       <c r="E43" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F43" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G43" s="25" t="n">
-        <v>320</v>
+        <v>1800</v>
       </c>
       <c r="H43" s="26">
         <f>F43*G43</f>
@@ -3847,7 +3851,7 @@
       </c>
       <c r="I43" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>OA W/regeltechniek</t>
         </is>
       </c>
       <c r="J43" s="23" t="inlineStr">
@@ -3855,11 +3859,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K43" s="23" t="inlineStr">
-        <is>
-          <t>E.001: 12 Wi-Fi-punten</t>
-        </is>
-      </c>
+      <c r="K43" s="23" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
@@ -3872,24 +3872,24 @@
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>Patchpanelen/rangeerpanelen in bestaand 19"-rack + aansluit- en patchsnoeren (75%)</t>
+          <t>Data-aansluiting CAT6a LSZH incl. outlet en bekabeling</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2.1</t>
+          <t>E&amp;W 11.2 + E.001</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F44" s="24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G44" s="25" t="n">
-        <v>2800</v>
+        <v>195</v>
       </c>
       <c r="H44" s="26">
         <f>F44*G44</f>
@@ -3905,7 +3905,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K44" s="23" t="inlineStr"/>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>E.001: 8 D-punten (kantoor, gespreksruimten, beveiliging)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="23" t="n">
@@ -3918,24 +3922,24 @@
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>Bekabeling camera's en toegangscontrole volgens opgave Trigion</t>
+          <t>WLAN access point-aansluiting 2-voudig met PoE</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 11.2 / bijlage 13</t>
+          <t>E&amp;W 11.2 + E.001</t>
         </is>
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F45" s="24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G45" s="25" t="n">
-        <v>4500</v>
+        <v>320</v>
       </c>
       <c r="H45" s="26">
         <f>F45*G45</f>
@@ -3948,44 +3952,44 @@
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>Opgave Trigion (bijlage) uitrekenen</t>
+          <t>E.001: 12 Wi-Fi-punten</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Toegangscontrole en beveiliging</t>
+          <t>Communicatievoorzieningen</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>Rookmelders met NEN 2555-functionaliteit in bewonerskamers incl. sturingen</t>
+          <t>Patchpanelen/rangeerpanelen in bestaand 19"-rack + aansluit- en patchsnoeren (75%)</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.3</t>
+          <t>E&amp;W 11.2.1</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F46" s="24" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>290</v>
+        <v>2800</v>
       </c>
       <c r="H46" s="26">
         <f>F46*G46</f>
@@ -3993,33 +3997,33 @@
       </c>
       <c r="I46" s="23" t="inlineStr">
         <is>
-          <t>Erkend branddetectiebedrijf</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>Toegangscontrole en beveiliging</t>
+          <t>Communicatievoorzieningen</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Automatische melders verkeers-, gezamenlijke en risicoruimten</t>
+          <t>Bekabeling toegangscontrole per kamerdeur: lezer-, slot- en deurcontactkabel (3×, gem. 35 m) naar deurcontroller in techniekruimte 0.27a/0.59a, incl. kabelovergang kozijn, labeling en 2 m overlengte</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.3 + E.001</t>
+          <t>Bijlage 5 (Trigion) + tekeningen toegangscontrole</t>
         </is>
       </c>
       <c r="E47" s="23" t="inlineStr">
@@ -4028,10 +4032,10 @@
         </is>
       </c>
       <c r="F47" s="24" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G47" s="25" t="n">
-        <v>230</v>
+        <v>520</v>
       </c>
       <c r="H47" s="26">
         <f>F47*G47</f>
@@ -4039,33 +4043,37 @@
       </c>
       <c r="I47" s="23" t="inlineStr">
         <is>
-          <t>Erkend branddetectiebedrijf</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="inlineStr"/>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>Trigion levert/monteert alleen apparatuur; bekabeling, leidingwegen en doorvoeringen zijn uitgesloten (was: SPIE). 17 deuren naar techniek zuid, 12 naar techniek noord</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Toegangscontrole en beveiliging</t>
+          <t>Communicatievoorzieningen</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>Handbrandmelders (4) + slow-whoops / sirenesokkels klasse B (ca. 35)</t>
+          <t>Bekabeling camera's CAT6a (7 binnen, 3 buiten) naar PoE-switches in techniekruimten, incl. geveldoorvoer buitencamera's</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.6/12.3 + E.001</t>
+          <t>Bijlage 5 (Trigion)</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
@@ -4074,10 +4082,10 @@
         </is>
       </c>
       <c r="F48" s="24" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G48" s="25" t="n">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="H48" s="26">
         <f>F48*G48</f>
@@ -4085,17 +4093,17 @@
       </c>
       <c r="I48" s="23" t="inlineStr">
         <is>
-          <t>Erkend branddetectiebedrijf</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>E.001: HBM 4, SW/R-SW/MS-SW-combinaties ca. 35 na doorrekenen typische kamers. Extra signaalgevers niet verrekenbaar</t>
+          <t>Camera's zelf door Trigion</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4118,7 @@
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>Uitbreiding BMC/lus-capaciteit + aanpassen OAI-zonering</t>
+          <t>Rookmelders met NEN 2555-functionaliteit in bewonerskamers incl. sturingen</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
@@ -4120,14 +4128,14 @@
       </c>
       <c r="E49" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F49" s="24" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G49" s="25" t="n">
-        <v>4500</v>
+        <v>290</v>
       </c>
       <c r="H49" s="26">
         <f>F49*G49</f>
@@ -4143,11 +4151,7 @@
           <t>Offerte aanvragen</t>
         </is>
       </c>
-      <c r="K49" s="23" t="inlineStr">
-        <is>
-          <t>Capaciteit bestaande BMC onbekend – zie risico's</t>
-        </is>
-      </c>
+      <c r="K49" s="23" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="23" t="n">
@@ -4160,24 +4164,24 @@
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>PvE/Nota van Aanvulling BMI/OAI + goedkeuring brandweer, projectering</t>
+          <t>Automatische melders verkeers-, gezamenlijke en risicoruimten</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.1</t>
+          <t>E&amp;W 12.2.3 + E.001</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F50" s="24" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G50" s="25" t="n">
-        <v>3500</v>
+        <v>230</v>
       </c>
       <c r="H50" s="26">
         <f>F50*G50</f>
@@ -4206,24 +4210,24 @@
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>Inbedrijfstelling, rapport van oplevering, inspectie erkende instelling, eerste certificaat</t>
+          <t>Handbrandmelders (4) + slow-whoops / sirenesokkels klasse B (ca. 35)</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.1/12.2.2</t>
+          <t>E&amp;W 12.2.6/12.3 + E.001</t>
         </is>
       </c>
       <c r="E51" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F51" s="24" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G51" s="25" t="n">
-        <v>4800</v>
+        <v>245</v>
       </c>
       <c r="H51" s="26">
         <f>F51*G51</f>
@@ -4239,7 +4243,11 @@
           <t>Offerte aanvragen</t>
         </is>
       </c>
-      <c r="K51" s="23" t="inlineStr"/>
+      <c r="K51" s="23" t="inlineStr">
+        <is>
+          <t>E.001: HBM 4, SW/R-SW/MS-SW-combinaties ca. 35 na doorrekenen typische kamers. Extra signaalgevers niet verrekenbaar</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="23" t="n">
@@ -4252,12 +4260,12 @@
       </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
-          <t>GTV-voedingen en aansturing brandkleppen + deurvastzetters/vrijloopdrangers</t>
+          <t>Uitbreiding BMC/lus-capaciteit + aanpassen OAI-zonering</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.2.4</t>
+          <t>E&amp;W 12.2.3</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
@@ -4282,12 +4290,12 @@
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K52" s="23" t="inlineStr">
         <is>
-          <t>Demarcatie onduidelijk (8.4.2 'door derden' vs 12.2.4 'aannemer') – hier meegeprijsd</t>
+          <t>Capaciteit bestaande BMC onbekend – zie risico's</t>
         </is>
       </c>
     </row>
@@ -4302,24 +4310,24 @@
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>Alarmsignalering mindervalidentoilet</t>
+          <t>PvE/Nota van Aanvulling BMI/OAI + goedkeuring brandweer, projectering</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.5</t>
+          <t>E&amp;W 12.2.1</t>
         </is>
       </c>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F53" s="24" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="25" t="n">
-        <v>850</v>
+        <v>3500</v>
       </c>
       <c r="H53" s="26">
         <f>F53*G53</f>
@@ -4327,12 +4335,12 @@
       </c>
       <c r="I53" s="23" t="inlineStr">
         <is>
-          <t>OA E-installateur</t>
+          <t>Erkend branddetectiebedrijf</t>
         </is>
       </c>
       <c r="J53" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K53" s="23" t="inlineStr"/>
@@ -4348,12 +4356,12 @@
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>Stelpost toegangscontrole tussendeur 'time-out' (Salto-tag)</t>
+          <t>Inbedrijfstelling, rapport van oplevering, inspectie erkende instelling, eerste certificaat</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 12.4</t>
+          <t>E&amp;W 12.2.1/12.2.2</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
@@ -4364,8 +4372,8 @@
       <c r="F54" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="27" t="n">
-        <v>2000</v>
+      <c r="G54" s="25" t="n">
+        <v>4800</v>
       </c>
       <c r="H54" s="26">
         <f>F54*G54</f>
@@ -4373,37 +4381,33 @@
       </c>
       <c r="I54" s="23" t="inlineStr">
         <is>
-          <t>Stelpost</t>
+          <t>Erkend branddetectiebedrijf</t>
         </is>
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>Stelpost (voorgeschreven)</t>
-        </is>
-      </c>
-      <c r="K54" s="23" t="inlineStr">
-        <is>
-          <t>Voorgeschreven verrekenbare stelpost</t>
-        </is>
-      </c>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (installaties)</t>
+          <t>Toegangscontrole en beveiliging</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
-          <t>Stelpost tijdelijke voorzieningen t.b.v. bedrijfsvoering tijdens werkzaamheden</t>
+          <t>GTV-voedingen en aansturing brandkleppen + deurvastzetters/vrijloopdrangers</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 5.1</t>
+          <t>E&amp;W 12.2.4</t>
         </is>
       </c>
       <c r="E55" s="23" t="inlineStr">
@@ -4414,8 +4418,8 @@
       <c r="F55" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="27" t="n">
-        <v>10000</v>
+      <c r="G55" s="25" t="n">
+        <v>4500</v>
       </c>
       <c r="H55" s="26">
         <f>F55*G55</f>
@@ -4423,49 +4427,49 @@
       </c>
       <c r="I55" s="23" t="inlineStr">
         <is>
-          <t>Stelpost</t>
+          <t>Erkend branddetectiebedrijf</t>
         </is>
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>Stelpost (voorgeschreven)</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K55" s="23" t="inlineStr">
         <is>
-          <t>Voorgeschreven verrekenbare stelpost</t>
+          <t>Demarcatie onduidelijk (8.4.2 'door derden' vs 12.2.4 'aannemer') – hier meegeprijsd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (installaties)</t>
+          <t>Toegangscontrole en beveiliging</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>Horizontaal/verticaal transport installatiedelen + hulpmiddelen</t>
+          <t>Alarmsignalering mindervalidentoilet</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.10</t>
+          <t>E&amp;W 12.5</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F56" s="24" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="25" t="n">
-        <v>2000</v>
+        <v>850</v>
       </c>
       <c r="H56" s="26">
         <f>F56*G56</f>
@@ -4473,7 +4477,7 @@
       </c>
       <c r="I56" s="23" t="inlineStr">
         <is>
-          <t>OA installateurs</t>
+          <t>OA E-installateur</t>
         </is>
       </c>
       <c r="J56" s="23" t="inlineStr">
@@ -4485,21 +4489,21 @@
     </row>
     <row r="57">
       <c r="A57" s="23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
+          <t>Toegangscontrole en beveiliging</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
-          <t>Opname kozijnen en ruiten, vaststellen scope</t>
+          <t>Stelpost toegangscontrole tussendeur 'time-out' (Salto-tag)</t>
         </is>
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.3</t>
+          <t>E&amp;W 12.4</t>
         </is>
       </c>
       <c r="E57" s="23" t="inlineStr">
@@ -4510,8 +4514,8 @@
       <c r="F57" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G57" s="25" t="n">
-        <v>750</v>
+      <c r="G57" s="27" t="n">
+        <v>2000</v>
       </c>
       <c r="H57" s="26">
         <f>F57*G57</f>
@@ -4519,45 +4523,49 @@
       </c>
       <c r="I57" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>Stelpost</t>
         </is>
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K57" s="23" t="inlineStr"/>
+          <t>Stelpost (voorgeschreven)</t>
+        </is>
+      </c>
+      <c r="K57" s="23" t="inlineStr">
+        <is>
+          <t>Voorgeschreven verrekenbare stelpost</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
+          <t>Evt. andere bijkomende kosten (installaties)</t>
         </is>
       </c>
       <c r="C58" s="23" t="inlineStr">
         <is>
-          <t>Vervangen beschadigde ruiten ZHR++/HR++ (U≤1,1), zo nodig gelaagd/gehard, incl. glaslatten</t>
+          <t>Stelpost tijdelijke voorzieningen t.b.v. bedrijfsvoering tijdens werkzaamheden</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.3</t>
+          <t>E&amp;W 5.1</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F58" s="24" t="n">
-        <v>25</v>
-      </c>
-      <c r="G58" s="25" t="n">
-        <v>275</v>
+        <v>1</v>
+      </c>
+      <c r="G58" s="27" t="n">
+        <v>10000</v>
       </c>
       <c r="H58" s="26">
         <f>F58*G58</f>
@@ -4565,49 +4573,49 @@
       </c>
       <c r="I58" s="23" t="inlineStr">
         <is>
-          <t>OA glaszetter</t>
+          <t>Stelpost</t>
         </is>
       </c>
       <c r="J58" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Stelpost (voorgeschreven)</t>
         </is>
       </c>
       <c r="K58" s="23" t="inlineStr">
         <is>
-          <t>Hoeveelheid onbekend – schouw! Zie risico's</t>
+          <t>Voorgeschreven verrekenbare stelpost</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
+          <t>Evt. andere bijkomende kosten (installaties)</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>Privacyfolie ruiten sanitair blok (lichtdoorlatend, waterbestendig)</t>
+          <t>Horizontaal/verticaal transport installatiedelen + hulpmiddelen</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.2</t>
+          <t>E&amp;W 3.10</t>
         </is>
       </c>
       <c r="E59" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F59" s="24" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G59" s="25" t="n">
-        <v>75</v>
+        <v>2000</v>
       </c>
       <c r="H59" s="26">
         <f>F59*G59</f>
@@ -4615,7 +4623,7 @@
       </c>
       <c r="I59" s="23" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>OA installateurs</t>
         </is>
       </c>
       <c r="J59" s="23" t="inlineStr">
@@ -4636,24 +4644,24 @@
       </c>
       <c r="C60" s="23" t="inlineStr">
         <is>
-          <t>Doorgeefluik binnenzijde demonteren, sluiten, isoleren en afwerken</t>
+          <t>Opname kozijnen en ruiten, vaststellen scope</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.1.4</t>
+          <t>BBN 3.1.3</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F60" s="24" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="25" t="n">
-        <v>1250</v>
+        <v>750</v>
       </c>
       <c r="H60" s="26">
         <f>F60*G60</f>
@@ -4673,21 +4681,21 @@
     </row>
     <row r="61">
       <c r="A61" s="23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>Vervangen vloerafwerking en plinten</t>
+          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
         <is>
-          <t>Verwijderen bestaande vloerafwerking incl. lijmresten en egalisatie (excl. terrazzo gangen en toilettegels)</t>
+          <t>Vervangen beschadigde ruiten ZHR++/HR++ (U≤1,1), zo nodig gelaagd/gehard, incl. glaslatten</t>
         </is>
       </c>
       <c r="D61" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.1</t>
+          <t>BBN 3.1.3</t>
         </is>
       </c>
       <c r="E61" s="23" t="inlineStr">
@@ -4696,10 +4704,10 @@
         </is>
       </c>
       <c r="F61" s="24" t="n">
-        <v>1100</v>
+        <v>25</v>
       </c>
       <c r="G61" s="25" t="n">
-        <v>12</v>
+        <v>275</v>
       </c>
       <c r="H61" s="26">
         <f>F61*G61</f>
@@ -4707,7 +4715,7 @@
       </c>
       <c r="I61" s="23" t="inlineStr">
         <is>
-          <t>OA vloerenlegger</t>
+          <t>OA glaszetter</t>
         </is>
       </c>
       <c r="J61" s="23" t="inlineStr">
@@ -4717,27 +4725,27 @@
       </c>
       <c r="K61" s="23" t="inlineStr">
         <is>
-          <t>m² uitmeten op bijlage 3</t>
+          <t>Hoeveelheid onbekend – schouw! Zie risico's</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Vervangen vloerafwerking en plinten</t>
+          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
         </is>
       </c>
       <c r="C62" s="23" t="inlineStr">
         <is>
-          <t>Ondergrond herstellen en egaliseren</t>
+          <t>Privacyfolie ruiten sanitair blok (lichtdoorlatend, waterbestendig)</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.1</t>
+          <t>BBN 3.1.2</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
@@ -4746,10 +4754,10 @@
         </is>
       </c>
       <c r="F62" s="24" t="n">
-        <v>1100</v>
+        <v>20</v>
       </c>
       <c r="G62" s="25" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H62" s="26">
         <f>F62*G62</f>
@@ -4757,7 +4765,7 @@
       </c>
       <c r="I62" s="23" t="inlineStr">
         <is>
-          <t>OA vloerenlegger</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J62" s="23" t="inlineStr">
@@ -4765,41 +4773,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K62" s="23" t="inlineStr">
-        <is>
-          <t>Volledig aangenomen</t>
-        </is>
-      </c>
+      <c r="K62" s="23" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>Vervangen vloerafwerking en plinten</t>
+          <t>Vervangen kozijnen, ramen en gevelpanelen/-onderdelen</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
         <is>
-          <t>Naadloze marmoleum-achtige afwerking in alle ruimten (kamers, gangen, woonkamers, keukens)</t>
+          <t>Doorgeefluik binnenzijde demonteren, sluiten, isoleren en afwerken</t>
         </is>
       </c>
       <c r="D63" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.2/3.2.4 + NvI vraag 11/17 + Bijlage 3</t>
+          <t>BBN 3.1.4</t>
         </is>
       </c>
       <c r="E63" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F63" s="24" t="n">
-        <v>1042</v>
+        <v>1</v>
       </c>
       <c r="G63" s="25" t="n">
-        <v>44</v>
+        <v>1250</v>
       </c>
       <c r="H63" s="26">
         <f>F63*G63</f>
@@ -4807,7 +4811,7 @@
       </c>
       <c r="I63" s="23" t="inlineStr">
         <is>
-          <t>OA vloerenlegger</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J63" s="23" t="inlineStr">
@@ -4815,11 +4819,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K63" s="23" t="inlineStr">
-        <is>
-          <t>Gemeten op Bijlage 3: tapijt 939 m² (wordt marmoleum) + marmoleum 103 m². Hal 0.01 valt buiten scope; terrazzo 32 m² blijft</t>
-        </is>
-      </c>
+      <c r="K63" s="23" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="23" t="n">
@@ -4832,24 +4832,24 @@
       </c>
       <c r="C64" s="23" t="inlineStr">
         <is>
-          <t>Hardhouten plint 54x15 mm</t>
+          <t>Verwijderen bestaande vloerafwerking incl. lijmresten en egalisatie (excl. terrazzo gangen en toilettegels)</t>
         </is>
       </c>
       <c r="D64" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.2</t>
+          <t>BBN 3.2.1</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F64" s="24" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="G64" s="25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H64" s="26">
         <f>F64*G64</f>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="I64" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA vloerenlegger</t>
         </is>
       </c>
       <c r="J64" s="23" t="inlineStr">
@@ -4865,7 +4865,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K64" s="23" t="inlineStr"/>
+      <c r="K64" s="23" t="inlineStr">
+        <is>
+          <t>m² uitmeten op bijlage 3</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="n">
@@ -4878,7 +4882,7 @@
       </c>
       <c r="C65" s="23" t="inlineStr">
         <is>
-          <t>Overgangsprofielen en dorpels (natte ruimten, buitendeuren)</t>
+          <t>Ondergrond herstellen en egaliseren</t>
         </is>
       </c>
       <c r="D65" s="23" t="inlineStr">
@@ -4888,14 +4892,14 @@
       </c>
       <c r="E65" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F65" s="24" t="n">
-        <v>45</v>
+        <v>1100</v>
       </c>
       <c r="G65" s="25" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="H65" s="26">
         <f>F65*G65</f>
@@ -4903,7 +4907,7 @@
       </c>
       <c r="I65" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA vloerenlegger</t>
         </is>
       </c>
       <c r="J65" s="23" t="inlineStr">
@@ -4911,7 +4915,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K65" s="23" t="inlineStr"/>
+      <c r="K65" s="23" t="inlineStr">
+        <is>
+          <t>Volledig aangenomen</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="23" t="n">
@@ -4924,24 +4932,24 @@
       </c>
       <c r="C66" s="23" t="inlineStr">
         <is>
-          <t>Herstel en reinigen tegels toiletruimten</t>
+          <t>Naadloze marmoleum-achtige afwerking in alle ruimten (kamers, gangen, woonkamers, keukens)</t>
         </is>
       </c>
       <c r="D66" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.2.3</t>
+          <t>BBN 3.2.2/3.2.4 + NvI vraag 11/17 + Bijlage 3</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F66" s="24" t="n">
-        <v>1</v>
+        <v>1042</v>
       </c>
       <c r="G66" s="25" t="n">
-        <v>1200</v>
+        <v>44</v>
       </c>
       <c r="H66" s="26">
         <f>F66*G66</f>
@@ -4949,7 +4957,7 @@
       </c>
       <c r="I66" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA vloerenlegger</t>
         </is>
       </c>
       <c r="J66" s="23" t="inlineStr">
@@ -4957,37 +4965,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K66" s="23" t="inlineStr"/>
+      <c r="K66" s="23" t="inlineStr">
+        <is>
+          <t>Gemeten op Bijlage 3: tapijt 939 m² (wordt marmoleum) + marmoleum 103 m². Hal 0.01 valt buiten scope; terrazzo 32 m² blijft</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
+          <t>Vervangen vloerafwerking en plinten</t>
         </is>
       </c>
       <c r="C67" s="23" t="inlineStr">
         <is>
-          <t>Slopen niet-dragende binnenwanden + herstel aansluitvlakken</t>
+          <t>Hardhouten plint 54x15 mm</t>
         </is>
       </c>
       <c r="D67" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1</t>
+          <t>BBN 3.2.2</t>
         </is>
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F67" s="24" t="n">
-        <v>1</v>
+        <v>900</v>
       </c>
       <c r="G67" s="25" t="n">
-        <v>8500</v>
+        <v>14</v>
       </c>
       <c r="H67" s="26">
         <f>F67*G67</f>
@@ -5007,33 +5019,33 @@
     </row>
     <row r="68">
       <c r="A68" s="23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B68" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
+          <t>Vervangen vloerafwerking en plinten</t>
         </is>
       </c>
       <c r="C68" s="23" t="inlineStr">
         <is>
-          <t>Glaswanden zorgvuldig demonteren, labelen, beschermd opslaan in het gebouw voor hergebruik op locatie</t>
+          <t>Overgangsprofielen en dorpels (natte ruimten, buitendeuren)</t>
         </is>
       </c>
       <c r="D68" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.2 + NvI vraag 21</t>
+          <t>BBN 3.2.1</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F68" s="24" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G68" s="25" t="n">
-        <v>4500</v>
+        <v>65</v>
       </c>
       <c r="H68" s="26">
         <f>F68*G68</f>
@@ -5049,29 +5061,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K68" s="23" t="inlineStr">
-        <is>
-          <t>NvI vraag 21: alleen glazen wanden; opslag in overleg, mogelijk in het gebouw</t>
-        </is>
-      </c>
+      <c r="K68" s="23" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
+          <t>Vervangen vloerafwerking en plinten</t>
         </is>
       </c>
       <c r="C69" s="23" t="inlineStr">
         <is>
-          <t>Herstel aansluitingen vloer/wand/plafond na slopen binnenwanden (inschatting)</t>
+          <t>Herstel en reinigen tegels toiletruimten</t>
         </is>
       </c>
       <c r="D69" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 19</t>
+          <t>BBN 3.2.3</t>
         </is>
       </c>
       <c r="E69" s="23" t="inlineStr">
@@ -5083,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="25" t="n">
-        <v>3500</v>
+        <v>1200</v>
       </c>
       <c r="H69" s="26">
         <f>F69*G69</f>
@@ -5099,11 +5107,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K69" s="23" t="inlineStr">
-        <is>
-          <t>NvI vraag 19: inschatting door aannemer, meenemen in de posten</t>
-        </is>
-      </c>
+      <c r="K69" s="23" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="23" t="n">
@@ -5116,24 +5120,24 @@
       </c>
       <c r="C70" s="23" t="inlineStr">
         <is>
-          <t>Metal-stud wand EI30, dubbel beplaat, geïsoleerd, tot betondek, gelijmd op vloer (vloerverwarming)</t>
+          <t>Slopen niet-dragende binnenwanden + herstel aansluitvlakken</t>
         </is>
       </c>
       <c r="D70" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1/3.3.3 + NvI vraag 6 + Bijlage 4</t>
+          <t>BBN 3.3.1</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F70" s="24" t="n">
-        <v>1050</v>
+        <v>1</v>
       </c>
       <c r="G70" s="25" t="n">
-        <v>105</v>
+        <v>8500</v>
       </c>
       <c r="H70" s="26">
         <f>F70*G70</f>
@@ -5149,11 +5153,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K70" s="23" t="inlineStr">
-        <is>
-          <t>Gemeten op Bijlage 4: ca. 329 m1 scheiding 30 min WBDBO, waarvan ca. 320 m1 nieuwe wand × 3,3 m. Opbouw volgens Bijlage 4: 2× 12,5 mm gips beide zijden + minerale wol. Hoogte tot betondek nameten</t>
-        </is>
-      </c>
+      <c r="K70" s="23" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="23" t="n">
@@ -5166,24 +5166,24 @@
       </c>
       <c r="C71" s="23" t="inlineStr">
         <is>
-          <t>Toeslag verhoogde geluidsisolatie 47 dB kamers noord (0.49–0.56, 0.74–0.76)</t>
+          <t>Glaswanden zorgvuldig demonteren, labelen, beschermd opslaan in het gebouw voor hergebruik op locatie</t>
         </is>
       </c>
       <c r="D71" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.3</t>
+          <t>BBN 3.3.2 + NvI vraag 21</t>
         </is>
       </c>
       <c r="E71" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F71" s="24" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="G71" s="25" t="n">
-        <v>32</v>
+        <v>4500</v>
       </c>
       <c r="H71" s="26">
         <f>F71*G71</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="K71" s="23" t="inlineStr">
         <is>
-          <t>Ca. 48 m1 × 3,3 m</t>
+          <t>NvI vraag 21: alleen glazen wanden; opslag in overleg, mogelijk in het gebouw</t>
         </is>
       </c>
     </row>
@@ -5216,24 +5216,24 @@
       </c>
       <c r="C72" s="23" t="inlineStr">
         <is>
-          <t>Toeslag 59 dB: dubbele metal-stud frame wand 155–170 mm (kantoor/gespreksruimten 0.04, 0.05, 0.62, 0.63)</t>
+          <t>Herstel aansluitingen vloer/wand/plafond na slopen binnenwanden (inschatting)</t>
         </is>
       </c>
       <c r="D72" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.2 / NvI vraag 5</t>
+          <t>NvI vraag 19</t>
         </is>
       </c>
       <c r="E72" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F72" s="24" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G72" s="25" t="n">
-        <v>115</v>
+        <v>3500</v>
       </c>
       <c r="H72" s="26">
         <f>F72*G72</f>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="K72" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 5: alleen haalbaar met dubbele frames; DnT,A of Rw niet beantwoord. Ca. 18 m1 × 3,3 m</t>
+          <t>NvI vraag 19: inschatting door aannemer, meenemen in de posten</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="C73" s="23" t="inlineStr">
         <is>
-          <t>Scanbehang + sauswerk wanden (beide zijden)</t>
+          <t>Metal-stud wand EI30, dubbel beplaat, geïsoleerd, tot betondek, gelijmd op vloer (vloerverwarming)</t>
         </is>
       </c>
       <c r="D73" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1</t>
+          <t>BBN 3.3.1/3.3.3 + NvI vraag 6 + Bijlage 4</t>
         </is>
       </c>
       <c r="E73" s="23" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="F73" s="24" t="n">
-        <v>2100</v>
+        <v>1050</v>
       </c>
       <c r="G73" s="25" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="H73" s="26">
         <f>F73*G73</f>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="I73" s="23" t="inlineStr">
         <is>
-          <t>OA schilder</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J73" s="23" t="inlineStr">
@@ -5299,7 +5299,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K73" s="23" t="inlineStr"/>
+      <c r="K73" s="23" t="inlineStr">
+        <is>
+          <t>Gemeten op Bijlage 4: ca. 329 m1 scheiding 30 min WBDBO, waarvan ca. 320 m1 nieuwe wand × 3,3 m. Opbouw volgens Bijlage 4: 2× 12,5 mm gips beide zijden + minerale wol. Hoogte tot betondek nameten</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="23" t="n">
@@ -5312,24 +5316,24 @@
       </c>
       <c r="C74" s="23" t="inlineStr">
         <is>
-          <t>Deurstel EI30 akoestisch, 40-44 mm, insteekslot, elektrische sluitplaat (voorbereid op Trigion), vrijloopdranger</t>
+          <t>Toeslag verhoogde geluidsisolatie 47 dB kamers noord (0.49–0.56, 0.74–0.76)</t>
         </is>
       </c>
       <c r="D74" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.2 + E.001</t>
+          <t>BBN 3.3.3</t>
         </is>
       </c>
       <c r="E74" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F74" s="24" t="n">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="G74" s="25" t="n">
-        <v>2150</v>
+        <v>32</v>
       </c>
       <c r="H74" s="26">
         <f>F74*G74</f>
@@ -5337,17 +5341,17 @@
       </c>
       <c r="I74" s="23" t="inlineStr">
         <is>
-          <t>VDL / OA leverancier</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J74" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K74" s="23" t="inlineStr">
         <is>
-          <t>29 kamerdeuren + 6 overig. E.001 toont VLD per kamerdeur maar maar 2 ES + 3 kaartlezers: BBN (ES per deur) aangehouden als strengste eis. Levertijd kritisch</t>
+          <t>Ca. 48 m1 × 3,3 m</t>
         </is>
       </c>
     </row>
@@ -5362,24 +5366,24 @@
       </c>
       <c r="C75" s="23" t="inlineStr">
         <is>
-          <t>Overige binnendeurstellen (techniek, berging, gemeenschappelijk)</t>
+          <t>Toeslag 59 dB: dubbele metal-stud frame wand 155–170 mm (kantoor/gespreksruimten 0.04, 0.05, 0.62, 0.63)</t>
         </is>
       </c>
       <c r="D75" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1</t>
+          <t>BBN 3.3.2 / NvI vraag 5</t>
         </is>
       </c>
       <c r="E75" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F75" s="24" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="G75" s="25" t="n">
-        <v>1250</v>
+        <v>115</v>
       </c>
       <c r="H75" s="26">
         <f>F75*G75</f>
@@ -5395,7 +5399,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K75" s="23" t="inlineStr"/>
+      <c r="K75" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 5: alleen haalbaar met dubbele frames; DnT,A of Rw niet beantwoord. Ca. 18 m1 × 3,3 m</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="23" t="n">
@@ -5408,24 +5416,24 @@
       </c>
       <c r="C76" s="23" t="inlineStr">
         <is>
-          <t>Zelfsluitende deurstellen EI60 in 60-min compartimentsgrenzen</t>
+          <t>Scanbehang + sauswerk wanden (beide zijden)</t>
         </is>
       </c>
       <c r="D76" s="23" t="inlineStr">
         <is>
-          <t>Bijlage 4</t>
+          <t>BBN 3.3.1</t>
         </is>
       </c>
       <c r="E76" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F76" s="24" t="n">
-        <v>4</v>
+        <v>2100</v>
       </c>
       <c r="G76" s="25" t="n">
-        <v>2800</v>
+        <v>14</v>
       </c>
       <c r="H76" s="26">
         <f>F76*G76</f>
@@ -5433,7 +5441,7 @@
       </c>
       <c r="I76" s="23" t="inlineStr">
         <is>
-          <t>VDL / OA leverancier</t>
+          <t>OA schilder</t>
         </is>
       </c>
       <c r="J76" s="23" t="inlineStr">
@@ -5441,11 +5449,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K76" s="23" t="inlineStr">
-        <is>
-          <t>Aantal inschatten; Bijlage 4 toont ca. 96 m1 scheiding 60 min, grotendeels bestaand</t>
-        </is>
-      </c>
+      <c r="K76" s="23" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="23" t="n">
@@ -5458,24 +5462,24 @@
       </c>
       <c r="C77" s="23" t="inlineStr">
         <is>
-          <t>Aansluiten nieuwe wanden op bestaande 60-min scheidingen, controle en herstel</t>
+          <t>Deurstel EI30 akoestisch, 40-44 mm, insteekslot, elektrische sluitplaat (voorbereid op Trigion), vrijloopdranger</t>
         </is>
       </c>
       <c r="D77" s="23" t="inlineStr">
         <is>
-          <t>Bijlage 4 / BBN 4.1</t>
+          <t>BBN 3.4.2 + E.001</t>
         </is>
       </c>
       <c r="E77" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F77" s="24" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="G77" s="25" t="n">
-        <v>3500</v>
+        <v>2150</v>
       </c>
       <c r="H77" s="26">
         <f>F77*G77</f>
@@ -5483,15 +5487,19 @@
       </c>
       <c r="I77" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>VDL / OA leverancier</t>
         </is>
       </c>
       <c r="J77" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K77" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K77" s="23" t="inlineStr">
+        <is>
+          <t>29 kamerdeuren + 6 overig. Trigion-offerte bevestigt: 29 kamerdeuren met paslezer; beslag, insteeksloten en elektrische sluitplaten zijn bouwkundig (bij aannemer). E.001 (2 ES) is daarmee achterhaald. Levertijd kritisch</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="23" t="n">
@@ -5504,24 +5512,24 @@
       </c>
       <c r="C78" s="23" t="inlineStr">
         <is>
-          <t>Ondoorzichtige folie op hergebruikte glazen puien (0.44, 0.45, 0.62, 0.63, 0.64)</t>
+          <t>Overige binnendeurstellen (techniek, berging, gemeenschappelijk)</t>
         </is>
       </c>
       <c r="D78" s="23" t="inlineStr">
         <is>
-          <t>Bijlage 4</t>
+          <t>BBN 3.4.1</t>
         </is>
       </c>
       <c r="E78" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F78" s="24" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="G78" s="25" t="n">
-        <v>60</v>
+        <v>1250</v>
       </c>
       <c r="H78" s="26">
         <f>F78*G78</f>
@@ -5529,7 +5537,7 @@
       </c>
       <c r="I78" s="23" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J78" s="23" t="inlineStr">
@@ -5537,11 +5545,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K78" s="23" t="inlineStr">
-        <is>
-          <t>Bijlage 4: glazen puien hergebruiken en voorzien van ondoorzichtige folie</t>
-        </is>
-      </c>
+      <c r="K78" s="23" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="23" t="n">
@@ -5554,12 +5558,12 @@
       </c>
       <c r="C79" s="23" t="inlineStr">
         <is>
-          <t>Sluitplan / cilinders met moedersleutelsysteem, hang- en sluitwerk SKG2</t>
+          <t>Zelfsluitende deurstellen EI60 in 60-min compartimentsgrenzen</t>
         </is>
       </c>
       <c r="D79" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1 + NvI vraag 4</t>
+          <t>Bijlage 4</t>
         </is>
       </c>
       <c r="E79" s="23" t="inlineStr">
@@ -5568,10 +5572,10 @@
         </is>
       </c>
       <c r="F79" s="24" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="G79" s="25" t="n">
-        <v>150</v>
+        <v>2800</v>
       </c>
       <c r="H79" s="26">
         <f>F79*G79</f>
@@ -5579,7 +5583,7 @@
       </c>
       <c r="I79" s="23" t="inlineStr">
         <is>
-          <t>OA</t>
+          <t>VDL / OA leverancier</t>
         </is>
       </c>
       <c r="J79" s="23" t="inlineStr">
@@ -5589,7 +5593,7 @@
       </c>
       <c r="K79" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 4: nieuw hang- en sluitwerk SKG2; wanden hotelstandaard, geen extra inbraakwerendheid</t>
+          <t>Aantal inschatten; Bijlage 4 toont ca. 96 m1 scheiding 60 min, grotendeels bestaand</t>
         </is>
       </c>
     </row>
@@ -5604,24 +5608,24 @@
       </c>
       <c r="C80" s="23" t="inlineStr">
         <is>
-          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
+          <t>Aansluiten nieuwe wanden op bestaande 60-min scheidingen, controle en herstel</t>
         </is>
       </c>
       <c r="D80" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.1</t>
+          <t>Bijlage 4 / BBN 4.1</t>
         </is>
       </c>
       <c r="E80" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F80" s="24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G80" s="25" t="n">
-        <v>260</v>
+        <v>3500</v>
       </c>
       <c r="H80" s="26">
         <f>F80*G80</f>
@@ -5641,21 +5645,21 @@
     </row>
     <row r="81">
       <c r="A81" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>Vervangen plafondafwerking</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
         <is>
-          <t>Verwijderen bestaand plafond incl. constructie</t>
+          <t>Ondoorzichtige folie op hergebruikte glazen puien (0.44, 0.45, 0.62, 0.63, 0.64)</t>
         </is>
       </c>
       <c r="D81" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.5</t>
+          <t>Bijlage 4</t>
         </is>
       </c>
       <c r="E81" s="23" t="inlineStr">
@@ -5664,10 +5668,10 @@
         </is>
       </c>
       <c r="F81" s="24" t="n">
-        <v>1250</v>
+        <v>90</v>
       </c>
       <c r="G81" s="25" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="H81" s="26">
         <f>F81*G81</f>
@@ -5675,7 +5679,7 @@
       </c>
       <c r="I81" s="23" t="inlineStr">
         <is>
-          <t>OA plafondmonteur</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J81" s="23" t="inlineStr">
@@ -5683,37 +5687,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K81" s="23" t="inlineStr"/>
+      <c r="K81" s="23" t="inlineStr">
+        <is>
+          <t>Bijlage 4: glazen puien hergebruiken en voorzien van ondoorzichtige folie</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B82" s="23" t="inlineStr">
         <is>
-          <t>Vervangen plafondafwerking</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C82" s="23" t="inlineStr">
         <is>
-          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
+          <t>Sluitplan / cilinders met moedersleutelsysteem, hang- en sluitwerk SKG2</t>
         </is>
       </c>
       <c r="D82" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.5</t>
+          <t>BBN 3.4.1 + NvI vraag 4</t>
         </is>
       </c>
       <c r="E82" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F82" s="24" t="n">
-        <v>1200</v>
+        <v>45</v>
       </c>
       <c r="G82" s="25" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="H82" s="26">
         <f>F82*G82</f>
@@ -5721,7 +5729,7 @@
       </c>
       <c r="I82" s="23" t="inlineStr">
         <is>
-          <t>OA plafondmonteur</t>
+          <t>OA</t>
         </is>
       </c>
       <c r="J82" s="23" t="inlineStr">
@@ -5729,37 +5737,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K82" s="23" t="inlineStr"/>
+      <c r="K82" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 4: nieuw hang- en sluitwerk SKG2; wanden hotelstandaard, geen extra inbraakwerendheid</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B83" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen zonwering</t>
+          <t>Aanpassen binnenwanden, -kozijnen en deuren</t>
         </is>
       </c>
       <c r="C83" s="23" t="inlineStr">
         <is>
-          <t>Demonteren bestaande binnenzonwering</t>
+          <t>Kleefmagneten/openzetvoorzieningen verkeersdeuren (mechanisch deel)</t>
         </is>
       </c>
       <c r="D83" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.1</t>
+          <t>BBN 3.4.1</t>
         </is>
       </c>
       <c r="E83" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F83" s="24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G83" s="25" t="n">
-        <v>1500</v>
+        <v>260</v>
       </c>
       <c r="H83" s="26">
         <f>F83*G83</f>
@@ -5775,41 +5787,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K83" s="23" t="inlineStr">
-        <is>
-          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
-        </is>
-      </c>
+      <c r="K83" s="23" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B84" s="23" t="inlineStr">
         <is>
-          <t>Aanpassen zonwering</t>
+          <t>Vervangen plafondafwerking</t>
         </is>
       </c>
       <c r="C84" s="23" t="inlineStr">
         <is>
-          <t>Verduisterende gordijnen brandvertragend (hotelfunctie) incl. rails, gelijk aan verdiepingen</t>
+          <t>Verwijderen bestaand plafond incl. constructie</t>
         </is>
       </c>
       <c r="D84" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.1 + NvI vraag 7/26</t>
+          <t>BBN 3.5</t>
         </is>
       </c>
       <c r="E84" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F84" s="24" t="n">
-        <v>150</v>
+        <v>1250</v>
       </c>
       <c r="G84" s="25" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="H84" s="26">
         <f>F84*G84</f>
@@ -5817,7 +5825,7 @@
       </c>
       <c r="I84" s="23" t="inlineStr">
         <is>
-          <t>OA stoffeerder</t>
+          <t>OA plafondmonteur</t>
         </is>
       </c>
       <c r="J84" s="23" t="inlineStr">
@@ -5825,41 +5833,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K84" s="23" t="inlineStr">
-        <is>
-          <t>Raamlengtes uitmeten</t>
-        </is>
-      </c>
+      <c r="K84" s="23" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B85" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Vervangen plafondafwerking</t>
         </is>
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
+          <t>Nieuw systeemplafond 600x600 incl. inspectieluiken en aanpassingen armaturen/roosters</t>
         </is>
       </c>
       <c r="D85" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.5</t>
         </is>
       </c>
       <c r="E85" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F85" s="24" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="G85" s="25" t="n">
-        <v>780</v>
+        <v>42</v>
       </c>
       <c r="H85" s="26">
         <f>F85*G85</f>
@@ -5867,7 +5871,7 @@
       </c>
       <c r="I85" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>OA plafondmonteur</t>
         </is>
       </c>
       <c r="J85" s="23" t="inlineStr">
@@ -5879,33 +5883,33 @@
     </row>
     <row r="86">
       <c r="A86" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B86" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Aanpassen zonwering</t>
         </is>
       </c>
       <c r="C86" s="23" t="inlineStr">
         <is>
-          <t>Keukenblok eetruimte</t>
+          <t>Demonteren bestaande binnenzonwering</t>
         </is>
       </c>
       <c r="D86" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.7.1</t>
         </is>
       </c>
       <c r="E86" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F86" s="24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G86" s="25" t="n">
-        <v>780</v>
+        <v>1500</v>
       </c>
       <c r="H86" s="26">
         <f>F86*G86</f>
@@ -5913,7 +5917,7 @@
       </c>
       <c r="I86" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J86" s="23" t="inlineStr">
@@ -5921,37 +5925,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K86" s="23" t="inlineStr"/>
+      <c r="K86" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 4.1.3 zegt: pand heeft geen zonwering – navragen</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B87" s="23" t="inlineStr">
         <is>
-          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+          <t>Aanpassen zonwering</t>
         </is>
       </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
+          <t>Verduisterende gordijnen brandvertragend (hotelfunctie) incl. rails, gelijk aan verdiepingen</t>
         </is>
       </c>
       <c r="D87" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.2</t>
+          <t>BBN 3.7.1 + NvI vraag 7/26</t>
         </is>
       </c>
       <c r="E87" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F87" s="24" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="G87" s="25" t="n">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="H87" s="26">
         <f>F87*G87</f>
@@ -5959,7 +5967,7 @@
       </c>
       <c r="I87" s="23" t="inlineStr">
         <is>
-          <t>OA keukenbouwer</t>
+          <t>OA stoffeerder</t>
         </is>
       </c>
       <c r="J87" s="23" t="inlineStr">
@@ -5969,7 +5977,7 @@
       </c>
       <c r="K87" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
+          <t>Raamlengtes uitmeten</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5992,7 @@
       </c>
       <c r="C88" s="23" t="inlineStr">
         <is>
-          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
+          <t>Keukenblok woonkamer (multiplex/HPL, RVS-grepen, onderkasten)</t>
         </is>
       </c>
       <c r="D88" s="23" t="inlineStr">
@@ -5994,14 +6002,14 @@
       </c>
       <c r="E88" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F88" s="24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G88" s="25" t="n">
-        <v>520</v>
+        <v>780</v>
       </c>
       <c r="H88" s="26">
         <f>F88*G88</f>
@@ -6030,24 +6038,24 @@
       </c>
       <c r="C89" s="23" t="inlineStr">
         <is>
-          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+          <t>Keukenblok eetruimte</t>
         </is>
       </c>
       <c r="D89" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.7.3</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E89" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F89" s="24" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G89" s="25" t="n">
-        <v>1350</v>
+        <v>780</v>
       </c>
       <c r="H89" s="26">
         <f>F89*G89</f>
@@ -6063,29 +6071,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K89" s="23" t="inlineStr">
-        <is>
-          <t>29 kamers (kk op alle plattegronden). LET OP: T.0.01/R.0.01 tonen GEEN water/afvoer naar de kamers; BBN 3.7.3 vraagt wel RVS-spoelbak + kraan</t>
-        </is>
-      </c>
+      <c r="K89" s="23" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B90" s="23" t="inlineStr">
         <is>
-          <t>Realiseren douchevoorzieningen</t>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
         </is>
       </c>
       <c r="C90" s="23" t="inlineStr">
         <is>
-          <t>HPL-douchecabines incl. scheidingswanden, deuren en beslag (0.37 en 0.42)</t>
+          <t>Inductiekookplaat 4-pits (4 st woonkamer, 2 st eetruimte)</t>
         </is>
       </c>
       <c r="D90" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 14</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E90" s="23" t="inlineStr">
@@ -6094,10 +6098,10 @@
         </is>
       </c>
       <c r="F90" s="24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G90" s="25" t="n">
-        <v>1650</v>
+        <v>950</v>
       </c>
       <c r="H90" s="26">
         <f>F90*G90</f>
@@ -6105,49 +6109,49 @@
       </c>
       <c r="I90" s="23" t="inlineStr">
         <is>
-          <t>OA leverancier cabines</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J90" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
+          <t>Richtprijs</t>
         </is>
       </c>
       <c r="K90" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 14: HPL-cabines en -wanden toegestaan, zoals op de verdiepingen</t>
+          <t>E&amp;W 10.7.6 zegt: keukenapparatuur door derden – navragen</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B91" s="23" t="inlineStr">
         <is>
-          <t>Realiseren douchevoorzieningen</t>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
         </is>
       </c>
       <c r="C91" s="23" t="inlineStr">
         <is>
-          <t>Wandtegelwerk wit geglazuurd op buitenwanden douche-/badruimten incl. afdichtingssysteem</t>
+          <t>RVS spoelbak + kraan gemeenschappelijke keukens</t>
         </is>
       </c>
       <c r="D91" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.4 + NvI vraag 16</t>
+          <t>BBN 3.7.2</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F91" s="24" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="G91" s="25" t="n">
-        <v>92</v>
+        <v>520</v>
       </c>
       <c r="H91" s="26">
         <f>F91*G91</f>
@@ -6155,7 +6159,7 @@
       </c>
       <c r="I91" s="23" t="inlineStr">
         <is>
-          <t>OA tegelzetter</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J91" s="23" t="inlineStr">
@@ -6163,41 +6167,37 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K91" s="23" t="inlineStr">
-        <is>
-          <t>NvI vraag 16: gebruikelijke kwaliteit, geglazuurd wit. Minder m² door HPL-cabines</t>
-        </is>
-      </c>
+      <c r="K91" s="23" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B92" s="23" t="inlineStr">
+        <is>
+          <t>Realiseren vaste keukenvoorzieningen en pantry's</t>
+        </is>
+      </c>
+      <c r="C92" s="23" t="inlineStr">
+        <is>
+          <t>Pantry slaapkamer (werkblad, onderkast, RVS spoelbak/kraan, nis koelkast, WCD)</t>
+        </is>
+      </c>
+      <c r="D92" s="23" t="inlineStr">
+        <is>
+          <t>BBN 3.7.3</t>
+        </is>
+      </c>
+      <c r="E92" s="23" t="inlineStr">
+        <is>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="F92" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="B92" s="23" t="inlineStr">
-        <is>
-          <t>Realiseren douchevoorzieningen</t>
-        </is>
-      </c>
-      <c r="C92" s="23" t="inlineStr">
-        <is>
-          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
-        </is>
-      </c>
-      <c r="D92" s="23" t="inlineStr">
-        <is>
-          <t>BBN 3.2.3</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="F92" s="24" t="n">
-        <v>45</v>
-      </c>
       <c r="G92" s="25" t="n">
-        <v>145</v>
+        <v>1350</v>
       </c>
       <c r="H92" s="26">
         <f>F92*G92</f>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="I92" s="23" t="inlineStr">
         <is>
-          <t>OA tegelzetter</t>
+          <t>OA keukenbouwer</t>
         </is>
       </c>
       <c r="J92" s="23" t="inlineStr">
@@ -6213,7 +6213,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K92" s="23" t="inlineStr"/>
+      <c r="K92" s="23" t="inlineStr">
+        <is>
+          <t>29 kamers (kk op alle plattegronden). LET OP: T.0.01/R.0.01 tonen GEEN water/afvoer naar de kamers; BBN 3.7.3 vraagt wel RVS-spoelbak + kraan</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="23" t="n">
@@ -6226,12 +6230,12 @@
       </c>
       <c r="C93" s="23" t="inlineStr">
         <is>
-          <t>Douchedeuren 0.70/0.71 (vochtbestendig, Trespa o.g.)</t>
+          <t>HPL-douchecabines incl. scheidingswanden, deuren en beslag (0.37 en 0.42)</t>
         </is>
       </c>
       <c r="D93" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.4.3</t>
+          <t>NvI vraag 14</t>
         </is>
       </c>
       <c r="E93" s="23" t="inlineStr">
@@ -6240,10 +6244,10 @@
         </is>
       </c>
       <c r="F93" s="24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G93" s="25" t="n">
-        <v>680</v>
+        <v>1650</v>
       </c>
       <c r="H93" s="26">
         <f>F93*G93</f>
@@ -6251,49 +6255,49 @@
       </c>
       <c r="I93" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA leverancier cabines</t>
         </is>
       </c>
       <c r="J93" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
+          <t>Offerte aanvragen</t>
         </is>
       </c>
       <c r="K93" s="23" t="inlineStr">
         <is>
-          <t>Deuren van de cabines in 0.37/0.42 zitten in de HPL-post</t>
+          <t>NvI vraag 14: HPL-cabines en -wanden toegestaan, zoals op de verdiepingen</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B94" s="23" t="inlineStr">
         <is>
-          <t>Realiseren hekwerk terrein</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C94" s="23" t="inlineStr">
         <is>
-          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
+          <t>Wandtegelwerk wit geglazuurd op buitenwanden douche-/badruimten incl. afdichtingssysteem</t>
         </is>
       </c>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.2</t>
+          <t>BBN 3.3.4 + NvI vraag 16</t>
         </is>
       </c>
       <c r="E94" s="23" t="inlineStr">
         <is>
-          <t>m1</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F94" s="24" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="G94" s="25" t="n">
-        <v>285</v>
+        <v>92</v>
       </c>
       <c r="H94" s="26">
         <f>F94*G94</f>
@@ -6301,7 +6305,7 @@
       </c>
       <c r="I94" s="23" t="inlineStr">
         <is>
-          <t>OA hekwerk</t>
+          <t>OA tegelzetter</t>
         </is>
       </c>
       <c r="J94" s="23" t="inlineStr">
@@ -6311,39 +6315,39 @@
       </c>
       <c r="K94" s="23" t="inlineStr">
         <is>
-          <t>Bijlage 1: aluminium balustrade gelijk aan uitvoering bij de trappen. Lengte uitmeten</t>
+          <t>NvI vraag 16: gebruikelijke kwaliteit, geglazuurd wit. Minder m² door HPL-cabines</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B95" s="23" t="inlineStr">
         <is>
-          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C95" s="23" t="inlineStr">
         <is>
-          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
+          <t>Vloertegels douches, antislip, incl. afschot en afdichting</t>
         </is>
       </c>
       <c r="D95" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.1</t>
+          <t>BBN 3.2.3</t>
         </is>
       </c>
       <c r="E95" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="F95" s="24" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="G95" s="25" t="n">
-        <v>1500</v>
+        <v>145</v>
       </c>
       <c r="H95" s="26">
         <f>F95*G95</f>
@@ -6351,7 +6355,7 @@
       </c>
       <c r="I95" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA tegelzetter</t>
         </is>
       </c>
       <c r="J95" s="23" t="inlineStr">
@@ -6363,33 +6367,33 @@
     </row>
     <row r="96">
       <c r="A96" s="23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B96" s="23" t="inlineStr">
         <is>
-          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
+          <t>Realiseren douchevoorzieningen</t>
         </is>
       </c>
       <c r="C96" s="23" t="inlineStr">
         <is>
-          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
+          <t>Douchedeuren 0.70/0.71 (vochtbestendig, Trespa o.g.)</t>
         </is>
       </c>
       <c r="D96" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.8.1</t>
+          <t>BBN 3.4.3</t>
         </is>
       </c>
       <c r="E96" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F96" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="25" t="n">
-        <v>4300</v>
+        <v>680</v>
       </c>
       <c r="H96" s="26">
         <f>F96*G96</f>
@@ -6405,37 +6409,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K96" s="23" t="inlineStr"/>
+      <c r="K96" s="23" t="inlineStr">
+        <is>
+          <t>Deuren van de cabines in 0.37/0.42 zitten in de HPL-post</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B97" s="23" t="inlineStr">
         <is>
-          <t>Realiseren fietsenstalling</t>
+          <t>Realiseren hekwerk terrein</t>
         </is>
       </c>
       <c r="C97" s="23" t="inlineStr">
         <is>
-          <t>Fietsenstalling: buiten beschouwing volgens NvI vraag 3/29</t>
+          <t>Hekwerk ≥1 m op gemetselde muur, chemische ankers, 'zwevend' boven tegels, incl. opname</t>
         </is>
       </c>
       <c r="D97" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 3/29</t>
+          <t>BBN 3.8.2</t>
         </is>
       </c>
       <c r="E97" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="F97" s="24" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G97" s="25" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="H97" s="26">
         <f>F97*G97</f>
@@ -6443,7 +6451,7 @@
       </c>
       <c r="I97" s="23" t="inlineStr">
         <is>
-          <t>n.v.t.</t>
+          <t>OA hekwerk</t>
         </is>
       </c>
       <c r="J97" s="23" t="inlineStr">
@@ -6453,27 +6461,27 @@
       </c>
       <c r="K97" s="23" t="inlineStr">
         <is>
-          <t>NvI: fietsenstalling wordt buiten beschouwing gelaten → € 0 in het formulier</t>
+          <t>Bijlage 1: aluminium balustrade gelijk aan uitvoering bij de trappen. Lengte uitmeten</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="23" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B98" s="23" t="inlineStr">
         <is>
-          <t>Doorvoeringen inbranden voor de installaties</t>
+          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
         </is>
       </c>
       <c r="C98" s="23" t="inlineStr">
         <is>
-          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
+          <t>Drie entrees tuinzijde met hergebruik dubbele deuren</t>
         </is>
       </c>
       <c r="D98" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
+          <t>BBN 3.8.1</t>
         </is>
       </c>
       <c r="E98" s="23" t="inlineStr">
@@ -6482,10 +6490,10 @@
         </is>
       </c>
       <c r="F98" s="24" t="n">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="G98" s="25" t="n">
-        <v>48</v>
+        <v>1500</v>
       </c>
       <c r="H98" s="26">
         <f>F98*G98</f>
@@ -6493,37 +6501,33 @@
       </c>
       <c r="I98" s="23" t="inlineStr">
         <is>
-          <t>VMT Brandpreventie</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J98" s="23" t="inlineStr">
         <is>
-          <t>Offerte aanvragen</t>
-        </is>
-      </c>
-      <c r="K98" s="23" t="inlineStr">
-        <is>
-          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
-        </is>
-      </c>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K98" s="23" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="23" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B99" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
+          <t>Realiseren entree's, incl. bijbehorende voorzieningen</t>
         </is>
       </c>
       <c r="C99" s="23" t="inlineStr">
         <is>
-          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
+          <t>Betontegels 1x2x0,1 m als opstap + toegankelijke helling binnen ≤3 m</t>
         </is>
       </c>
       <c r="D99" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.1</t>
+          <t>BBN 3.8.1</t>
         </is>
       </c>
       <c r="E99" s="23" t="inlineStr">
@@ -6535,7 +6539,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="25" t="n">
-        <v>5000</v>
+        <v>4300</v>
       </c>
       <c r="H99" s="26">
         <f>F99*G99</f>
@@ -6555,21 +6559,21 @@
     </row>
     <row r="100">
       <c r="A100" s="23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B100" s="23" t="inlineStr">
         <is>
-          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
+          <t>Realiseren fietsenstalling</t>
         </is>
       </c>
       <c r="C100" s="23" t="inlineStr">
         <is>
-          <t>Opleveringsschoonmaak</t>
+          <t>Fietsenstalling: buiten beschouwing volgens NvI vraag 3/29</t>
         </is>
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>BBN 6.2</t>
+          <t>NvI vraag 3/29</t>
         </is>
       </c>
       <c r="E100" s="23" t="inlineStr">
@@ -6578,10 +6582,10 @@
         </is>
       </c>
       <c r="F100" s="24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="25" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H100" s="26">
         <f>F100*G100</f>
@@ -6589,7 +6593,7 @@
       </c>
       <c r="I100" s="23" t="inlineStr">
         <is>
-          <t>OA schoonmaak</t>
+          <t>n.v.t.</t>
         </is>
       </c>
       <c r="J100" s="23" t="inlineStr">
@@ -6597,37 +6601,41 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K100" s="23" t="inlineStr"/>
+      <c r="K100" s="23" t="inlineStr">
+        <is>
+          <t>NvI: fietsenstalling wordt buiten beschouwing gelaten → € 0 in het formulier</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="23" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B101" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Doorvoeringen inbranden voor de installaties</t>
         </is>
       </c>
       <c r="C101" s="23" t="inlineStr">
         <is>
-          <t>Bouwkundige engineering, detaillering, constructeur</t>
+          <t>Brandwerende doorvoeringen (W/E/data) incl. codering en logboek conform bovenverdiepingen (VMT Zwolle)</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.1</t>
+          <t>BBN 3.3.1 / E&amp;W 4.6/10.5.7</t>
         </is>
       </c>
       <c r="E101" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F101" s="24" t="n">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="G101" s="25" t="n">
-        <v>12000</v>
+        <v>48</v>
       </c>
       <c r="H101" s="26">
         <f>F101*G101</f>
@@ -6635,33 +6643,37 @@
       </c>
       <c r="I101" s="23" t="inlineStr">
         <is>
-          <t>VDL / adviseur</t>
+          <t>VMT Brandpreventie</t>
         </is>
       </c>
       <c r="J101" s="23" t="inlineStr">
         <is>
-          <t>Richtprijs</t>
-        </is>
-      </c>
-      <c r="K101" s="23" t="inlineStr"/>
+          <t>Offerte aanvragen</t>
+        </is>
+      </c>
+      <c r="K101" s="23" t="inlineStr">
+        <is>
+          <t>VMT is 'voorgesteld' – offerte opvragen; aantal inschatten met installateurs</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B102" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
         </is>
       </c>
       <c r="C102" s="23" t="inlineStr">
         <is>
-          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
+          <t>Bescherming bestaande bouw (vloeren, lift, looproutes), nulmeting met foto's</t>
         </is>
       </c>
       <c r="D102" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.7/3.9</t>
+          <t>BBN 6.1</t>
         </is>
       </c>
       <c r="E102" s="23" t="inlineStr">
@@ -6673,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="25" t="n">
-        <v>18000</v>
+        <v>5000</v>
       </c>
       <c r="H102" s="26">
         <f>F102*G102</f>
@@ -6681,7 +6693,7 @@
       </c>
       <c r="I102" s="23" t="inlineStr">
         <is>
-          <t>OA installateurs</t>
+          <t>VDL</t>
         </is>
       </c>
       <c r="J102" s="23" t="inlineStr">
@@ -6689,29 +6701,25 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K102" s="23" t="inlineStr">
-        <is>
-          <t>Reken op 5 weken review-cyclus met Winkelman</t>
-        </is>
-      </c>
+      <c r="K102" s="23" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B103" s="23" t="inlineStr">
         <is>
-          <t>Engineering en coördinatiekosten</t>
+          <t>Evt. andere bijkomende kosten (bouwkundig)</t>
         </is>
       </c>
       <c r="C103" s="23" t="inlineStr">
         <is>
-          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
+          <t>Opleveringsschoonmaak</t>
         </is>
       </c>
       <c r="D103" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9 / E&amp;W 3.3</t>
+          <t>BBN 6.2</t>
         </is>
       </c>
       <c r="E103" s="23" t="inlineStr">
@@ -6723,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="G103" s="25" t="n">
-        <v>16000</v>
+        <v>3500</v>
       </c>
       <c r="H103" s="26">
         <f>F103*G103</f>
@@ -6731,7 +6739,7 @@
       </c>
       <c r="I103" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA schoonmaak</t>
         </is>
       </c>
       <c r="J103" s="23" t="inlineStr">
@@ -6743,21 +6751,21 @@
     </row>
     <row r="104">
       <c r="A104" s="23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B104" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C104" s="23" t="inlineStr">
         <is>
-          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
+          <t>Bouwkundige engineering, detaillering, constructeur</t>
         </is>
       </c>
       <c r="D104" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.6 / E&amp;W 3.9</t>
+          <t>BBN 4.1</t>
         </is>
       </c>
       <c r="E104" s="23" t="inlineStr">
@@ -6769,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="25" t="n">
-        <v>6500</v>
+        <v>12000</v>
       </c>
       <c r="H104" s="26">
         <f>F104*G104</f>
@@ -6777,7 +6785,7 @@
       </c>
       <c r="I104" s="23" t="inlineStr">
         <is>
-          <t>VDL + OA</t>
+          <t>VDL / adviseur</t>
         </is>
       </c>
       <c r="J104" s="23" t="inlineStr">
@@ -6789,33 +6797,33 @@
     </row>
     <row r="105">
       <c r="A105" s="23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B105" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C105" s="23" t="inlineStr">
         <is>
-          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
+          <t>Installatie-engineering: werktekeningen, VABI, tapwater-, licht-, kabelberekeningen</t>
         </is>
       </c>
       <c r="D105" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9</t>
+          <t>E&amp;W 3.7/3.9</t>
         </is>
       </c>
       <c r="E105" s="23" t="inlineStr">
         <is>
-          <t>week</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F105" s="24" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G105" s="25" t="n">
-        <v>2600</v>
+        <v>18000</v>
       </c>
       <c r="H105" s="26">
         <f>F105*G105</f>
@@ -6823,7 +6831,7 @@
       </c>
       <c r="I105" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA installateurs</t>
         </is>
       </c>
       <c r="J105" s="23" t="inlineStr">
@@ -6833,27 +6841,27 @@
       </c>
       <c r="K105" s="23" t="inlineStr">
         <is>
-          <t>Start ca. 9 nov; NvI vraag 8: uitloop maximaal 6 weken toegestaan</t>
+          <t>Reken op 5 weken review-cyclus met Winkelman</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B106" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Engineering en coördinatiekosten</t>
         </is>
       </c>
       <c r="C106" s="23" t="inlineStr">
         <is>
-          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
+          <t>Projectleiding, werkvoorbereiding, coördinatie nevenaannemers (Trigion) en VGM-coördinatie</t>
         </is>
       </c>
       <c r="D106" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3</t>
+          <t>BBN 3.9 / E&amp;W 3.3</t>
         </is>
       </c>
       <c r="E106" s="23" t="inlineStr">
@@ -6865,7 +6873,7 @@
         <v>1</v>
       </c>
       <c r="G106" s="25" t="n">
-        <v>5500</v>
+        <v>16000</v>
       </c>
       <c r="H106" s="26">
         <f>F106*G106</f>
@@ -6885,33 +6893,33 @@
     </row>
     <row r="107">
       <c r="A107" s="23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B107" s="23" t="inlineStr">
         <is>
-          <t>Algemene Bouwplaatskosten (ABK)</t>
+          <t>Revisietekeningen</t>
         </is>
       </c>
       <c r="C107" s="23" t="inlineStr">
         <is>
-          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
+          <t>Revisietekeningen (PDF + DWG/IFC), technisch dossier, opleverdossier fysiek + digitaal</t>
         </is>
       </c>
       <c r="D107" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.3/6.2</t>
+          <t>BBN 4.6 / E&amp;W 3.9</t>
         </is>
       </c>
       <c r="E107" s="23" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>post</t>
         </is>
       </c>
       <c r="F107" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G107" s="25" t="n">
-        <v>475</v>
+        <v>6500</v>
       </c>
       <c r="H107" s="26">
         <f>F107*G107</f>
@@ -6919,7 +6927,7 @@
       </c>
       <c r="I107" s="23" t="inlineStr">
         <is>
-          <t>OA afval</t>
+          <t>VDL + OA</t>
         </is>
       </c>
       <c r="J107" s="23" t="inlineStr">
@@ -6940,24 +6948,24 @@
       </c>
       <c r="C108" s="23" t="inlineStr">
         <is>
-          <t>V&amp;G-plan uitvoeringsfase (concept 2 weken voor start), werkplan, bouwplaatsinrichting, afzettingen</t>
+          <t>Uitvoerder (VCA-Vol, dagelijks aanwezig)</t>
         </is>
       </c>
       <c r="D108" s="23" t="inlineStr">
         <is>
-          <t>BBN 3.9/4.3/6.3 + NvI vraag 8</t>
+          <t>BBN 3.9</t>
         </is>
       </c>
       <c r="E108" s="23" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>week</t>
         </is>
       </c>
       <c r="F108" s="24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G108" s="25" t="n">
-        <v>3500</v>
+        <v>2600</v>
       </c>
       <c r="H108" s="26">
         <f>F108*G108</f>
@@ -6973,7 +6981,11 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K108" s="23" t="inlineStr"/>
+      <c r="K108" s="23" t="inlineStr">
+        <is>
+          <t>Start ca. 9 nov; NvI vraag 8: uitloop maximaal 6 weken toegestaan</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="23" t="n">
@@ -6986,12 +6998,12 @@
       </c>
       <c r="C109" s="23" t="inlineStr">
         <is>
-          <t>Klein materieel, steigers/rolsteigers, transport</t>
+          <t>Inpandige schaft-, sanitaire en opslagvoorzieningen</t>
         </is>
       </c>
       <c r="D109" s="23" t="inlineStr">
         <is>
-          <t>BBN 4.2</t>
+          <t>BBN 4.3</t>
         </is>
       </c>
       <c r="E109" s="23" t="inlineStr">
@@ -7003,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="25" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="H109" s="26">
         <f>F109*G109</f>
@@ -7032,24 +7044,24 @@
       </c>
       <c r="C110" s="23" t="inlineStr">
         <is>
-          <t>Parkeerkosten openbare weg (2 voertuigen × ca. 65 werkdagen)</t>
+          <t>Afvalcontainers gescheiden afvoer incl. vergunning</t>
         </is>
       </c>
       <c r="D110" s="23" t="inlineStr">
         <is>
-          <t>NvI vraag 9</t>
+          <t>BBN 4.3/6.2</t>
         </is>
       </c>
       <c r="E110" s="23" t="inlineStr">
         <is>
-          <t>dag</t>
+          <t>st</t>
         </is>
       </c>
       <c r="F110" s="24" t="n">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="G110" s="25" t="n">
-        <v>20</v>
+        <v>475</v>
       </c>
       <c r="H110" s="26">
         <f>F110*G110</f>
@@ -7057,7 +7069,7 @@
       </c>
       <c r="I110" s="23" t="inlineStr">
         <is>
-          <t>VDL</t>
+          <t>OA afval</t>
         </is>
       </c>
       <c r="J110" s="23" t="inlineStr">
@@ -7065,11 +7077,7 @@
           <t>Richtprijs</t>
         </is>
       </c>
-      <c r="K110" s="23" t="inlineStr">
-        <is>
-          <t>NvI vraag 9: geen plekken op terrein, openbare weg is betaald parkeren</t>
-        </is>
-      </c>
+      <c r="K110" s="23" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="23" t="n">
@@ -7082,12 +7090,12 @@
       </c>
       <c r="C111" s="23" t="inlineStr">
         <is>
-          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+          <t>V&amp;G-plan uitvoeringsfase (concept 2 weken voor start), werkplan, bouwplaatsinrichting, afzettingen</t>
         </is>
       </c>
       <c r="D111" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 3.2 / BBN 4.4</t>
+          <t>BBN 3.9/4.3/6.3 + NvI vraag 8</t>
         </is>
       </c>
       <c r="E111" s="23" t="inlineStr">
@@ -7099,7 +7107,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="25" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="H111" s="26">
         <f>F111*G111</f>
@@ -7117,27 +7125,169 @@
       </c>
       <c r="K111" s="23" t="inlineStr"/>
     </row>
-    <row r="112"/>
+    <row r="112">
+      <c r="A112" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B112" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C112" s="23" t="inlineStr">
+        <is>
+          <t>Klein materieel, steigers/rolsteigers, transport</t>
+        </is>
+      </c>
+      <c r="D112" s="23" t="inlineStr">
+        <is>
+          <t>BBN 4.2</t>
+        </is>
+      </c>
+      <c r="E112" s="23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="25" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H112" s="26">
+        <f>F112*G112</f>
+        <v/>
+      </c>
+      <c r="I112" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J112" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K112" s="23" t="inlineStr"/>
+    </row>
     <row r="113">
-      <c r="C113" s="16" t="inlineStr">
+      <c r="A113" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
+        <is>
+          <t>Parkeerkosten openbare weg (2 voertuigen × ca. 65 werkdagen)</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 9</t>
+        </is>
+      </c>
+      <c r="E113" s="23" t="inlineStr">
+        <is>
+          <t>dag</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="G113" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H113" s="26">
+        <f>F113*G113</f>
+        <v/>
+      </c>
+      <c r="I113" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J113" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K113" s="23" t="inlineStr">
+        <is>
+          <t>NvI vraag 9: geen plekken op terrein, openbare weg is betaald parkeren</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>Algemene Bouwplaatskosten (ABK)</t>
+        </is>
+      </c>
+      <c r="C114" s="23" t="inlineStr">
+        <is>
+          <t>Hinderbeperking bewoond gebouw (stofschotten, geluidsarm werken, bewonerscommunicatie)</t>
+        </is>
+      </c>
+      <c r="D114" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 3.2 / BBN 4.4</t>
+        </is>
+      </c>
+      <c r="E114" s="23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H114" s="26">
+        <f>F114*G114</f>
+        <v/>
+      </c>
+      <c r="I114" s="23" t="inlineStr">
+        <is>
+          <t>VDL</t>
+        </is>
+      </c>
+      <c r="J114" s="23" t="inlineStr">
+        <is>
+          <t>Richtprijs</t>
+        </is>
+      </c>
+      <c r="K114" s="23" t="inlineStr"/>
+    </row>
+    <row r="115"/>
+    <row r="116">
+      <c r="C116" s="16" t="inlineStr">
         <is>
           <t>Totaal directe kosten (excl. opslagen AK/W&amp;R/CAR en risico's)</t>
         </is>
       </c>
-      <c r="H113" s="28">
-        <f>SUM(H2:H111)</f>
+      <c r="H116" s="28">
+        <f>SUM(H2:H114)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K111"/>
-  <conditionalFormatting sqref="J2:J111">
+  <autoFilter ref="A1:K114"/>
+  <conditionalFormatting sqref="J2:J114">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J2="Richtprijs"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104 J105 J106 J107 J108 J109 J110 J111 J112 J113 J114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Richtprijs,Offerte aanvragen,Offerte ontvangen,Eigen norm,Stelpost (voorgeschreven)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7151,7 +7301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7804,19 +7954,19 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Tellingen uit PDF-tekeningen wijken af van de werkelijke aantallen</t>
+          <t>Coördinatie nevenaannemer Trigion: geen coördinatieplicht, offerte aan gemeente verlopen (30 dagen vanaf 7 apr 2026), kabels moeten gereed en gelabeld zijn bij start</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Tekeningen E.001, L.0.01, T.0.01</t>
+          <t>Bijlage 5 (Trigion)</t>
         </is>
       </c>
       <c r="D16" s="29" t="n">
         <v>0.3</v>
       </c>
       <c r="E16" s="30" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="F16" s="26">
         <f>D16*E16</f>
@@ -7836,7 +7986,7 @@
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>Tellingen zijn visueel/uit tekstlabels. Laat installateurs natellen op DWG (NvI vraag 2).</t>
+          <t>Planning en interface Trigion ligt feitelijk bij de hoofdaannemer.</t>
         </is>
       </c>
     </row>
@@ -7846,19 +7996,19 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+          <t>Deurcontacten niet in Trigion-offerte (29 deuren)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>E&amp;W 4.2.2/7.1</t>
+          <t>Bijlage 5 vs E.001 (deurcontact)</t>
         </is>
       </c>
       <c r="D17" s="29" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>8000</v>
+        <v>2500</v>
       </c>
       <c r="F17" s="26">
         <f>D17*E17</f>
@@ -7866,11 +8016,11 @@
       </c>
       <c r="G17" s="31" t="inlineStr">
         <is>
-          <t>Nee</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="H17" s="31" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I17" s="26">
         <f>IF(G17="Ja",F17,0)</f>
@@ -7878,36 +8028,162 @@
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
+          <t>E.001 toont deurcontact; Trigion-materiaallijst niet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Plasmafilter geschikt voor max. 55 m³ ruimte; keukens 0.24 (76 m²) en 0.64 groter → geurklachten/extra filters</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Bijlage 6</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F18" s="26">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" s="26">
+        <f>IF(G18="Ja",F18,0)</f>
+        <v/>
+      </c>
+      <c r="J18" s="23" t="inlineStr">
+        <is>
+          <t>Opdrachtgever accepteert restgeur (E&amp;W 8.4.6); gelijkwaardig alternatief toegestaan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Tellingen uit PDF-tekeningen wijken af van de werkelijke aantallen</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Tekeningen E.001, L.0.01, T.0.01</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F19" s="26">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="n">
+        <v>36</v>
+      </c>
+      <c r="I19" s="26">
+        <f>IF(G19="Ja",F19,0)</f>
+        <v/>
+      </c>
+      <c r="J19" s="23" t="inlineStr">
+        <is>
+          <t>Tellingen zijn visueel/uit tekstlabels. Laat installateurs natellen op DWG (NvI vraag 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>WKO-capaciteit / inregelen onvoldoende (nooit waterzijdig ingeregeld)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>E&amp;W 4.2.2/7.1</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F20" s="26">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" s="26">
+        <f>IF(G20="Ja",F20,0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
+        <is>
           <t>Het bestek stelt dat de aannemer mag uitgaan van voldoende capaciteit, dus dit risico ligt bij de opdrachtgever.</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="16" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Totaal meegeprijsde risico's</t>
         </is>
       </c>
-      <c r="I19" s="28">
-        <f>SUM(I2:I17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="32" t="inlineStr">
+      <c r="I22" s="28">
+        <f>SUM(I2:I20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Totaal verwachte waarde alle risico's (ter info)</t>
         </is>
       </c>
-      <c r="I20" s="20">
-        <f>SUM(F2:F17)</f>
+      <c r="I23" s="20">
+        <f>SUM(F2:F20)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G2:G20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Ja,Nee"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9546,7 +9822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10269,52 +10545,133 @@
     <row r="29">
       <c r="A29" s="37" t="inlineStr">
         <is>
-          <t>Glazen puien hergebruik + folie</t>
+          <t>Toegangscontrole: paslezers / deurcontrollers</t>
         </is>
       </c>
       <c r="B29" s="37" t="inlineStr">
         <is>
-          <t>ca. 90 m²</t>
+          <t>29 / 29 (17 zuid, 12 noord)</t>
         </is>
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>Bijlage 4</t>
+          <t>Bijlage 5 + schetsen toegangscontrole</t>
         </is>
       </c>
       <c r="D29" s="37" t="inlineStr">
         <is>
-          <t>0.44/0.45, 0.62/0.63 (halzijde), 0.64</t>
+          <t>Controllers centraal in techniekruimten 0.27a en 0.59a</t>
         </is>
       </c>
       <c r="E29" s="37" t="inlineStr">
         <is>
-          <t>Laag</t>
+          <t>Hoog</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="37" t="inlineStr">
         <is>
+          <t>Camera's</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>10 (7 binnen, 3 buiten)</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 5</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="inlineStr">
+        <is>
+          <t>Apparatuur door Trigion; bekabeling door aannemer</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>Afzuigkappen + plasmafilters</t>
+        </is>
+      </c>
+      <c r="B31" s="37" t="inlineStr">
+        <is>
+          <t>4 in offerte / 8 volgens E&amp;W / 7 op E.001</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 6</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="inlineStr">
+        <is>
+          <t>€ 1.774,08 per kap + filter, af magazijn</t>
+        </is>
+      </c>
+      <c r="E31" s="37" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>Glazen puien hergebruik + folie</t>
+        </is>
+      </c>
+      <c r="B32" s="37" t="inlineStr">
+        <is>
+          <t>ca. 90 m²</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>Bijlage 4</t>
+        </is>
+      </c>
+      <c r="D32" s="37" t="inlineStr">
+        <is>
+          <t>0.44/0.45, 0.62/0.63 (halzijde), 0.64</t>
+        </is>
+      </c>
+      <c r="E32" s="37" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
           <t>Douches in 0.37/0.42</t>
         </is>
       </c>
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>8 (waarvan 2 van 2,3 m²)</t>
         </is>
       </c>
-      <c r="C30" s="37" t="inlineStr">
+      <c r="C33" s="37" t="inlineStr">
         <is>
           <t>Bijlage 1</t>
         </is>
       </c>
-      <c r="D30" s="37" t="inlineStr">
+      <c r="D33" s="37" t="inlineStr">
         <is>
           <t>0.38–0.46; mogelijk 2 MIVA-douches (componentenboek nr. 10)</t>
         </is>
       </c>
-      <c r="E30" s="37" t="inlineStr">
+      <c r="E33" s="37" t="inlineStr">
         <is>
           <t>Middel</t>
         </is>
